--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16D95B83-542B-4046-816F-5C09D0943877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5317489F-AD58-4C14-864F-F83A47E41F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -289,54 +289,6 @@
       <t>イチランガメン</t>
     </rPh>
     <rPh sb="8" eb="10">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.従業員がメニュー画面で「タスク一覧」を選択する。
-2.システムがデータベースからタスク情報を取得する。
-3.システムが取得した情報を一覧表示用に編集する。
-4.システムがタスク一覧画面を表示する。</t>
-    <rPh sb="2" eb="5">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガメンイチランガメンヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">A1:タスク情報が存在しない場合
-発生箇所：基本フロー2
-A1-1:「登録されているタスクはありません。」を表示する。
-A2：タスク未選択で編集ボタン押下
-発生箇所：基本フロー4
-A2-1:「タスクを選択してください。」を表示する。
-A3：タスク未選択で削除ボタン押下
-発生箇所：基本フロー4
-A3-1:「タスクを選択してください。」を表示する。
-</t>
-    <rPh sb="101" eb="103">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">E1:データベース接続失敗
-発生箇所：基本フロー2
-E1-1「システムエラーが発生しました。」を表示する。
-</t>
-    <rPh sb="9" eb="11">
-      <t>セツゾク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -635,6 +587,71 @@
   </si>
   <si>
     <t>画面設計書</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
+2.システムがデータベースからタスク情報を取得する。
+3.システムが取得した情報を一覧表示用に編集する。
+4.システムがタスク一覧画面を表示する。
+</t>
+    <rPh sb="2" eb="5">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメンイチランガメンヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">E1:データベース接続に失敗した場合
+E1-1.基本フロー4でシステムはデータベース接続に失敗する。
+E1-2.システムはエラーメッセージを表示する。
+E1-3.従業員は基本フロー1に戻る。
+</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A1:タスク情報が存在しない場合
+A1-1:基本フロー2でシステムはタスクの情報の有無を検出する。
+A1-2:「登録されているタスクはありません。」を表示する。
+A1-3:従業員は基本フロー1に戻る。
+A2：タスク未選択で編集ボタン押下
+A2-1:基本フロー4でシステムはタスク未選択を検出
+A2-1:「タスクを選択してください。」を表示する。
+A2-2:従業員は基本フロー1に戻る。
+A3：タスク未選択で削除ボタン押下
+A3-1:基本フロー4でシステムはタスク未選択を検出
+A3-1:「タスクを選択してください。」を表示する。
+A3-2:従業員は基本フロー1に戻る。
+</t>
+    <rPh sb="38" eb="40">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ウム</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="86" eb="89">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="140" eb="143">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>センタク</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1531,12 +1548,360 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1546,138 +1911,102 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1687,323 +2016,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3409,85 +3426,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="113"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3507,46 +3524,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="73" t="s">
+      <c r="G13" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="73" t="s">
+      <c r="H13" s="111"/>
+      <c r="I13" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="50"/>
-      <c r="K13" s="48"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="111"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="73"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="48"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="111"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="73"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="48"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="111"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3555,13 +3572,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="74" t="s">
+      <c r="G17" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4575,19 +4592,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="32" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="32" t="s">
+      <c r="E1" s="137"/>
+      <c r="F1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="33"/>
+      <c r="G1" s="137"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4599,192 +4616,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="34" t="s">
+      <c r="A2" s="131"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="34" t="s">
+      <c r="E2" s="151"/>
+      <c r="F2" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="40">
+      <c r="G2" s="151"/>
+      <c r="H2" s="154">
         <v>46176</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="44"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="45"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="147"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="148"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="70" t="s">
+      <c r="B5" s="121"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="71"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="122"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="51" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="52"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="51" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="138" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="51" t="s">
+      <c r="B8" s="110"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="52"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="65" t="s">
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="124"/>
+    </row>
+    <row r="9" spans="1:10" ht="97.5" customHeight="1">
+      <c r="A9" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="52"/>
-    </row>
-    <row r="10" spans="1:10" ht="165.75" customHeight="1">
-      <c r="A10" s="66"/>
-      <c r="B10" s="47" t="s">
+      <c r="C9" s="111"/>
+      <c r="D9" s="125" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="124"/>
+    </row>
+    <row r="10" spans="1:10" ht="204.75" customHeight="1">
+      <c r="A10" s="140"/>
+      <c r="B10" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="52"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="67"/>
-      <c r="B11" s="47" t="s">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="52"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="125" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="51" t="s">
+      <c r="B12" s="110"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="52"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="124"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="69"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="119"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5775,6 +5792,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5783,25 +5819,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5820,19 +5837,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="32" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="32" t="s">
+      <c r="E1" s="137"/>
+      <c r="F1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="33"/>
+      <c r="G1" s="137"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5844,40 +5861,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
+      <c r="A2" s="131"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="45"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="147"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="148"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7227,595 +7244,595 @@
   <dimension ref="A1:J1014"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="95" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="95" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="95" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="95"/>
+    <col min="1" max="3" width="5.140625" style="32" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="32" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="32" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="167" t="s">
+      <c r="B1" s="162"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="187"/>
-      <c r="F1" s="167" t="s">
+      <c r="E1" s="170"/>
+      <c r="F1" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="187"/>
-      <c r="H1" s="165" t="s">
+      <c r="G1" s="170"/>
+      <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="164" t="s">
+      <c r="I1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="163" t="s">
+      <c r="J1" s="48" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="185"/>
-      <c r="B2" s="184"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="162" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="186"/>
-      <c r="F2" s="162" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="186"/>
-      <c r="H2" s="160">
+      <c r="G2" s="171"/>
+      <c r="H2" s="92">
         <v>46177</v>
       </c>
-      <c r="I2" s="159" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="158"/>
+      <c r="I2" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="185"/>
-      <c r="B3" s="184"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="181"/>
-      <c r="I3" s="181"/>
-      <c r="J3" s="180"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="160"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="179"/>
-      <c r="B4" s="178"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="177"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="174"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="161"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="170"/>
-      <c r="B5" s="169"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="169"/>
-      <c r="J5" s="173"/>
+      <c r="A5" s="101"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="156"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="136"/>
-      <c r="B6" s="127"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="127"/>
-      <c r="F6" s="127"/>
-      <c r="G6" s="127"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="127"/>
-      <c r="J6" s="126"/>
+      <c r="A6" s="60"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="136"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="126"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="136"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="126"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="136"/>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="126"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="136"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="127"/>
-      <c r="J10" s="126"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="136"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="126"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="136"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="126"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="136"/>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="126"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="136"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="126"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="136"/>
-      <c r="B15" s="127"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="126"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="136"/>
-      <c r="B16" s="127"/>
-      <c r="C16" s="127"/>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="126"/>
+      <c r="A16" s="60"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="136"/>
-      <c r="B17" s="127"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="126"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="136"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="126"/>
+      <c r="A18" s="60"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="136"/>
-      <c r="B19" s="127"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="126"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="136"/>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="126"/>
+      <c r="A20" s="60"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="136"/>
-      <c r="B21" s="127"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="126"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="136"/>
-      <c r="B22" s="127"/>
-      <c r="C22" s="127"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="126"/>
+      <c r="A22" s="60"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="136"/>
-      <c r="B23" s="127"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="126"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="136"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="126"/>
+      <c r="A24" s="60"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="136"/>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="126"/>
+      <c r="A25" s="60"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="136"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="127"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="127"/>
-      <c r="J26" s="126"/>
+      <c r="A26" s="60"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="53"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="136"/>
-      <c r="B27" s="127"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="126"/>
+      <c r="A27" s="60"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="53"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="136"/>
-      <c r="B28" s="127"/>
-      <c r="C28" s="127"/>
-      <c r="D28" s="127"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="126"/>
+      <c r="A28" s="60"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="53"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="136"/>
-      <c r="B29" s="127"/>
-      <c r="C29" s="127"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="126"/>
+      <c r="A29" s="60"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="53"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="136"/>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127"/>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="126"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="53"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="136"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="127"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="126"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="53"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="136"/>
-      <c r="B32" s="127"/>
-      <c r="C32" s="127"/>
-      <c r="D32" s="127"/>
-      <c r="E32" s="127"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127"/>
-      <c r="I32" s="127"/>
-      <c r="J32" s="126"/>
+      <c r="A32" s="60"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="53"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="136"/>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="126"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="53"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="136"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="127"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="126"/>
+      <c r="A34" s="60"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="53"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="136"/>
-      <c r="B35" s="127"/>
-      <c r="C35" s="127"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="126"/>
+      <c r="A35" s="60"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="53"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="136"/>
-      <c r="B36" s="127"/>
-      <c r="C36" s="127"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="126"/>
+      <c r="A36" s="60"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="53"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="136"/>
-      <c r="B37" s="127"/>
-      <c r="C37" s="127"/>
-      <c r="D37" s="127"/>
-      <c r="E37" s="127"/>
-      <c r="F37" s="127"/>
-      <c r="G37" s="127"/>
-      <c r="H37" s="127"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="126"/>
+      <c r="A37" s="60"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="53"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="136"/>
-      <c r="B38" s="127"/>
-      <c r="C38" s="127"/>
-      <c r="D38" s="127"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="127"/>
-      <c r="H38" s="127"/>
-      <c r="I38" s="127"/>
-      <c r="J38" s="126"/>
+      <c r="A38" s="60"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="53"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="136"/>
-      <c r="B39" s="127"/>
-      <c r="C39" s="127"/>
-      <c r="D39" s="127"/>
-      <c r="E39" s="127"/>
-      <c r="F39" s="127"/>
-      <c r="G39" s="127"/>
-      <c r="H39" s="127"/>
-      <c r="I39" s="127"/>
-      <c r="J39" s="126"/>
+      <c r="A39" s="60"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="53"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="136"/>
-      <c r="B40" s="127"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="127"/>
-      <c r="J40" s="126"/>
+      <c r="A40" s="60"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="53"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="136"/>
-      <c r="B41" s="127"/>
-      <c r="C41" s="127"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="126"/>
+      <c r="A41" s="60"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="53"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="136"/>
-      <c r="B42" s="127"/>
-      <c r="C42" s="127"/>
-      <c r="D42" s="127"/>
-      <c r="E42" s="127"/>
-      <c r="F42" s="127"/>
-      <c r="G42" s="127"/>
-      <c r="H42" s="127"/>
-      <c r="I42" s="127"/>
-      <c r="J42" s="126"/>
+      <c r="A42" s="60"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="53"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="136"/>
-      <c r="B43" s="127"/>
-      <c r="C43" s="127"/>
-      <c r="D43" s="127"/>
-      <c r="E43" s="127"/>
-      <c r="F43" s="127"/>
-      <c r="G43" s="127"/>
-      <c r="H43" s="127"/>
-      <c r="I43" s="127"/>
-      <c r="J43" s="126"/>
+      <c r="A43" s="60"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="53"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="136"/>
-      <c r="B44" s="127"/>
-      <c r="C44" s="127"/>
-      <c r="D44" s="127"/>
-      <c r="E44" s="127"/>
-      <c r="F44" s="127"/>
-      <c r="G44" s="127"/>
-      <c r="H44" s="127"/>
-      <c r="I44" s="127"/>
-      <c r="J44" s="126"/>
+      <c r="A44" s="60"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="53"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="136"/>
-      <c r="B45" s="127"/>
-      <c r="C45" s="127"/>
-      <c r="D45" s="127"/>
-      <c r="E45" s="127"/>
-      <c r="F45" s="127"/>
-      <c r="G45" s="127"/>
-      <c r="H45" s="127"/>
-      <c r="I45" s="127"/>
-      <c r="J45" s="126"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="53"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="136"/>
-      <c r="B46" s="127"/>
-      <c r="C46" s="127"/>
-      <c r="D46" s="127"/>
-      <c r="E46" s="127"/>
-      <c r="F46" s="127"/>
-      <c r="G46" s="127"/>
-      <c r="H46" s="127"/>
-      <c r="I46" s="127"/>
-      <c r="J46" s="126"/>
+      <c r="A46" s="60"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="53"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="152"/>
-      <c r="B47" s="151"/>
-      <c r="C47" s="151"/>
-      <c r="D47" s="151"/>
-      <c r="E47" s="151"/>
-      <c r="F47" s="151"/>
-      <c r="G47" s="151"/>
-      <c r="H47" s="151"/>
-      <c r="I47" s="151"/>
-      <c r="J47" s="172"/>
+      <c r="A47" s="104"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="157"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
@@ -7828,7 +7845,7 @@
     <row r="56" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="57" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="58" spans="10:10" ht="12.75" customHeight="1">
-      <c r="J58" s="171"/>
+      <c r="J58" s="51"/>
     </row>
     <row r="59" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="60" spans="10:10" ht="12.75" customHeight="1"/>
@@ -7836,956 +7853,956 @@
     <row r="62" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="63" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="64" spans="10:10" ht="12.75" customHeight="1"/>
-    <row r="65" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1001" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1002" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1003" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1004" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1005" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1006" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1007" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1008" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1009" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1010" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1011" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1012" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1013" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1014" s="95" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1002" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1003" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1004" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1005" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1006" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1007" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1008" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1009" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1010" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1011" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1012" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1013" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1014" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:J47"/>
@@ -8813,459 +8830,459 @@
   <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="6.5703125" style="95" customWidth="1"/>
-    <col min="4" max="4" width="22" style="95" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="95" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="95" customWidth="1"/>
-    <col min="7" max="7" width="27.42578125" style="95" customWidth="1"/>
-    <col min="8" max="10" width="16.7109375" style="95" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="95" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="95"/>
+    <col min="1" max="3" width="6.5703125" style="32" customWidth="1"/>
+    <col min="4" max="4" width="22" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="32" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" style="32" customWidth="1"/>
+    <col min="8" max="10" width="16.7109375" style="32" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="32" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="170" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="167" t="s">
+      <c r="A1" s="101" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="166"/>
-      <c r="F1" s="167" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="166"/>
-      <c r="H1" s="165" t="s">
+      <c r="G1" s="75"/>
+      <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="164" t="s">
+      <c r="I1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="163" t="s">
+      <c r="J1" s="48" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="162" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="161"/>
-      <c r="F2" s="162" t="s">
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="161"/>
-      <c r="H2" s="160">
+      <c r="G2" s="81"/>
+      <c r="H2" s="92">
         <v>46177</v>
       </c>
-      <c r="I2" s="159" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="158"/>
+      <c r="I2" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="136"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="153"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="152"/>
-      <c r="B4" s="151"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="146"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="142" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="141"/>
-      <c r="F5" s="141"/>
-      <c r="G5" s="141"/>
-      <c r="H5" s="141"/>
-      <c r="I5" s="141"/>
-      <c r="J5" s="140"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="76" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="116"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="68"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="139"/>
-      <c r="B7" s="138"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="138"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
-      <c r="J7" s="137"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="59"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="136"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="127"/>
-      <c r="I8" s="127"/>
-      <c r="J8" s="126"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="135" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="134" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="134"/>
-      <c r="E9" s="135" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="135" t="s">
+      <c r="A9" s="45"/>
+      <c r="B9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="G9" s="135" t="s">
+      <c r="C9" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="135" t="s">
+      <c r="D9" s="61"/>
+      <c r="E9" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="134" t="s">
+      <c r="F9" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="133"/>
+      <c r="G9" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="62"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="130" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="127" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="130" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="132">
+      <c r="A10" s="45"/>
+      <c r="B10" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="46">
         <v>46203</v>
       </c>
-      <c r="G10" s="130" t="s">
+      <c r="G10" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="130" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="127" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="126"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="130" t="s">
+      <c r="A11" s="45"/>
+      <c r="B11" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="52"/>
+      <c r="E11" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="46">
+        <v>46295</v>
+      </c>
+      <c r="G11" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="132">
-        <v>46295</v>
-      </c>
-      <c r="G11" s="130" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="127" t="s">
-        <v>105</v>
-      </c>
-      <c r="J11" s="126"/>
+      <c r="H11" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="130" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="126"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="130" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="126"/>
+      <c r="A13" s="45"/>
+      <c r="B13" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="131"/>
-      <c r="B14" s="130" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="126"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="129"/>
-      <c r="B15" s="128"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="126"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="121" t="s">
+      <c r="A16" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="116"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="68"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="117"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="119" t="s">
+      <c r="B17" s="67"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="122" t="s">
-        <v>102</v>
+      <c r="J17" s="41" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="121" t="s">
+      <c r="A18" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="119" t="s">
+      <c r="B18" s="67"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="119" t="s">
+      <c r="E18" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="119" t="s">
+      <c r="F18" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="119" t="s">
+      <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="118" t="s">
+      <c r="H18" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="117"/>
-      <c r="J18" s="116"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="68"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A19" s="112" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="111"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="108" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="108" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="108" t="s">
+      <c r="A19" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="55"/>
+      <c r="J19" s="56"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="55"/>
+      <c r="J20" s="56"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="64"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="55"/>
+      <c r="J21" s="56"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="64"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="55"/>
+      <c r="J22" s="56"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="114" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" s="115" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" s="105"/>
-      <c r="J19" s="104"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="111"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="108" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="108" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="114" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="106" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" s="105"/>
-      <c r="J20" s="104"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="111"/>
-      <c r="C21" s="110"/>
-      <c r="D21" s="108" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="108" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="108" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="113" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="106" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" s="105"/>
-      <c r="J21" s="104"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="112" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="111"/>
-      <c r="C22" s="110"/>
-      <c r="D22" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="108" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="108" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="113" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="106" t="s">
-        <v>83</v>
-      </c>
-      <c r="I22" s="105"/>
-      <c r="J22" s="104"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="112" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="111"/>
-      <c r="C23" s="110"/>
-      <c r="D23" s="109" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="109" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="108" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="107" t="s">
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H23" s="106" t="s">
+      <c r="E23" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="105"/>
-      <c r="J23" s="104"/>
+      <c r="F23" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="55"/>
+      <c r="J23" s="56"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="103"/>
-      <c r="B24" s="102"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="96"/>
+      <c r="A24" s="86"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="91"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9275,990 +9292,997 @@
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1001" s="95" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="34" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="35" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="36" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="37" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="38" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="39" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="40" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="41" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="42" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="43" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="44" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="45" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="46" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="47" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="48" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="49" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
@@ -10269,26 +10293,19 @@
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="H20:J20"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10308,182 +10325,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="128" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="32" t="s">
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="32" t="s">
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="32" t="s">
+      <c r="P1" s="137"/>
+      <c r="Q1" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="33"/>
-      <c r="S1" s="32" t="s">
+      <c r="R1" s="137"/>
+      <c r="S1" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="71"/>
+      <c r="T1" s="122"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="82"/>
+      <c r="A2" s="131"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="150"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="150"/>
+      <c r="R2" s="151"/>
+      <c r="S2" s="150"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="37"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="83"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="152"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="152"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="152"/>
+      <c r="P3" s="132"/>
+      <c r="Q3" s="152"/>
+      <c r="R3" s="132"/>
+      <c r="S3" s="152"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="89"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="153"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="153"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="153"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="153"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="70" t="s">
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="64"/>
-      <c r="Q5" s="64"/>
-      <c r="R5" s="64"/>
-      <c r="S5" s="64"/>
-      <c r="T5" s="71"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="121"/>
+      <c r="S5" s="121"/>
+      <c r="T5" s="122"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="51" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="52"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="110"/>
+      <c r="T6" s="124"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="52"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="124"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10682,37 +10699,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="92" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="84" t="s">
+      <c r="D15" s="111"/>
+      <c r="E15" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="84" t="s">
+      <c r="F15" s="111"/>
+      <c r="G15" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="50"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="84" t="s">
+      <c r="H15" s="110"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="84" t="s">
+      <c r="K15" s="111"/>
+      <c r="L15" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="50"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="84" t="s">
+      <c r="M15" s="110"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="48"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="111"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10724,37 +10741,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="90">
+      <c r="A16" s="174">
         <v>1</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="91" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="91" t="s">
+      <c r="D16" s="111"/>
+      <c r="E16" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="85" t="s">
+      <c r="F16" s="111"/>
+      <c r="G16" s="182" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="50"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="85" t="s">
+      <c r="H16" s="110"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="48"/>
-      <c r="L16" s="87" t="s">
+      <c r="K16" s="111"/>
+      <c r="L16" s="178" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="50"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="87" t="s">
+      <c r="M16" s="110"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="178" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="48"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="111"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10766,37 +10783,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="90">
+      <c r="A17" s="174">
         <v>2</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="91" t="s">
+      <c r="B17" s="111"/>
+      <c r="C17" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="91" t="s">
+      <c r="D17" s="111"/>
+      <c r="E17" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="85" t="s">
+      <c r="F17" s="111"/>
+      <c r="G17" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="85" t="s">
+      <c r="H17" s="110"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="182" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="87" t="s">
+      <c r="K17" s="111"/>
+      <c r="L17" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="50"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="87" t="s">
+      <c r="M17" s="110"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="178" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="48"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="111"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10808,23 +10825,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="91"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="87"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="48"/>
+      <c r="A18" s="174"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="111"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10836,23 +10853,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="85"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="87"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="48"/>
+      <c r="A19" s="174"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="111"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10864,23 +10881,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="90"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="85"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="87"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="48"/>
+      <c r="A20" s="174"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="111"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10892,23 +10909,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="90"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="87"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="48"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="110"/>
+      <c r="Q21" s="111"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10920,23 +10937,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="87"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="48"/>
+      <c r="A22" s="174"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="111"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10948,23 +10965,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="90"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="87"/>
-      <c r="P23" s="50"/>
-      <c r="Q23" s="48"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="110"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="110"/>
+      <c r="Q23" s="111"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10976,23 +10993,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="90"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="87"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="48"/>
+      <c r="A24" s="174"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="111"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11004,23 +11021,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="90"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="87"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="48"/>
+      <c r="A25" s="174"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="110"/>
+      <c r="Q25" s="111"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11032,23 +11049,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="90"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="87"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="48"/>
+      <c r="A26" s="174"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="111"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11060,23 +11077,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="90"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="87"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="48"/>
+      <c r="A27" s="174"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="111"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="110"/>
+      <c r="Q27" s="111"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11088,23 +11105,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="90"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="87"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="48"/>
+      <c r="A28" s="174"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="175"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="110"/>
+      <c r="Q28" s="111"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11116,23 +11133,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="90"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="91"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="48"/>
+      <c r="A29" s="174"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="110"/>
+      <c r="Q29" s="111"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11144,23 +11161,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="90"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="87"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="48"/>
+      <c r="A30" s="174"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="111"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11172,23 +11189,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="93"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="88"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="55"/>
+      <c r="A31" s="176"/>
+      <c r="B31" s="127"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="127"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="127"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="127"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="118"/>
+      <c r="Q31" s="127"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12186,6 +12203,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12210,118 +12339,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5317489F-AD58-4C14-864F-F83A47E41F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5F4948-AA2B-4D9F-A295-A7CA89BEBEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -616,14 +616,6 @@
 A1-1:基本フロー2でシステムはタスクの情報の有無を検出する。
 A1-2:「登録されているタスクはありません。」を表示する。
 A1-3:従業員は基本フロー1に戻る。
-A2：タスク未選択で編集ボタン押下
-A2-1:基本フロー4でシステムはタスク未選択を検出
-A2-1:「タスクを選択してください。」を表示する。
-A2-2:従業員は基本フロー1に戻る。
-A3：タスク未選択で削除ボタン押下
-A3-1:基本フロー4でシステムはタスク未選択を検出
-A3-1:「タスクを選択してください。」を表示する。
-A3-2:従業員は基本フロー1に戻る。
 </t>
     <rPh sb="38" eb="40">
       <t>ジョウホウ</t>
@@ -642,15 +634,6 @@
     </rPh>
     <rPh sb="97" eb="98">
       <t>モド</t>
-    </rPh>
-    <rPh sb="140" eb="143">
-      <t>ミセンタク</t>
-    </rPh>
-    <rPh sb="144" eb="146">
-      <t>ケンシュツ</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>センタク</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1608,12 +1591,246 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1623,6 +1840,108 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1632,347 +1951,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1980,47 +1996,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3426,85 +3409,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="113"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3524,46 +3507,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="116" t="s">
+      <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="113"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="109" t="s">
+      <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="111"/>
-      <c r="I13" s="109" t="s">
+      <c r="H13" s="68"/>
+      <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="110"/>
-      <c r="K13" s="111"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="109"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="111"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="109"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="111"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3572,13 +3555,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="112" t="s">
+      <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4592,19 +4575,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="149" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="149" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4616,192 +4599,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="150" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="154">
+      <c r="G2" s="55"/>
+      <c r="H2" s="60">
         <v>46176</v>
       </c>
-      <c r="I2" s="143" t="s">
+      <c r="I2" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="146"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="147"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="120" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="122"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="91"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="138" t="s">
+      <c r="A6" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="123" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="124"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="138" t="s">
+      <c r="A7" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="123" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="124"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="110"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="123" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="124"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="97.5" customHeight="1">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="125" t="s">
+      <c r="C9" s="68"/>
+      <c r="D9" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="124"/>
-    </row>
-    <row r="10" spans="1:10" ht="204.75" customHeight="1">
-      <c r="A10" s="140"/>
-      <c r="B10" s="142" t="s">
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="72"/>
+    </row>
+    <row r="10" spans="1:10" ht="116.25" customHeight="1">
+      <c r="A10" s="86"/>
+      <c r="B10" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="125" t="s">
+      <c r="C10" s="68"/>
+      <c r="D10" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="124"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="141"/>
-      <c r="B11" s="142" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="125" t="s">
+      <c r="C11" s="68"/>
+      <c r="D11" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="124"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="123" t="s">
+      <c r="B12" s="70"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="124"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="119"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5792,17 +5775,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5811,14 +5791,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5837,19 +5820,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="149" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="149" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5861,40 +5844,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="146"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="147"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7251,19 +7234,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="74" t="s">
+      <c r="B1" s="115"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="74" t="s">
+      <c r="E1" s="124"/>
+      <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="124"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -7275,564 +7258,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="117"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="171"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="126"/>
+      <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="92">
+      <c r="G2" s="126"/>
+      <c r="H2" s="108">
         <v>46177</v>
       </c>
-      <c r="I2" s="95" t="s">
+      <c r="I2" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="98"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="160"/>
+      <c r="A3" s="117"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="167"/>
-      <c r="B4" s="168"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="161"/>
+      <c r="A4" s="120"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="101"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="156"/>
+      <c r="A5" s="99"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="60"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="A6" s="102"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="60"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
+      <c r="A9" s="102"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="104"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="53"/>
+      <c r="A10" s="102"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
+      <c r="A11" s="102"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
+      <c r="A12" s="102"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
+      <c r="A13" s="102"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53"/>
+      <c r="A14" s="102"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53"/>
+      <c r="A15" s="102"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="53"/>
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="104"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="60"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="53"/>
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="104"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="53"/>
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="104"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="53"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="104"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="60"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="53"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="104"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="60"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="53"/>
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="104"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="60"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="53"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="104"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="60"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="104"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="60"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53"/>
+      <c r="A24" s="102"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="104"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="60"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="53"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="104"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="60"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="53"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="104"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="60"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="53"/>
+      <c r="A27" s="102"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="104"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="60"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="53"/>
+      <c r="A28" s="102"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="103"/>
+      <c r="J28" s="104"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="60"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="53"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="104"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="60"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="53"/>
+      <c r="A30" s="102"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="103"/>
+      <c r="J30" s="104"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="60"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="53"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="104"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="60"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="53"/>
+      <c r="A32" s="102"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="104"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="60"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="53"/>
+      <c r="A33" s="102"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="104"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="60"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="53"/>
+      <c r="A34" s="102"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="104"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="60"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="53"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="104"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="60"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="53"/>
+      <c r="A36" s="102"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="104"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="60"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="53"/>
+      <c r="A37" s="102"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="104"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="60"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="53"/>
+      <c r="A38" s="102"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="104"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="60"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="53"/>
+      <c r="A39" s="102"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="104"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="60"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="53"/>
+      <c r="A40" s="102"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="104"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="60"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="53"/>
+      <c r="A41" s="102"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="103"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="103"/>
+      <c r="J41" s="104"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="60"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="53"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="104"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="60"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="53"/>
+      <c r="A43" s="102"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="104"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="60"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="53"/>
+      <c r="A44" s="102"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="103"/>
+      <c r="J44" s="104"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="60"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="53"/>
+      <c r="A45" s="102"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="103"/>
+      <c r="J45" s="104"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="60"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="53"/>
+      <c r="A46" s="102"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="103"/>
+      <c r="J46" s="104"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="104"/>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="157"/>
+      <c r="A47" s="105"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="106"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="106"/>
+      <c r="I47" s="106"/>
+      <c r="J47" s="107"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
@@ -8841,19 +8824,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="74" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="74" t="s">
+      <c r="E1" s="156"/>
+      <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="75"/>
+      <c r="G1" s="156"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -8865,112 +8848,112 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="92">
+      <c r="G2" s="141"/>
+      <c r="H2" s="108">
         <v>46177</v>
       </c>
-      <c r="I2" s="95" t="s">
+      <c r="I2" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="98"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="105"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="151"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="76" t="s">
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="160" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="78"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="162"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="68"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="163"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="59"/>
+      <c r="A7" s="169"/>
+      <c r="B7" s="170"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="170"/>
+      <c r="H7" s="170"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="171"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="172" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="61"/>
+      <c r="D9" s="172"/>
       <c r="E9" s="47" t="s">
         <v>116</v>
       </c>
@@ -8983,20 +8966,20 @@
       <c r="H9" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="61" t="s">
+      <c r="I9" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="62"/>
+      <c r="J9" s="173"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="103"/>
       <c r="E10" s="42" t="s">
         <v>109</v>
       </c>
@@ -9009,20 +8992,20 @@
       <c r="H10" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="J10" s="53"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="103"/>
       <c r="E11" s="42" t="s">
         <v>105</v>
       </c>
@@ -9035,92 +9018,92 @@
       <c r="H11" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="J11" s="53"/>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="44"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
       <c r="E15" s="43"/>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="68"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="163"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="70" t="s">
+      <c r="B17" s="158"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="165" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="72"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="167"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9129,11 +9112,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="69"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9146,18 +9129,18 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="73" t="s">
+      <c r="H18" s="168" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="67"/>
-      <c r="J18" s="68"/>
+      <c r="I18" s="158"/>
+      <c r="J18" s="163"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="129" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="36" t="s">
         <v>97</v>
       </c>
@@ -9170,18 +9153,18 @@
       <c r="G19" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="79" t="s">
+      <c r="H19" s="164" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="55"/>
-      <c r="J19" s="56"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="63" t="s">
+      <c r="A20" s="129" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
+      <c r="B20" s="130"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="36" t="s">
         <v>92</v>
       </c>
@@ -9194,18 +9177,18 @@
       <c r="G20" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="H20" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="55"/>
-      <c r="J20" s="56"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="134"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="36" t="s">
         <v>86</v>
       </c>
@@ -9218,18 +9201,18 @@
       <c r="G21" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="H21" s="54" t="s">
+      <c r="H21" s="132" t="s">
         <v>84</v>
       </c>
-      <c r="I21" s="55"/>
-      <c r="J21" s="56"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="134"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="36" t="s">
         <v>82</v>
       </c>
@@ -9242,18 +9225,18 @@
       <c r="G22" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="54" t="s">
+      <c r="H22" s="132" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="55"/>
-      <c r="J22" s="56"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="37" t="s">
         <v>78</v>
       </c>
@@ -9266,23 +9249,23 @@
       <c r="G23" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H23" s="54" t="s">
+      <c r="H23" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="55"/>
-      <c r="J23" s="56"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="86"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="88"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="137"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="91"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="140"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10263,6 +10246,33 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10279,33 +10289,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10325,182 +10308,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="149" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="149" t="s">
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="149" t="s">
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="149" t="s">
+      <c r="P1" s="53"/>
+      <c r="Q1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="137"/>
-      <c r="S1" s="149" t="s">
+      <c r="R1" s="53"/>
+      <c r="S1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="122"/>
+      <c r="T1" s="91"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="150"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="150"/>
-      <c r="R2" s="151"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="186"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="180"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="152"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="152"/>
-      <c r="R3" s="132"/>
-      <c r="S3" s="152"/>
-      <c r="T3" s="187"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="181"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="153"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="153"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="153"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="153"/>
-      <c r="T4" s="188"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="182"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="120" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="121"/>
-      <c r="T5" s="122"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="91"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="123" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="110"/>
-      <c r="S6" s="110"/>
-      <c r="T6" s="124"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="123" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="110"/>
-      <c r="T7" s="124"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="72"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10699,37 +10682,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="68"/>
+      <c r="C15" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="111"/>
-      <c r="E15" s="183" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="111"/>
-      <c r="G15" s="183" t="s">
+      <c r="F15" s="68"/>
+      <c r="G15" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="110"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="183" t="s">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="111"/>
-      <c r="L15" s="183" t="s">
+      <c r="K15" s="68"/>
+      <c r="L15" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="110"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="183" t="s">
+      <c r="M15" s="70"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="111"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10741,37 +10724,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="174">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="175" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="111"/>
-      <c r="E16" s="175" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="111"/>
-      <c r="G16" s="182" t="s">
+      <c r="F16" s="68"/>
+      <c r="G16" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="110"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="182" t="s">
+      <c r="H16" s="70"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="111"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="68"/>
+      <c r="L16" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="110"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="70"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="111"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="68"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10783,37 +10766,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="174">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="175" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="111"/>
-      <c r="E17" s="175" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="111"/>
-      <c r="G17" s="182" t="s">
+      <c r="F17" s="68"/>
+      <c r="G17" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="110"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="182" t="s">
+      <c r="H17" s="70"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="111"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="68"/>
+      <c r="L17" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="110"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="70"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="111"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="68"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10825,23 +10808,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="174"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="111"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="111"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="68"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10853,23 +10836,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="174"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="111"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="68"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10881,23 +10864,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="174"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="182"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="111"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="68"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10909,23 +10892,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="111"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="68"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10937,23 +10920,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="174"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="111"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="186"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10965,23 +10948,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="174"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="110"/>
-      <c r="Q23" s="111"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="68"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10993,23 +10976,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="174"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="110"/>
-      <c r="Q24" s="111"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="68"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11021,23 +11004,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="111"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="68"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11049,23 +11032,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="174"/>
-      <c r="B26" s="111"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="111"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="68"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11077,23 +11060,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="174"/>
-      <c r="B27" s="111"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="111"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="68"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11105,23 +11088,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="111"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="110"/>
-      <c r="Q28" s="111"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="68"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11133,23 +11116,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="111"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="110"/>
-      <c r="Q29" s="111"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="68"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11161,23 +11144,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="174"/>
-      <c r="B30" s="111"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="110"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="110"/>
-      <c r="Q30" s="111"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="68"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11189,23 +11172,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="127"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="118"/>
-      <c r="N31" s="127"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="118"/>
-      <c r="Q31" s="127"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="75"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12203,62 +12186,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12283,62 +12266,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5F4948-AA2B-4D9F-A295-A7CA89BEBEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00E85D5-9BF6-440D-BE01-D835E0AE3E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,14 +601,6 @@
     <rPh sb="10" eb="12">
       <t>ガメンイチランガメンヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">E1:データベース接続に失敗した場合
-E1-1.基本フロー4でシステムはデータベース接続に失敗する。
-E1-2.システムはエラーメッセージを表示する。
-E1-3.従業員は基本フロー1に戻る。
-</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -635,6 +627,14 @@
     <rPh sb="97" eb="98">
       <t>モド</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">E1:データベース接続に失敗した場
+E1-1.基本フロー2でシステムはデータベース接続に失敗する。
+E1-2.システムはエラーメッセージを表示する。
+E1-3.従業員は基本フロー1に戻る。
+</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1591,12 +1591,114 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1606,114 +1708,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1831,6 +1831,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1840,6 +1864,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1858,21 +1915,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1906,15 +1948,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1924,86 +1957,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3427,67 +3427,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3510,14 +3510,14 @@
       <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3527,26 +3527,26 @@
       <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="68"/>
+      <c r="H13" s="76"/>
       <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="70"/>
-      <c r="K13" s="68"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="76"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="93"/>
-      <c r="H14" s="68"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="68"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="76"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="93"/>
-      <c r="H15" s="68"/>
+      <c r="H15" s="76"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="68"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="76"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3558,10 +3558,10 @@
       <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4575,19 +4575,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4599,192 +4599,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="60">
+      <c r="G2" s="89"/>
+      <c r="H2" s="92">
         <v>46176</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="64"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="91"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="71" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="72"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="71" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="72"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="71" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="72"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="97.5" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="92" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="72"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
     </row>
     <row r="10" spans="1:10" ht="116.25" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="67" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="92" t="s">
+      <c r="C10" s="76"/>
+      <c r="D10" s="61" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="60"/>
+    </row>
+    <row r="11" spans="1:10" ht="108" customHeight="1">
+      <c r="A11" s="79"/>
+      <c r="B11" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="72"/>
-    </row>
-    <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="92" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="72"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="71" t="s">
+      <c r="B12" s="59"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="72"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5775,6 +5775,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5783,25 +5802,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5823,16 +5823,16 @@
       <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5844,40 +5844,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8828,15 +8828,15 @@
         <v>121</v>
       </c>
       <c r="B1" s="100"/>
-      <c r="C1" s="152"/>
+      <c r="C1" s="166"/>
       <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="156"/>
+      <c r="E1" s="170"/>
       <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="156"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -8850,15 +8850,15 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="102"/>
       <c r="B2" s="103"/>
-      <c r="C2" s="143"/>
+      <c r="C2" s="146"/>
       <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="141"/>
+      <c r="E2" s="144"/>
       <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="141"/>
+      <c r="G2" s="144"/>
       <c r="H2" s="108">
         <v>46177</v>
       </c>
@@ -8870,68 +8870,68 @@
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="150"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="105"/>
       <c r="B4" s="106"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="151"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="165"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="160" t="s">
+      <c r="B5" s="168"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="171" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="162"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="173"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="158"/>
-      <c r="J6" s="163"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="134"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="169"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="170"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="170"/>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="171"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -8950,10 +8950,10 @@
       <c r="B9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="172" t="s">
+      <c r="C9" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="172"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="47" t="s">
         <v>116</v>
       </c>
@@ -8966,10 +8966,10 @@
       <c r="H9" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="172" t="s">
+      <c r="I9" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="173"/>
+      <c r="J9" s="153"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
@@ -9078,32 +9078,32 @@
       <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-      <c r="J16" s="163"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="134"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="157" t="s">
+      <c r="A17" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="158"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="165" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="166"/>
-      <c r="F17" s="166"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="167"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="138"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9112,11 +9112,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="157" t="s">
+      <c r="A18" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="158"/>
-      <c r="C18" s="159"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="135"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9129,11 +9129,11 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="168" t="s">
+      <c r="H18" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="158"/>
-      <c r="J18" s="163"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="134"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
@@ -9153,11 +9153,11 @@
       <c r="G19" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="164" t="s">
+      <c r="H19" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="133"/>
-      <c r="J19" s="134"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="142"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
@@ -9177,11 +9177,11 @@
       <c r="G20" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="132" t="s">
+      <c r="H20" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="133"/>
-      <c r="J20" s="134"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="142"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
@@ -9201,11 +9201,11 @@
       <c r="G21" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="H21" s="132" t="s">
+      <c r="H21" s="140" t="s">
         <v>84</v>
       </c>
-      <c r="I21" s="133"/>
-      <c r="J21" s="134"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="142"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
@@ -9225,11 +9225,11 @@
       <c r="G22" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="H22" s="132" t="s">
+      <c r="H22" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="133"/>
-      <c r="J22" s="134"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="142"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
@@ -9249,23 +9249,23 @@
       <c r="G23" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H23" s="132" t="s">
+      <c r="H23" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="142"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="136"/>
-      <c r="C24" s="137"/>
+      <c r="A24" s="154"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="156"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="140"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="158"/>
+      <c r="J24" s="159"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10246,33 +10246,6 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10289,6 +10262,33 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10308,182 +10308,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="52" t="s">
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52" t="s">
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="52" t="s">
+      <c r="P1" s="74"/>
+      <c r="Q1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="53"/>
-      <c r="S1" s="52" t="s">
+      <c r="R1" s="74"/>
+      <c r="S1" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="91"/>
+      <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="180"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="181"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="90"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="182"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="90" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="91"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="71" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="72"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="71" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="72"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10682,37 +10682,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="187" t="s">
+      <c r="B15" s="76"/>
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="174" t="s">
+      <c r="D15" s="76"/>
+      <c r="E15" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="174" t="s">
+      <c r="F15" s="76"/>
+      <c r="G15" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="70"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="174" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="68"/>
-      <c r="L15" s="174" t="s">
+      <c r="K15" s="76"/>
+      <c r="L15" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="174" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="68"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="76"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10724,37 +10724,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="174">
         <v>1</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="186" t="s">
+      <c r="B16" s="76"/>
+      <c r="C16" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="76"/>
+      <c r="E16" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="175" t="s">
+      <c r="F16" s="76"/>
+      <c r="G16" s="182" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="175" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="177" t="s">
+      <c r="K16" s="76"/>
+      <c r="L16" s="178" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="177" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="178" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="68"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="76"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10766,37 +10766,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="174">
         <v>2</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="186" t="s">
+      <c r="B17" s="76"/>
+      <c r="C17" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="186" t="s">
+      <c r="D17" s="76"/>
+      <c r="E17" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="175" t="s">
+      <c r="F17" s="76"/>
+      <c r="G17" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="175" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="182" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="68"/>
-      <c r="L17" s="177" t="s">
+      <c r="K17" s="76"/>
+      <c r="L17" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="177" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="178" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="68"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="76"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10808,23 +10808,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="186"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="177"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="177"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="68"/>
+      <c r="A18" s="174"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="76"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10836,23 +10836,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="177"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="177"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="68"/>
+      <c r="A19" s="174"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="76"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10864,23 +10864,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="177"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="177"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="68"/>
+      <c r="A20" s="174"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="76"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10892,23 +10892,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="177"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="68"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="76"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10920,23 +10920,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="177"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="177"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="68"/>
+      <c r="A22" s="174"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="76"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10948,23 +10948,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="177"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="177"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="68"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="76"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10976,23 +10976,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="177"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="177"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="68"/>
+      <c r="A24" s="174"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="76"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11004,23 +11004,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="177"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="68"/>
+      <c r="A25" s="174"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="76"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11032,23 +11032,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="68"/>
+      <c r="A26" s="174"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="76"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11060,23 +11060,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="177"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="68"/>
+      <c r="A27" s="174"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="76"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11088,23 +11088,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="68"/>
+      <c r="A28" s="174"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="175"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="76"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11116,23 +11116,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="177"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="68"/>
+      <c r="A29" s="174"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="76"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11144,23 +11144,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="177"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="68"/>
+      <c r="A30" s="174"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="76"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11172,23 +11172,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="188"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="75"/>
+      <c r="A31" s="176"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="63"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12186,6 +12186,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12210,118 +12322,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5F4948-AA2B-4D9F-A295-A7CA89BEBEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF8BFCD8-5F19-4AE6-B8AF-5E185B8DF83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5445" yWindow="645" windowWidth="13260" windowHeight="9165" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
-    <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
-    <sheet name="詳細クラス図 " sheetId="8" r:id="rId4"/>
-    <sheet name="画面設計書 " sheetId="7" r:id="rId5"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId3"/>
+    <sheet name="画面遷移図" sheetId="3" r:id="rId4"/>
+    <sheet name="詳細クラス図 " sheetId="8" r:id="rId5"/>
+    <sheet name="画面設計書 " sheetId="7" r:id="rId6"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -280,16 +282,6 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>ズ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク一覧画面が表示されている</t>
-    <rPh sb="3" eb="7">
-      <t>イチランガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -592,8 +584,11 @@
   <si>
     <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
 2.システムがデータベースからタスク情報を取得する。
-3.システムが取得した情報を一覧表示用に編集する。
-4.システムがタスク一覧画面を表示する。
+3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
+4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
+5. メモおよび期限がNULLの場合は空欄に変換する
+6.システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+7.システムがログイン中のユーザIDとタスクの担当者IDを比較し、本人のタスクのみ選択可能にする。
 </t>
     <rPh sb="2" eb="5">
       <t>ジュウギョウイン</t>
@@ -604,19 +599,19 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">E1:データベース接続に失敗した場合
-E1-1.基本フロー4でシステムはデータベース接続に失敗する。
-E1-2.システムはエラーメッセージを表示する。
-E1-3.従業員は基本フロー1に戻る。
-</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t xml:space="preserve">A1:タスク情報が存在しない場合
 A1-1:基本フロー2でシステムはタスクの情報の有無を検出する。
-A1-2:「登録されているタスクはありません。」を表示する。
-A1-3:従業員は基本フロー1に戻る。
-</t>
+A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
+A2:メモ、期限の任意項目が未入力の場合
+A2-1:基本フロー5でシステムが任意項目の値を確認する。
+A2-2:システムが任意項目がNULLであることを確認する。
+A2-3:システムが空文字を設定する。
+A2-4:システムが一覧表示画面の任意項目で空文字を表示する。
+A3:本人以外のタスクが表示される場合
+A3-1:基本フロー7でシステムがログイン中のユーザIDとタスクの担当者IDを比較する
+A3-2:担当者IDがログイン中のユーザIDと一致しないことを確認する
+A3-3:システムは該当タスクの選択用ラジオボタンを表示しない
+A3-4:システムはタスク一覧画面を表示する          </t>
     <rPh sb="38" eb="40">
       <t>ジョウホウ</t>
     </rPh>
@@ -626,14 +621,80 @@
     <rPh sb="44" eb="46">
       <t>ケンシュツ</t>
     </rPh>
-    <rPh sb="86" eb="89">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="90" eb="92">
+    <rPh sb="121" eb="123">
       <t>キホン</t>
     </rPh>
-    <rPh sb="97" eb="98">
+    <rPh sb="144" eb="146">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="147" eb="151">
+      <t>ニンイコウモク</t>
+    </rPh>
+    <rPh sb="152" eb="155">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="174" eb="175">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="176" eb="178">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="192" eb="194">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="223" eb="226">
+      <t>カラモジイチランヒョウジガメンニンイコウモクカラモジヒョウジ</t>
+    </rPh>
+    <rPh sb="247" eb="249">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">E1:データベース接続に失敗した場
+E1-1.基本フロー2でシステムはデータベース接続に失敗する。
+E1-2.システムはエラーメッセージを表示する。
+E1-３:メニュー画面へ戻る。
+</t>
+    <rPh sb="84" eb="86">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="87" eb="88">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>登録済みタスクの一覧、または「登録されているタスクはありません。」というメッセージが表示される</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1927,35 +1988,35 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4706,7 +4767,7 @@
       <c r="I8" s="70"/>
       <c r="J8" s="72"/>
     </row>
-    <row r="9" spans="1:10" ht="97.5" customHeight="1">
+    <row r="9" spans="1:10" ht="153.75" customHeight="1">
       <c r="A9" s="85" t="s">
         <v>15</v>
       </c>
@@ -4715,7 +4776,7 @@
       </c>
       <c r="C9" s="68"/>
       <c r="D9" s="92" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="70"/>
       <c r="F9" s="70"/>
@@ -4724,14 +4785,14 @@
       <c r="I9" s="70"/>
       <c r="J9" s="72"/>
     </row>
-    <row r="10" spans="1:10" ht="116.25" customHeight="1">
+    <row r="10" spans="1:10" ht="314.25" customHeight="1">
       <c r="A10" s="86"/>
       <c r="B10" s="67" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="68"/>
       <c r="D10" s="92" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E10" s="70"/>
       <c r="F10" s="70"/>
@@ -4763,7 +4824,7 @@
       <c r="B12" s="70"/>
       <c r="C12" s="68"/>
       <c r="D12" s="71" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="E12" s="70"/>
       <c r="F12" s="70"/>
@@ -5810,6 +5871,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DCAC7F-87A3-4F01-A307-6B0B43660074}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -7222,7 +7293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38D70E1-6E38-4E12-9BAB-766F67908DAD}">
   <dimension ref="A1:J1014"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -7273,7 +7344,7 @@
         <v>46177</v>
       </c>
       <c r="I2" s="111" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J2" s="112"/>
     </row>
@@ -8805,7 +8876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B352BAB-1396-4817-AE14-ADCF7C7B549D}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8825,7 +8896,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1" s="100"/>
       <c r="C1" s="152"/>
@@ -8863,7 +8934,7 @@
         <v>46177</v>
       </c>
       <c r="I2" s="111" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J2" s="112"/>
     </row>
@@ -8898,7 +8969,7 @@
       <c r="B5" s="154"/>
       <c r="C5" s="155"/>
       <c r="D5" s="160" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E5" s="161"/>
       <c r="F5" s="161"/>
@@ -8922,16 +8993,16 @@
       <c r="J6" s="163"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="169"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="170"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="170"/>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="171"/>
+      <c r="A7" s="164"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="166"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -8948,85 +9019,85 @@
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="172" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="172"/>
+      <c r="C9" s="167" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="167"/>
       <c r="E9" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="173"/>
+      <c r="I9" s="167" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="168"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="103"/>
       <c r="E10" s="42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F10" s="46">
         <v>46203</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I10" s="103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="103"/>
       <c r="E11" s="42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F11" s="46">
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I11" s="103" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="103"/>
       <c r="D12" s="103"/>
@@ -9040,7 +9111,7 @@
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="103"/>
       <c r="D13" s="103"/>
@@ -9054,7 +9125,7 @@
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="103"/>
       <c r="D14" s="103"/>
@@ -9097,18 +9168,18 @@
       </c>
       <c r="B17" s="158"/>
       <c r="C17" s="159"/>
-      <c r="D17" s="165" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="166"/>
-      <c r="F17" s="166"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="167"/>
+      <c r="D17" s="169" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="170"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
@@ -9129,7 +9200,7 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="168" t="s">
+      <c r="H18" s="172" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="158"/>
@@ -9137,120 +9208,120 @@
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="130"/>
       <c r="C19" s="131"/>
       <c r="D19" s="36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="164" t="s">
         <v>94</v>
+      </c>
+      <c r="H19" s="173" t="s">
+        <v>93</v>
       </c>
       <c r="I19" s="133"/>
       <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" s="130"/>
       <c r="C20" s="131"/>
       <c r="D20" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H20" s="132" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I20" s="133"/>
       <c r="J20" s="134"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="130"/>
       <c r="C21" s="131"/>
       <c r="D21" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H21" s="132" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I21" s="133"/>
       <c r="J21" s="134"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="130"/>
       <c r="C22" s="131"/>
       <c r="D22" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H22" s="132" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I22" s="133"/>
       <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23" s="130"/>
       <c r="C23" s="131"/>
       <c r="D23" s="37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H23" s="132" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I23" s="133"/>
       <c r="J23" s="134"/>
@@ -10297,7 +10368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00E85D5-9BF6-440D-BE01-D835E0AE3E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF11DE6-F6EF-4112-A4E6-1658AA6FB795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,16 +280,6 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>ズ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク一覧画面が表示されている</t>
-    <rPh sb="3" eb="7">
-      <t>イチランガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -592,49 +582,40 @@
   <si>
     <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
 2.システムがデータベースからタスク情報を取得する。
-3.システムが取得した情報を一覧表示用に編集する。
-4.システムがタスク一覧画面を表示する。
+3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
+4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
+5. メモおよび期限がNULLの場合は空欄に変換する
+6.システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+7.システムがログイン中のユーザIDとタスクの担当者IDを比較し、本人のタスクのみ選択可能にする。
 </t>
-    <rPh sb="2" eb="5">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガメンイチランガメンヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">A1:タスク情報が存在しない場合
 A1-1:基本フロー2でシステムはタスクの情報の有無を検出する。
-A1-2:「登録されているタスクはありません。」を表示する。
-A1-3:従業員は基本フロー1に戻る。
+A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
+A2:メモ、期限の任意項目が未入力の場合
+A2-1:基本フロー5でシステムが任意項目の値を確認する。
+A2-2:システムが任意項目がNULLであることを確認する。
+A2-3:システムが空文字を設定する。
+A2-4:システムが一覧表示画面の任意項目で空文字を表示する。
+A3:本人以外のタスクが表示される場合
+A3-1:基本フロー7でシステムがログイン中のユーザIDとタスクの担当者IDを比較する
+A3-2:担当者IDがログイン中のユーザIDと一致しないことを確認する
+A3-3:システムは該当タスクの選択用ラジオボタンを表示しない
+A3-4:システムはタスク一覧画面を表示する
 </t>
-    <rPh sb="38" eb="40">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ウム</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ケンシュツ</t>
-    </rPh>
-    <rPh sb="86" eb="89">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="97" eb="98">
-      <t>モド</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">E1:データベース接続に失敗した場
+    <t>E1:データベース接続に失敗した場
 E1-1.基本フロー2でシステムはデータベース接続に失敗する。
 E1-2.システムはエラーメッセージを表示する。
-E1-3.従業員は基本フロー1に戻る。
-</t>
+E1-3:メニュー画面へ戻る。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>登録済みタスクの一覧、または「登録されているタスクはありません。」というメッセージが表示される</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1591,128 +1572,128 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1831,16 +1812,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1856,106 +1936,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1963,47 +1977,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3427,67 +3408,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3510,14 +3491,14 @@
       <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3527,26 +3508,26 @@
       <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="76"/>
+      <c r="H13" s="68"/>
       <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="76"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="93"/>
-      <c r="H14" s="76"/>
+      <c r="H14" s="68"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="76"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="93"/>
-      <c r="H15" s="76"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="76"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3558,10 +3539,10 @@
       <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4575,19 +4556,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4599,192 +4580,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="92">
+      <c r="G2" s="55"/>
+      <c r="H2" s="60">
         <v>46176</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="86"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="55" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="91"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="58" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
-    </row>
-    <row r="9" spans="1:10" ht="97.5" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="72"/>
+    </row>
+    <row r="9" spans="1:10" ht="132.75" customHeight="1">
+      <c r="A9" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="61" t="s">
+      <c r="C9" s="68"/>
+      <c r="D9" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="72"/>
+    </row>
+    <row r="10" spans="1:10" ht="228.75" customHeight="1">
+      <c r="A10" s="86"/>
+      <c r="B10" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="68"/>
+      <c r="D10" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
-    </row>
-    <row r="10" spans="1:10" ht="116.25" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="61" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="72"/>
+    </row>
+    <row r="11" spans="1:10" ht="108" customHeight="1">
+      <c r="A11" s="87"/>
+      <c r="B11" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="60"/>
-    </row>
-    <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="61" t="s">
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="72"/>
+    </row>
+    <row r="12" spans="1:10" ht="99.75" customHeight="1">
+      <c r="A12" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="70"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60"/>
-    </row>
-    <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5775,17 +5756,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5794,14 +5772,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5823,16 +5804,16 @@
       <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5844,40 +5825,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="86"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7273,7 +7254,7 @@
         <v>46177</v>
       </c>
       <c r="I2" s="111" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J2" s="112"/>
     </row>
@@ -8825,18 +8806,18 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1" s="100"/>
-      <c r="C1" s="166"/>
+      <c r="C1" s="152"/>
       <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
+      <c r="E1" s="156"/>
       <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="156"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -8850,88 +8831,88 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="102"/>
       <c r="B2" s="103"/>
-      <c r="C2" s="146"/>
+      <c r="C2" s="143"/>
       <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="144"/>
+      <c r="E2" s="141"/>
       <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="144"/>
+      <c r="G2" s="141"/>
       <c r="H2" s="108">
         <v>46177</v>
       </c>
       <c r="I2" s="111" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="164"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="105"/>
       <c r="B4" s="106"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="165"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="151"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="171" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="173"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="160" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="162"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="163"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="164"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="166"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -8948,85 +8929,85 @@
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="152"/>
+      <c r="C9" s="167" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="167"/>
       <c r="E9" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="152" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="153"/>
+      <c r="I9" s="167" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="168"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="103"/>
       <c r="E10" s="42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F10" s="46">
         <v>46203</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I10" s="103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="103"/>
       <c r="E11" s="42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F11" s="46">
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I11" s="103" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="103"/>
       <c r="D12" s="103"/>
@@ -9040,7 +9021,7 @@
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="103"/>
       <c r="D13" s="103"/>
@@ -9054,7 +9035,7 @@
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="103"/>
       <c r="D14" s="103"/>
@@ -9078,45 +9059,45 @@
       <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="132" t="s">
+      <c r="A16" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="163"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="136" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="138"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="169" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="170"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="132" t="s">
+      <c r="A18" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="133"/>
-      <c r="C18" s="135"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9129,143 +9110,143 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="139" t="s">
+      <c r="H18" s="172" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="134"/>
+      <c r="I18" s="158"/>
+      <c r="J18" s="163"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="130"/>
       <c r="C19" s="131"/>
       <c r="D19" s="36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="141"/>
-      <c r="J19" s="142"/>
+      <c r="H19" s="173" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="133"/>
+      <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" s="130"/>
       <c r="C20" s="131"/>
       <c r="D20" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="H20" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="141"/>
-      <c r="J20" s="142"/>
+      <c r="H20" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="133"/>
+      <c r="J20" s="134"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="130"/>
       <c r="C21" s="131"/>
       <c r="D21" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" s="140" t="s">
         <v>84</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="H21" s="132" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" s="133"/>
+      <c r="J21" s="134"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="130"/>
       <c r="C22" s="131"/>
       <c r="D22" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="141"/>
-      <c r="J22" s="142"/>
+      <c r="H22" s="132" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" s="133"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23" s="130"/>
       <c r="C23" s="131"/>
       <c r="D23" s="37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="141"/>
-      <c r="J23" s="142"/>
+      <c r="H23" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="154"/>
-      <c r="B24" s="155"/>
-      <c r="C24" s="156"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="137"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="159"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="140"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10246,6 +10227,33 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10262,33 +10270,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10308,182 +10289,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="87" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="87" t="s">
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="87" t="s">
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="87" t="s">
+      <c r="P1" s="53"/>
+      <c r="Q1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="74"/>
-      <c r="S1" s="87" t="s">
+      <c r="R1" s="53"/>
+      <c r="S1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="57"/>
+      <c r="T1" s="91"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="186"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="180"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="187"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="181"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="188"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="182"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="55" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="57"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="91"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="58" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="60"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="58" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="60"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="72"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10682,37 +10663,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="76"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="68"/>
+      <c r="C15" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="183" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="76"/>
-      <c r="G15" s="183" t="s">
+      <c r="F15" s="68"/>
+      <c r="G15" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="183" t="s">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="76"/>
-      <c r="L15" s="183" t="s">
+      <c r="K15" s="68"/>
+      <c r="L15" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="183" t="s">
+      <c r="M15" s="70"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="76"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10724,37 +10705,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="174">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="175" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="175" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="76"/>
-      <c r="G16" s="182" t="s">
+      <c r="F16" s="68"/>
+      <c r="G16" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="182" t="s">
+      <c r="H16" s="70"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="76"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="68"/>
+      <c r="L16" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="70"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="76"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="68"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10766,37 +10747,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="174">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="175" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="175" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="76"/>
-      <c r="G17" s="182" t="s">
+      <c r="F17" s="68"/>
+      <c r="G17" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="182" t="s">
+      <c r="H17" s="70"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="76"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="68"/>
+      <c r="L17" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="70"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="76"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="68"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10808,23 +10789,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="174"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="76"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="68"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10836,23 +10817,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="174"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="76"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="68"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10864,23 +10845,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="174"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="182"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="76"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="68"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10892,23 +10873,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="76"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="68"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10920,23 +10901,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="174"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="76"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="186"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10948,23 +10929,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="174"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="76"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="68"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10976,23 +10957,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="174"/>
-      <c r="B24" s="76"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="76"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="68"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11004,23 +10985,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="76"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="68"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11032,23 +11013,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="174"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="76"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="76"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="68"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11060,23 +11041,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="174"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="76"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="68"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11088,23 +11069,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="76"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="76"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="68"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11116,23 +11097,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="76"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="76"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="68"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11144,23 +11125,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="174"/>
-      <c r="B30" s="76"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="76"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="68"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11172,23 +11153,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="63"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="75"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12186,62 +12167,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12266,62 +12247,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF11DE6-F6EF-4112-A4E6-1658AA6FB795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C60F8-E810-4428-B996-5502B2EF1933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -580,42 +580,47 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
-2.システムがデータベースからタスク情報を取得する。
-3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
-4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
-5. メモおよび期限がNULLの場合は空欄に変換する
-6.システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
-7.システムがログイン中のユーザIDとタスクの担当者IDを比較し、本人のタスクのみ選択可能にする。
-</t>
+    <t>登録済みタスクの一覧、または「登録されているタスクはありません。」というメッセージが表示される</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>E1:データベース接続に失敗した場合。
+E1-1.基本フロー2でシステムはデータベース接続に失敗する。
+E1-2.システムはエラーメッセージを表示する。
+E1-3:システムがメニュー画面を表示する。</t>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t xml:space="preserve">A1:タスク情報が存在しない場合
-A1-1:基本フロー2でシステムはタスクの情報の有無を検出する。
+A1-1:基本フロー2でシステムはタスク情報が0件であることを確認する。
 A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
 A2:メモ、期限の任意項目が未入力の場合
 A2-1:基本フロー5でシステムが任意項目の値を確認する。
 A2-2:システムが任意項目がNULLであることを確認する。
 A2-3:システムが空文字を設定する。
 A2-4:システムが一覧表示画面の任意項目で空文字を表示する。
-A3:本人以外のタスクが表示される場合
-A3-1:基本フロー7でシステムがログイン中のユーザIDとタスクの担当者IDを比較する
-A3-2:担当者IDがログイン中のユーザIDと一致しないことを確認する
-A3-3:システムは該当タスクの選択用ラジオボタンを表示しない
-A3-4:システムはタスク一覧画面を表示する
 </t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1:データベース接続に失敗した場
-E1-1.基本フロー2でシステムはデータベース接続に失敗する。
-E1-2.システムはエラーメッセージを表示する。
-E1-3:メニュー画面へ戻る。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>登録済みタスクの一覧、または「登録されているタスクはありません。」というメッセージが表示される</t>
+    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
+2.システムがデータベースからタスク情報を取得する。
+3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
+4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
+5:システムがログイン中のユーザIDとタスクの担当者IDを比較する
+6:担当者IDがログイン中のユーザIDと一致しないことを確認する
+7:システムは該当タスクの選択用ラジオボタンを表示しない
+6. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1572,12 +1577,114 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1587,114 +1694,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1812,6 +1817,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1821,6 +1850,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1839,21 +1901,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1887,15 +1934,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1905,86 +1943,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3408,67 +3413,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3491,14 +3496,14 @@
       <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3508,26 +3513,26 @@
       <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="68"/>
+      <c r="H13" s="76"/>
       <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="70"/>
-      <c r="K13" s="68"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="76"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="93"/>
-      <c r="H14" s="68"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="68"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="76"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="93"/>
-      <c r="H15" s="68"/>
+      <c r="H15" s="76"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="68"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="76"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3539,10 +3544,10 @@
       <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4556,19 +4561,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4580,192 +4585,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="60">
+      <c r="G2" s="89"/>
+      <c r="H2" s="92">
         <v>46176</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="64"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="91"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="71" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="72"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="71" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="72"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="71" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="72"/>
-    </row>
-    <row r="9" spans="1:10" ht="132.75" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
+    </row>
+    <row r="9" spans="1:10" ht="180.75" customHeight="1">
+      <c r="A9" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="92" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
+    </row>
+    <row r="10" spans="1:10" ht="209.25" customHeight="1">
+      <c r="A10" s="78"/>
+      <c r="B10" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="76"/>
+      <c r="D10" s="61" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="60"/>
+    </row>
+    <row r="11" spans="1:10" ht="108" customHeight="1">
+      <c r="A11" s="79"/>
+      <c r="B11" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+    </row>
+    <row r="12" spans="1:10" ht="99.75" customHeight="1">
+      <c r="A12" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="72"/>
-    </row>
-    <row r="10" spans="1:10" ht="228.75" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="92" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="72"/>
-    </row>
-    <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="92" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="72"/>
-    </row>
-    <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="71" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="72"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5756,6 +5761,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5764,25 +5788,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5804,16 +5809,16 @@
       <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5825,40 +5830,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8809,15 +8814,15 @@
         <v>120</v>
       </c>
       <c r="B1" s="100"/>
-      <c r="C1" s="152"/>
+      <c r="C1" s="166"/>
       <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="156"/>
+      <c r="E1" s="170"/>
       <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="156"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -8831,15 +8836,15 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="102"/>
       <c r="B2" s="103"/>
-      <c r="C2" s="143"/>
+      <c r="C2" s="146"/>
       <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="141"/>
+      <c r="E2" s="144"/>
       <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="141"/>
+      <c r="G2" s="144"/>
       <c r="H2" s="108">
         <v>46177</v>
       </c>
@@ -8851,68 +8856,68 @@
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="150"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="105"/>
       <c r="B4" s="106"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="151"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="165"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="160" t="s">
+      <c r="B5" s="168"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="171" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="162"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="173"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="158"/>
-      <c r="J6" s="163"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="134"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="164"/>
-      <c r="B7" s="165"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="165"/>
-      <c r="I7" s="165"/>
-      <c r="J7" s="166"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -8931,10 +8936,10 @@
       <c r="B9" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="167" t="s">
+      <c r="C9" s="152" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="167"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="47" t="s">
         <v>115</v>
       </c>
@@ -8947,10 +8952,10 @@
       <c r="H9" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="167" t="s">
+      <c r="I9" s="152" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="168"/>
+      <c r="J9" s="153"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
@@ -9059,32 +9064,32 @@
       <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-      <c r="J16" s="163"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="134"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="157" t="s">
+      <c r="A17" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="158"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="169" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="170"/>
-      <c r="F17" s="170"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="171"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="138"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9093,11 +9098,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="157" t="s">
+      <c r="A18" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="158"/>
-      <c r="C18" s="159"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="135"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9110,11 +9115,11 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="172" t="s">
+      <c r="H18" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="158"/>
-      <c r="J18" s="163"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="134"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
@@ -9134,11 +9139,11 @@
       <c r="G19" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="173" t="s">
+      <c r="H19" s="143" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="133"/>
-      <c r="J19" s="134"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="142"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
@@ -9158,11 +9163,11 @@
       <c r="G20" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="132" t="s">
+      <c r="H20" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="133"/>
-      <c r="J20" s="134"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="142"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
@@ -9182,11 +9187,11 @@
       <c r="G21" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="132" t="s">
+      <c r="H21" s="140" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="133"/>
-      <c r="J21" s="134"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="142"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
@@ -9206,11 +9211,11 @@
       <c r="G22" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="132" t="s">
+      <c r="H22" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="133"/>
-      <c r="J22" s="134"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="142"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
@@ -9230,23 +9235,23 @@
       <c r="G23" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="132" t="s">
+      <c r="H23" s="140" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="142"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="136"/>
-      <c r="C24" s="137"/>
+      <c r="A24" s="154"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="156"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="140"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="158"/>
+      <c r="J24" s="159"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10227,33 +10232,6 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10270,6 +10248,33 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10289,182 +10294,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="52" t="s">
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52" t="s">
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="52" t="s">
+      <c r="P1" s="74"/>
+      <c r="Q1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="53"/>
-      <c r="S1" s="52" t="s">
+      <c r="R1" s="74"/>
+      <c r="S1" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="91"/>
+      <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="180"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="181"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="90"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="182"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="90" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="91"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="71" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="72"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="71" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="72"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10663,37 +10668,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="187" t="s">
+      <c r="B15" s="76"/>
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="174" t="s">
+      <c r="D15" s="76"/>
+      <c r="E15" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="174" t="s">
+      <c r="F15" s="76"/>
+      <c r="G15" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="70"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="174" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="68"/>
-      <c r="L15" s="174" t="s">
+      <c r="K15" s="76"/>
+      <c r="L15" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="174" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="68"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="76"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10705,37 +10710,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="174">
         <v>1</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="186" t="s">
+      <c r="B16" s="76"/>
+      <c r="C16" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="76"/>
+      <c r="E16" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="175" t="s">
+      <c r="F16" s="76"/>
+      <c r="G16" s="182" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="175" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="177" t="s">
+      <c r="K16" s="76"/>
+      <c r="L16" s="178" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="177" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="178" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="68"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="76"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10747,37 +10752,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="174">
         <v>2</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="186" t="s">
+      <c r="B17" s="76"/>
+      <c r="C17" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="186" t="s">
+      <c r="D17" s="76"/>
+      <c r="E17" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="175" t="s">
+      <c r="F17" s="76"/>
+      <c r="G17" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="175" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="182" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="68"/>
-      <c r="L17" s="177" t="s">
+      <c r="K17" s="76"/>
+      <c r="L17" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="177" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="178" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="68"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="76"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10789,23 +10794,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="186"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="177"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="177"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="68"/>
+      <c r="A18" s="174"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="76"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10817,23 +10822,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="177"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="177"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="68"/>
+      <c r="A19" s="174"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="76"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10845,23 +10850,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="177"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="177"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="68"/>
+      <c r="A20" s="174"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="76"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10873,23 +10878,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="177"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="68"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="76"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10901,23 +10906,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="177"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="177"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="68"/>
+      <c r="A22" s="174"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="76"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10929,23 +10934,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="177"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="177"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="68"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="76"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10957,23 +10962,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="177"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="177"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="68"/>
+      <c r="A24" s="174"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="76"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -10985,23 +10990,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="177"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="68"/>
+      <c r="A25" s="174"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="76"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11013,23 +11018,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="68"/>
+      <c r="A26" s="174"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="76"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11041,23 +11046,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="177"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="68"/>
+      <c r="A27" s="174"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="76"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11069,23 +11074,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="68"/>
+      <c r="A28" s="174"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="175"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="76"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11097,23 +11102,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="177"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="68"/>
+      <c r="A29" s="174"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="76"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11125,23 +11130,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="177"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="68"/>
+      <c r="A30" s="174"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="76"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11153,23 +11158,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="188"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="75"/>
+      <c r="A31" s="176"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="63"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12167,6 +12172,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12191,118 +12308,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C60F8-E810-4428-B996-5502B2EF1933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE8CBD5-533B-4D61-B12B-A1EE75303502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,10 +617,15 @@
 3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
 4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
 5:システムがログイン中のユーザIDとタスクの担当者IDを比較する
-6:担当者IDがログイン中のユーザIDと一致しないことを確認する
-7:システムは該当タスクの選択用ラジオボタンを表示しない
-6. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+6:担当者IDがログイン中のユーザIDと一致したら該当タスクにラジオボタンを表示する。
+7. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
 </t>
+    <rPh sb="180" eb="182">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="193" eb="195">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1577,128 +1582,128 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1817,16 +1822,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1842,106 +1946,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1949,47 +1987,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3413,67 +3418,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3496,14 +3501,14 @@
       <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3513,26 +3518,26 @@
       <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="76"/>
+      <c r="H13" s="68"/>
       <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="76"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="93"/>
-      <c r="H14" s="76"/>
+      <c r="H14" s="68"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="76"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="93"/>
-      <c r="H15" s="76"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="76"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3544,10 +3549,10 @@
       <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4561,19 +4566,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4585,192 +4590,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="92">
+      <c r="G2" s="55"/>
+      <c r="H2" s="60">
         <v>46176</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="86"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="55" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="91"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="58" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="61" t="s">
+      <c r="C9" s="68"/>
+      <c r="D9" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="209.25" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="80" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="61" t="s">
+      <c r="C10" s="68"/>
+      <c r="D10" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="60"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="61" t="s">
+      <c r="C11" s="68"/>
+      <c r="D11" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="58" t="s">
+      <c r="B12" s="70"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5761,17 +5766,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5780,14 +5782,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5809,16 +5814,16 @@
       <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5830,40 +5835,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="86"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8814,15 +8819,15 @@
         <v>120</v>
       </c>
       <c r="B1" s="100"/>
-      <c r="C1" s="166"/>
+      <c r="C1" s="152"/>
       <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
+      <c r="E1" s="156"/>
       <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="156"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -8836,15 +8841,15 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="102"/>
       <c r="B2" s="103"/>
-      <c r="C2" s="146"/>
+      <c r="C2" s="143"/>
       <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="144"/>
+      <c r="E2" s="141"/>
       <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="144"/>
+      <c r="G2" s="141"/>
       <c r="H2" s="108">
         <v>46177</v>
       </c>
@@ -8856,68 +8861,68 @@
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="164"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="105"/>
       <c r="B4" s="106"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="165"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="151"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="171" t="s">
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="173"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="162"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="163"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="164"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="166"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -8936,10 +8941,10 @@
       <c r="B9" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="152" t="s">
+      <c r="C9" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="152"/>
+      <c r="D9" s="167"/>
       <c r="E9" s="47" t="s">
         <v>115</v>
       </c>
@@ -8952,10 +8957,10 @@
       <c r="H9" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="152" t="s">
+      <c r="I9" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="153"/>
+      <c r="J9" s="168"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
@@ -9064,32 +9069,32 @@
       <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="132" t="s">
+      <c r="A16" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="163"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="136" t="s">
+      <c r="B17" s="158"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="169" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="138"/>
+      <c r="E17" s="170"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9098,11 +9103,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="132" t="s">
+      <c r="A18" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="133"/>
-      <c r="C18" s="135"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9115,11 +9120,11 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="139" t="s">
+      <c r="H18" s="172" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="134"/>
+      <c r="I18" s="158"/>
+      <c r="J18" s="163"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
@@ -9139,11 +9144,11 @@
       <c r="G19" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="143" t="s">
+      <c r="H19" s="173" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="141"/>
-      <c r="J19" s="142"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
@@ -9163,11 +9168,11 @@
       <c r="G20" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="140" t="s">
+      <c r="H20" s="132" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="141"/>
-      <c r="J20" s="142"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="134"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
@@ -9187,11 +9192,11 @@
       <c r="G21" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="140" t="s">
+      <c r="H21" s="132" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="134"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
@@ -9211,11 +9216,11 @@
       <c r="G22" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="140" t="s">
+      <c r="H22" s="132" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="141"/>
-      <c r="J22" s="142"/>
+      <c r="I22" s="133"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
@@ -9235,23 +9240,23 @@
       <c r="G23" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="140" t="s">
+      <c r="H23" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="141"/>
-      <c r="J23" s="142"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="154"/>
-      <c r="B24" s="155"/>
-      <c r="C24" s="156"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="137"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="159"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="140"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10232,6 +10237,33 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10248,33 +10280,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10294,182 +10299,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="87" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="87" t="s">
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="87" t="s">
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="87" t="s">
+      <c r="P1" s="53"/>
+      <c r="Q1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="74"/>
-      <c r="S1" s="87" t="s">
+      <c r="R1" s="53"/>
+      <c r="S1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="57"/>
+      <c r="T1" s="91"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="186"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="180"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="187"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="181"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="188"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="182"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="55" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="57"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="91"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="58" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="60"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="58" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="60"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="72"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10668,37 +10673,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="76"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="68"/>
+      <c r="C15" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="183" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="76"/>
-      <c r="G15" s="183" t="s">
+      <c r="F15" s="68"/>
+      <c r="G15" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="183" t="s">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="76"/>
-      <c r="L15" s="183" t="s">
+      <c r="K15" s="68"/>
+      <c r="L15" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="183" t="s">
+      <c r="M15" s="70"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="76"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10710,37 +10715,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="174">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="175" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="175" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="76"/>
-      <c r="G16" s="182" t="s">
+      <c r="F16" s="68"/>
+      <c r="G16" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="182" t="s">
+      <c r="H16" s="70"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="76"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="68"/>
+      <c r="L16" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="70"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="76"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="68"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10752,37 +10757,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="174">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="175" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="175" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="76"/>
-      <c r="G17" s="182" t="s">
+      <c r="F17" s="68"/>
+      <c r="G17" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="182" t="s">
+      <c r="H17" s="70"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="76"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="68"/>
+      <c r="L17" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="70"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="76"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="68"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10794,23 +10799,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="174"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="76"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="68"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10822,23 +10827,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="174"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="76"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="68"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10850,23 +10855,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="174"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="182"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="76"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="68"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10878,23 +10883,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="76"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="68"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10906,23 +10911,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="174"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="76"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="186"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10934,23 +10939,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="174"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="76"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="68"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10962,23 +10967,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="174"/>
-      <c r="B24" s="76"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="76"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="68"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -10990,23 +10995,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="76"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="68"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11018,23 +11023,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="174"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="76"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="76"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="68"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11046,23 +11051,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="174"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="76"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="68"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11074,23 +11079,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="76"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="76"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="68"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11102,23 +11107,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="76"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="76"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="68"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11130,23 +11135,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="174"/>
-      <c r="B30" s="76"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="76"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="68"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11158,23 +11163,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="63"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="75"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12172,62 +12177,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12252,62 +12257,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE8CBD5-533B-4D61-B12B-A1EE75303502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843C64D3-9A0C-467D-871A-733C7B2130EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1582,12 +1582,114 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1597,114 +1699,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1822,6 +1822,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1831,6 +1855,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1849,21 +1906,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1897,15 +1939,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1915,86 +1948,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3190,7 +3190,413 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>34211</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>77555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>347051</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="41" name="インク 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A7BAA35-6A3D-54B2-F11A-237A84CB17AC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="471240" y="2677320"/>
+            <a:ext cx="312840" cy="90720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="41" name="インク 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A7BAA35-6A3D-54B2-F11A-237A84CB17AC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="408240" y="2299680"/>
+              <a:ext cx="438480" cy="846360"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>366120</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>99155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>6141</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>70991</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="128" name="インク 127">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36B3B25D-15BD-3D3B-8C7C-38C312D87F54}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="366120" y="2698920"/>
+            <a:ext cx="514080" cy="1047600"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="128" name="インク 127">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36B3B25D-15BD-3D3B-8C7C-38C312D87F54}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="303480" y="2320920"/>
+              <a:ext cx="639720" cy="1803240"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>33131</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>257576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>357851</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>268292</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="162" name="インク 161">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16ECBBD9-8F57-0996-7173-238FC1111C0A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="470160" y="2588400"/>
+            <a:ext cx="324720" cy="1086480"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="162" name="インク 161">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16ECBBD9-8F57-0996-7173-238FC1111C0A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="407520" y="2210760"/>
+              <a:ext cx="450360" cy="1842120"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-06-16T08:13:23.963"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.35" units="cm"/>
+      <inkml:brushProperty name="height" value="2.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFFFF"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+      <inkml:brushProperty name="inkEffects" value="pencil"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">497 252,'0'-6,"0"-11,5-9,7 0,2-1,3 5,0 0,1 4,3 5,-2-1,-14 3,-14 3,-16 7,-9 10,-3 4,-2-1,1-3,-4 9,1 0,6 3,4-2,3-5,21-4,18-4,16-4,11-1,2-1,-9-1,-17 0,-14 0,-14 1,-10-1,-5 1,-4 0,-1 0,0 0,0 0,1 0,1 0,0 0,0 0,1 0,0 0,11 0,13 0,14 0,11 0,8 0,4 0,3 0,1 0,0 0,-1 0,0 0,-1 0,0 0,-1 0,0 0,0 0,0 0,0 0,0 0,1 0,-1 0,0 0,0 0,0 0,0 0,-11 0,-13 0,-14 0,-11 0,-7 0,-6 0,-1 0,-2 0,0 0,1 0,0 0,1 0,0-5,1-2,-1 0,1-3,5-6,3-1,9 4,13 3,12 4,9 3,7 1,3 2,-2-5,-2-1,1-1,1 2,1-3,1-1,0 1,1 2,0 2,0 2,0 1,0 1,1 0,-1 1,0-1,0 0,1 1,-12-1,-13 0,-9-5,-9-3,-7 2,-7 0,-4 2,-3 2,0 0,-1 2,0 0,0 0,7 6,1 1,1 0,-2-1,-1-2,8-2,14 0,13-2,10 6,7 0,0 6,0 0,2-2,1-2,1-3,2-2,0-2,0 5,0 1,1-1,-6 4,-12 0,-14-1,-13-2,-8-3,-7-2,-4-1,-1 0,-1-2,0 1,1 0,1-1,0 1,0 0,1 0,0 0,0-1,0 2,0-1,0 0,10 0,15 0,13 0,11 0,7 0,5 0,3 0,1 0,0 0,-1 0,-5 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-06-16T08:14:07.766"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.35" units="cm"/>
+      <inkml:brushProperty name="height" value="2.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFFFF"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+      <inkml:brushProperty name="inkEffects" value="pencil"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">664 2340,'0'5,"0"-3,0-8,0-8,0-6,0-6,0-4,0-1,0-2,0 0,5 1,2 0,5 5,6 8,5 6,4 12,2 5,-3 8,-1 1,1-1,0-3,2-2,-4 2,0-1,-11 0,-12-3,-11-2,-10-1,-7-1,-3-1,-3-1,5 6,2 2,-1 0,0 3,4 6,6 6,6 3,5 4,3 2,2 1,2 0,0 0,6-5,6-8,7-6,10-6,6-4,1-3,1-6,-2-13,-1-3,-2 2,0-1,-7 9,-7 11,-7 11,-5 10,-10 6,-4 4,-6-3,-1 0,2-1,3 2,-2-5,0 0,3 0,-3-2,0-1,2-8,3-12,3-12,1-8,1-6,1-4,6-3,1 0,0-1,4 7,0 1,4 1,-1-1,2 4,-1 0,-3-1,1 3,-6 10,-11 8,-3 8,-7 4,-6 5,1 6,-3-2,-2-3,3 1,0-2,-2-5,3 2,-1-1,-1 3,-3-1,3 2,5-6,6-16,4-11,4-8,2-6,7-1,2-2,5 1,1 0,2 1,0 1,1 5,-1 14,1 13,-2 2,-4-5,7-13,6-8,4-6,8-2,-3-3,-6 1,-8 1,-7-1,-11 7,-11 8,-9 6,-7 12,1 10,-5 15,-4 9,0 4,5 0,2 0,-5 4,-2 0,-1-1,1-8,0 2,1-5,1-3,0 6,1-4,5 0,2 0,0 0,-7 1,2 1,1-5,5-1,1 0,-1 2,-2 1,-2 2,-2 1,5 1,0 0,0 1,-2-6,3-2,1 1,-1 1,-2-4,2-1,1-3,4-15,16-25,13-19,15-2,9-5,3 1,12-8,2-10,3 1,-2 0,5 1,3 6,-8 7,-3 6,-10 7,-6 3,-4 2,-1 7,-1 3,-5-1,-1 3,1 1,2 3,-3-1,-6 8,-5 10,-5 11,-3 8,-2 6,-1 4,-1 3,0 0,0 0,0 0,0 0,1-1,5-6,7-7,2-12,-2-13,-8-15,-5-11,-13-4,-3-1,-5 5,2 3,3 1,1 5,2 2,-2-2,3-1,-3-2,1-3,4-1,-1 0,0-2,4-4,2-3,2 1,2 1,2 2,0 1,0 2,1 0,-1 1,1 0,-1 0,0 0,0 0,0 0,-5 0,-2 0,0 0,1 0,2 0,2 0,0 0,2 0,0 0,0-1,0 1,1 0,-1 0,0 0,0 0,0 0,0 0,0 0,0-1,0 1,0-5,0-2,0 0,0 1,0 2,0 2,0 0,0 2,0 0,0 0,0 16,0 16,0 13,0 9,0 12,0 15,0 5,0-2,0 1,0 7,0-2,0-5,0-2,0-4,0 6,0-1,0 0,0-2,0 5,0 4,0-3,0-1,0-4,0-6,0-21,0-21,0-15,0-12,0-18,0-7,0-1,0 4,0 2,0 5,0 3,0-9,0-1,0 0,0 4,0 3,0 3,6-9,1-2,0 2,3 2,1 4,-2-8,-2-1,-3 1,-1 5,3 8,1 5,0 1,-2 1,-2-1,0 10,-2 12,-1 13,0 16,0 14,-1 5,1 2,0-2,0-3,-1-3,1-3,0-1,0-1,0 4,0 1,6-5,1-3,-1-12,-1-13,-1-14,-1-10,-2-6,-1-11,0-3,0-1,5 8,2 2,5 8,6 2,4 5,0 0,-5-4,6 3,4 4,2-1,3 1,0 4,-5-2,-2-5,0 0,2 4,1 3,0 3,8 3,1 2,-4 6,-4 2,0 1,-1-2,-4 4,-2 0,-4 3,-11 0,-11-3,-11-2,-8-4,-5-1,-3-2,-2-1,-1 0,1-1,0 1,1-1,5-4,3-3,-1-4,0-5,-3-1,5-1,0-4,5-3,4-2,6-2,-2-1,-4-6,0-2,3 1,2 1,-1 2,0 1,8 7,8 7,10 8,1 11,-2 11,2 4,3-1,4-8,-3-9,1-5,-3-6,0-6,2 2,3 2,3 6,-9 3,-13 4,-12 3,-10 0,-8 2,-5 0,-2 0,-2 0,0-1,1 0,6 6,7 12,7 8,6 5,4 3,3 0,1 1,0-2,1 5,-1 2,0-2,0-1,-1-2,0-1,0-2,0 5,0 1,0-1,0-1,0-1,-5-2,-2-1,0 0,2-1,-4-5,-1-2,-3 0,0 1,-3-3,1 0,-2 6,2 4,-2 2,2-5</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-06-16T08:13:01.605"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.35" units="cm"/>
+      <inkml:brushProperty name="height" value="2.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFFFF"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+      <inkml:brushProperty name="inkEffects" value="pencil"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">530 374,'0'5,"0"8,0 6,0 5,0 4,0 3,0 6,0 8,0 12,0 2,0-5,0 0,0-4,0-6,0-4,0-15,0-17,0-20,0-13,0-8,0-4,0 0,0 0,6-4,1 0,0-4,4 1,-1 2,-1 3,-2 3,3 2,-1 2,-2 1,-1 0,-3 0,-1 1,-1-1,-1 0,0 6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="671.66">623 187,'0'5,"0"8,0 6,0 5,0 5,-5-4,-2 0,1 1,0 1,-3 1,-5 7,-1 3,2-1,-2 0,2-2,3-1,-2-2,1 0,2 0,3-1,2 0,2-1,-4-4,-6-2,-1 0,1 1,3 3,-2-5,1 5,2 3,2 2,2-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2950.34">33 187,'5'0,"7"0,7 0,6 0,3 0,3 0,1 0,0 0,1 0,-1 0,0 0,-1 0,1 0,-1 5,-5 13,-7 19,-7 8,-6 2,-3-1,-3-4,-1-4,0-2,0-3,0-1,0-1,-5-1,-1 1,0 4,-4 3,-5 0,0-2,3 4,-2 0,1 0,4 2,-2 0,1-2,2-2,-2-3,0-2,3-1,-4 0,1-2,3 1,2-1,2 1,2 0,-4 0,-1-16,1-31,1-19,2-8,6-3,3 2,5-2,2 0,-3-1,4 1,3-7,0 0,2-1,-2 3,1-1,-2 4,-5-1,2-3,-1-2,2 1,-1 1,-3 2,3 6,-2 4,4 4,-2 3,-3 1,-2 2,-4 10,-2 14,-1 14,-1 11,0 17,-1 9,0 1,1-1,0-4,-1-3,-4 3,-2-1,1 9,0 2,-3 2,0 3,-5-3,1-5,3-5,-3-5,1-4,3-2,-3 4,1 2,2-2,3 0,2-2,-3-6,-1-3,1 0,2 0,2 2,1 2,-4 0,-1 2,0-11,2-13,2-24,1-15,1-7,0-2,1 1,1 2,-1 1,0 3,0 1,1-4,-1-1,0 0,0-3,5-6,2 0,-1 3,0 3,-2 4,3 8,2 3,-2 1,-1 0,-3 9,-1 12,5 24,0 13,-1 6,-1 2,-1-1,-2-2,-1 4,-1-1,0-2,0-1,-1-3,1-2,0-1,0-1,0 0,0 0,0-1,0 1,0 0,0-11,0-14,0-13,0-10,0-9,0-4,0-3,0 0,0-1,0 0,0 1,0 1,5 0,2-4,5 3,1 2,-3 1,-2-4,3-3,-1 1,-2 0,-3 1,-1 2,3 11,1 15,-1 14,-2 11,-2 8,-1 4,4 3,1 1,5 0,1 0,-3-2,-3 1,-2-2,-2 1,-2-1,-1 5,0 2,-1 0,1-1,-1-2,1-2,0-1,0 0,0-1,0 0,0 0,0-11,0-19,0-26,0-14,0-5,0-1,0 2,0 4,0-4,0 2,0-4,0 1,0 3,5 8,2 4,-1 2,0 1,-2 9,-2 14,-1 27,0 16,-1 6,-1 6,1 5,0-3,0 1,-1-4,1-5,0 0,0-3,0 2,0-1,-5-3,-2-2,-5 1,0 5,-4 6,2-1,-4 2,3-3,3-4,4-4,-2-5,1-2,-4-8,1-2,2-1,-3-14,2-14,1-11,-1-4,-5-8,0-5,-2-3,1 1,5 0,3 1,-1 1,-5-5,1-1,2 1,-2 2,2 1,-3 2,1 1,3 0,-1 1,0 0,3 0,3 6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4608.95">157 1183,'0'6,"0"-5,6-1,6 9,2 14,-2 9,-3 8,3 9,-2 2,-1 2,-3-3,2-4,1-5,-2-4,-1-3,-3-2,-1-1,-7-6,-1-23,-6-17,-1-22,2-10,3-7,3-1,2 0,2-3,0 5,2-1,-1-6,1 2,-1 0,0-1,1-1,-1 4,0 2,5 4,7 6,2 4,-2 5,-3-3,2 5,5 8,5 9,4 6,8 11,-1 21,0 6,-7 5,-7 1,-1 0,-4 0,2-6,-2-2,-4-1,-2 1,-3 1,-3 2,0-10,-1-13,-1-13,1-11,-1-7,1-5,-1-2,6 3,7 3,2-6,3 3,5 1,-2 0,1-1,2 5,3 7,2 5,2 6,0 3,-4 18,-7 18,-6 7,-6 4,-4 9,-2 1,-2 2,0 2,-6-3,-1-6,1-6,-4 0,-6 3,1 5,2-1,5-4,2 1,-1-7,-6-6,0-3,2-2,-2 0,2 0,-3 1,-5 5,2 2,4 1,4-2,-1-6,-4 2,0 1,-2 0,1 0,-1-6,-4-7,-3-8,2-10,6-17,4-11,0-11,1-5,3-1,-2-3,0 0,2 3,2-1,3 1,1-3,1 1,-4-2,-2 2,0 3,2 3,2 3,1 3,0 1,2 1,0 0,-5 1,-2-1,1 1,1-1,1 0,2 10,1 15,0 13,1 11,1 7,-1 5,0 3,0 1,1 0,-1-1,0 0,0-1,0 0,0-1,0 0,5 0,2 1,-1-1,0 0,-2 0,-2-11,-1-13,0-14,-1-11,-1-8,1-4,0-3,0-1,-1 1,7 4,6 14,7 36,1 19,-4 8,-5 1,-3-2,-4 1,-2-1,-2-5,0 2,-1-2,0-2,0-13,1-17,0-15,-1-13,1-7,-5-11,-2-5,0 0,1 2,3 1,-5 8,0 4,1 0,1 0,3-1,1-1,1-2,-5 0,-1-1,1 5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7005.74">343 1276,'6'0,"6"0,2 6,-2 6,-3 12,3 3,-1 1,-3 6,-2 9,-2 7,-2 1,-1-4,4-4,1-4,0-3,-1-3,-1-2,-2 0,-1-1,-1 1,0-11,0-25,0-16,-1-16,1-7,0-6,0 0,0-2,0 2,0 0,0 2,0 5,0 4,0-2,0 0,0 3,0 2,5 7,3 14,-2 15,0 12,-2 10,-2 6,0 9,-2 4,0 0,0-2,0-2,-1-2,1 4,0 0,0-1,0-2,0-2,0-11,0-16,0-19,0-13,0-18,0-7,0-5,0 0,0 6,0-1,0-1,0-4,0 3,0 5,5-5,2 0,0 4,3 5,1 5,-2 3,-2-3,3 0,4 0,1 3,-3 1,2 1,4 6,-1 14,-3 18,-5 15,-3 9,-3 4,-2 3,-1 5,0 1,-1 4,0 0,0-3,1-4,0-2,0-3,0-2,0-1,0 5,0 1,0 6,0 0,0 4,0-2,0-2,0-3,0-4,0-2,-6-2,0-1,-6-1,-1 1,2-1,4 1,1 0,-2-5,0-18,1-16,2-16,2-10,1-5,6-5,9-7,1 1,3-3,0 4,-4-2,-4 4,-3 3,-3-5,-2-1,4 3,2 5,-1 3,4 4,0 2,-1 2,-3 0,4 1,5 5,-1 12,-1 14,-4 11,-3 16,-3 7,-2 14,-1 3,0 5,-1 7,1-1,-1-7,1 4,-1 2,1 1,0-5,0-2,0-5,0 0,0 6,0 0,0-6,0 0,0-3,0 0,0-3,0 2,0 4,0-2,0-4,0-4,0-4,0-14,0-16,0-14,0-11,0-14,0-6,0-7,0-2,0 3,0 2,0 4,0 3,0 2,0 2,0 0,0 0,0 1,0-1,0 1,0-1,0-5,0-3,0 1,0-3,0-1,0 1,0 4,0 1,0 3,0 0,0 2,0 0,0-5,0-1,0-1,0-9,0 9,0 21,0 19,0 20,0 16,0 8,0 5,0 1,0-4,0 6,0-1,0 1,0-3,0 0,0-4,0 2,-5 3,-2 2,1-1,-5-6,0-5,2-4,2-4,3-23,1-24,2-20,1-11,0-18,1-4,-1 4,0-4,1-1,-1 1,0-5,0 4,0 9,0 4,0-1,0 5,0-5,0 1,0-1,0 4,0 6,5 4,3 4,-2 4,0 1,-2 23,-2 23,0 14,-2 19,0 6,0 0,0 7,-1-2,1 5,0-3,0 0,0-7,0-5,0-1,0-4,0 3,0-3,0-2,0-3,0 2,0 0,0 4,0-1,-6-7,-1-5,0-2,2-1,1 1,-4-6,0-16,1-15,2-12,1-18,2-8,1-12,-5-1,-1 4,1 5,-5 7,1 5,1 4,3 2,2 2,1 0,-3-5,-2-2,2-6,-4-5,-1-1,-3 4,1 3,2 5,4 2,2 2,2 2,3 10,-1 16,2 34,-1 22,1 9,0 5,-1 1,0 0,0-5,0-9,0-2,0-4,0-5,0-4,0 3,0-1,0 4,0-1,-5 5,-2 3,0-1,1 2,2-2,2-5,1-4,0-4,1-13,0-16,1-14,-1-17,0-9,0-10,0-3,0-4,0-4,0-4,0 3,0 0,0 5,0-1,0 4,0 4,0 4,0 4,0 2,0 2,0 0,0 1,0-6,0-1,0-1,0 2,0 2,0 0,0-4,0 0,0-5,0-1,0 24,0 20,0 15,0 11,0 6,0 9,0 1,0 6,0-2,0 9,0-1,0 2,0-4,0 0,-5 2,-2-3,1 0,0 2,-3 3,0-3,-5 0,1 2,3-4,-3-4,1-6,-3 1,2-1,2-2,4-3,2-2,-2-7,-1-2,1-1,2 1,2-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8676.07">95 281,'5'0,"8"0,6 0,10 0,6 0,3 0,-1 0,-6-11,-3-3,-1 1,0 2,1-2,6 1,3 2,-5-1,2 0,-4-3,-2 1,-11 2,-14 4,-13 7,-9 5,-8 6,-3 7,-3 0,-1-2,0-5,6 1,3-1,-1-2,0-4,-2 9,0 2,-2-2,0-4,-1 3,-1-2,6 4,13-2,13-3,12-3,9-3,7-1,3-2,3-2,-1 1,-4-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9347.22">126 249,'0'6,"0"6,5 2,7-2,8 2,4 0,4-4,3-2,1-4,0-2,1-1,-1-1,-5-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10045.05">220 374,'0'5,"0"8,5 0,7 5,7-2,0 3,2-3,3-4,8 1,4-1,-5 3,-1-2,-2-3,1-3,0-2,1-3,0-1,-5-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10697.19">343 468,'22'0,"11"0,6 0,2 0,-1 0,-2 0,-2 0,-2 0,-2 0,5 0,1 0,0 0,-2 0,-1 0,-2 0,-6 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11338.76">468 281,'5'0,"8"0,6 0,5 0,5 0,7 0,3 0,0 0,-1 0,-2 0,-7 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11872.58">63 249,'6'0,"6"0,7 0,6 0,3 6,3 1,1 0,0-2,1-1,4-2,2 0,-1-2,-1 0,-2 0,-1 0,-1-1,-2 1,-5 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12351.44">250 124,'0'6,"6"1,6 5,7 0,5-1,5-3,1-3,2-2,1-2,-1-1,-5 5,-2 2,0-1,1-1,-4-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="12833.99">406 311,'0'6,"0"6,0 7,5 1,7-4,8-4,4-5,5 3,-4-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="13436.63">500 343,'5'0,"7"0,12 0,8 0,3 0,1 0,5 0,1 0,-2 0,-1 0,-4 0,-6 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="14366.54">375 343,'5'0,"8"0,6 0,5 0,4 0,3 0,1 0,0 0,1 0,-1 0,0 0,0 0,-1 0,0 0,-5 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15010.14">437 343,'6'0,"6"5,7 2,0 5,2 1,3-3,3 4,1-2,2-3,1-2,1-3,-1-2,1-1,-11-1,-14-1,-14 1,-11-1,-7 1,0-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="15827.51">1 436,'0'6,"5"1,3 5,4 0,5-1,1 2,2-1,3-3,3-2,2-3,2-2,0-1,2-1,-1-1,1 1,0-1,-1 1,1-1,-1 1,0 0,0 0,1 0,-1 0,0 0,-6 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="17003.99">530 529,'0'6,"0"6,6 2,1 3,5 5,6-2,4-4,5-5,3-5,1-2,1-3,0-1,0-1,-5-5,-7-7,-13-2,-18-3,-12-3,-8 0,-4 5,5 0,1 2,1 4,-1 4,0 2,0 3,4 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="26490.86">157 1775,'6'0,"1"11,5 8,0 7,-1 3,2-2,-1 5,-3 1,3 6,-1 3,3-7,0 1,-4 0,-2 5,1-5,1-3,-3-2,-2-1,4-1,0 1,-1 0,-3 1,-1-1,-2-9,-1-15,-1-13,0-11,-1-7,1-11,0-3,-1-2,1 2,0 2,0 12,0 22,0 16,0 16,0 14,0 6,0-2,0 3,0-2,0-4,0-4,0-4,0-2,0-2,0-1,0-17,0-15,0-13,0-10,0-6,0-3,-5-1,-2 0,0 0,1 1,2 0,2 1,0 1,2 0,0-6,0-1,0 1,1-5,-1 0,0 2,0 2,0 13,0 22,0 15,0 18,0 8,0 4,0-1,0-2,0-2,0-2,0-2,0-1,0-1,0 0,0 0,0-1,0 1,0 0,0 0,0-10,0-31,0-23,0-12,0-9,0-5,0 1,0 6,0-5,0 3,0 0,0-8,0-2,0-2,0 0,0 5,0 3,0 7,0 0,0 4,6-6,1 1,0 4,-2 0,4 2,6 4,0 3,-2 4,-4-3,-3 0,3 1,-1 11,-1 17,-2 14,-2 12,-1 8,-1 6,-1 2,-1 1,1 0,0-1,-1 0,1 0,0-2,0 6,0 2,0-2,0 5,0 0,0-2,0-3,0-1,-5-3,-2 0,0-2,-3 0,-1 0,1 5,4 1,1 1,3-2,-5-1,0-2,1 0,1-12,2-15,1-13,1-11,1-8,0-4,5-8,8-3,1 0,-2 2,-2 3,1 1,0 2,-3 1,4 1,-2 0,-1 0,2 6,6 1,4 5,-1 11,-5 12,-3 11,-5 8,-4 6,-1 2,-2 2,-1 6,0 2,0-2,1 4,-1 0,1 3,0-1,0-3,0-3,0 2,-6 5,0 0,-6 2,-1-1,2 2,4-3,1-3,-2-9,0-5,-4-2,0-1,1 1,4 1,-3-4,1-11,1-14,3-12,1-8,2-7,2-9,0-3,0 0,0 1,1 2,-1 2,0-4,0 0,0-4,1-6,-1 1,0-3,-1 3,1 4,0 4,0 3,0-2,0 0,0 2,0 1,0 12,0 16,6 15,1 10,-1 9,-1 5,-1 2,-1 1,-2 0,-1-1,0 0,0-1,0 5,0 2,-1-1,1-2,0-1,0-1,0-2,0-1,0 0,0 0,0 0,0 0,0 0,0 0,0-11,0-13,0-14,0-11,0-7,0-6,0-2,0-1,0-5,0-1,0-5,0-5,0-4,0 1,0 4,0 6,0 5,0 3,0 2,0 2,0 1,0 0,0 0,0-1,5 6,3 12,-2 13,0 12,-2 10,-2 11,0 6,-2 1,0-1,0-2,0-1,-1 3,1 0,0 5,0 0,0-3,0-2,0-4,0-1,0-2,0-11,0-15,0-14,0-10,0-8,0-10,0-4,0 0,0 1,0 1,0 3,0 2,0-5,0 0,0 0,0-3,0-1,0 2,0 3,0 1,0 3,0 1,0 0,0 1,0 1,0 5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="26859.2">500 1557,'0'6,"0"6,0 7,5 10,2 17,0 6,-2-2,-1-2,-2-6,-1-3,0-4,-1-3,-1-1,1 0,0-1,0 0,0 1,-1-1,1 1,0 0,0 0,0 1,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="27214.33">468 1962,'0'5,"0"7,0 7,0 6,0 3,0 2,0 2,0 1,0 0,0-1,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="27586.36">406 1775,'0'5,"0"8,0 5,0 7,0 3,5-2,2-1,0 0,-1-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="27906.75">437 1775,'0'5,"0"8,0 5,0 7,0 3,0 3,0-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="28208.8">406 1619,'0'5,"0"7,0 7,0 6,5 3,2 3,5-4,1-2,-3 1,-2 1,-3 1,-2 1,-2-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="28550.62">468 1588,'5'0,"3"5,-2 7,0 7,-2 6,-2-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="28865.68">500 1650,'5'11,"7"8,2 7,-2 4,3-3,-2-1,2 6,-1 2,3 2,-3-1,-2-1,-4-1,1-1,1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="29192.3">562 1806,'5'16,"2"10,5 1,0 7,-1 2,-4 1,4-1,-1-1,-2-2,-2 0,-3-1,-1-1,-1 0,-1 0,0 0,-1 0,1-16,0-15,-1-20,1-10,0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="29523">530 1588,'0'5,"0"7,0 7,0 6,6 3,1 3,0 1,-2 0,-1 1,-1-1,-2 0,0 0,-1 0,-1-1,1-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="29863.9">562 1588,'5'5,"2"7,0 7,3 1,1 1,3 3,0 2,2 3,-1 1,-3 1,1 1,-1 0,-3-1,-2 1,2-1,0 0,-2 1,-2-1,-2 0,-1-11,-1-13,-1-14,-6-16,-6-10,-3-4,-2-1,0 1,4 0,-1 8,1 3,3 5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="30178.46">530 1059,'0'5,"0"7,0 7,0 6,0 9,0 3,0 2,0-1,0-2,0-1,0-2,0-1,0 0,0-1,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="30484.74">500 871,'0'6,"0"6,0 13,10 17,4 7,0 6,2-1,-1-5,-4-5,-3-5,-3-4,-3-2,-1-2,-1 0,-1-1,0 0,1 0,-1 1,1 0,0 0,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="30802.77">468 966,'5'10,"8"9,1 7,-2 4,2 2,0 1,-4 1,3-1,-2-1,-2 0,-3 0,-2-1,-2 0,-2 0,0 0,0 0,-1 0,1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="31073.24">530 686,'0'10,"0"9,6 12,1 6,0 2,4-1,-1-1,5-1,-2-2,-2-2,-3 0,2-1,0 0,3-5,-1-3,-2 2,-3 0,-2 2,-3 2,-1 1,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="31372.69">593 966,'5'0,"7"10,7 4,0 5,3 4,-4 4,2 2,-4 2,2 1,3 0,-3 0,-4-1,1 1,-2-1,-3 1,-4-1,-2 0,-2 0,-2 0,0 1,-1-1,1 0,-1 0,1 0,-1 0,1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="31726.85">748 779,'0'5,"0"13,0 8,0 5,0 2,0 2,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32041.31">500 63,'0'5,"0"8,0 5,0 12,0 5,0 3,0-1,0 0,0-3,0 0,0-1,0-2,0 1,0-2,0-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32297.02">468 1,'0'5,"0"7,0 7,0 6,0 3,0 2,0 2,0 1,0-1,0 1,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32569.68">468 281,'5'5,"3"7,4 7,0 6,4-2,-1 1,-3 1,-4 2,-3 1,-2-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32828.77">562 374,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33066.47">530 561,'0'5,"0"7,0 7,0 6,0 3,0 3,0 1,0 0,0 1,0-1,-5-5,-2-8</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33324.52">437 841,'0'5,"0"23,0 12,0 16,0 8,0-2,0 0,0-5,0-8,0-1,0-4,0-3,0-4,0-3,0-2,0-1,0 0,0-1,0 0,0-15,-5-22,-2-8</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33610.09">313 841,'0'5,"0"7,0 7,5 11,2 16,-1 6,0-1,-2-4,-2-5,-1-3,0-4,-1-3,-1-1,1 0,0-1,0 0,-1 1,1 0,0-1,0 1,0 1,0-1,0 0,0 0,0 0,0 0,0 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33913.01">281 779,'0'5,"5"18,3 10,4 26,0 8,4 9,-1-3,2 1,-2-6,-3-10,-4-8,-3-4,-3 3,-1-4,-1 3,-1 3,6 4,1-3,1 1,-2-4,-1-4,-2-5,-1 1,0 0,-1-3,0-2,-1-2,1-2,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34200.13">343 1433,'0'10,"0"10,0 11,0 5,6 14,1 2,0-1,-2-5,4-10,1-6,-2-2,-3-1,-1 0,-2 1,5 1,0 0,0 2,-2 0,-2 0,-1 0,0 0,-2 1,0-1,0 0,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34507.23">437 1743,'0'6,"0"6,0 7,0 11,0 5,0 3,0-1,6 5,1 0,-1-2,-1-2,-1-3,-1-1,3-2,2 0,-1-2,3-4,1-2,-2-1,-3 3,-2 1,-2 1,-1 2,-1 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34824.27">655 1775,'0'5,"0"8,0 5,0 7,0 9,0 3,0 7,0 1,0-2,0-3,0-3,0-2,0-2,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35134.21">655 1962,'0'10,"0"10,0 5,0 5,0 2,0 1,0 0,0 1,0-2,0 0,0-11,0-9</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35467.2">623 1930,'0'6,"0"6,0 23,0 16,0 10,0-1,0 1,0-5,0-7,0-6,0-5,0-4,0-3,0 0,-5-7,-2-1,1 0,0-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35753.54">530 1806,'0'10,"0"10,6 6,1 4,0 2,-2 1,-1 0,-1 0,-2-1,0 0,-1 0,-1-1,1 1,0-1,-1 0,1 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36042.39">530 2023,'0'11,"6"14,1 7,0 5,-2 1,-1-1,-1-1,3-7,2-3,-2-1,-1 1,-1 1,-2-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36299.26">500 2086,'0'10,"0"10,5 0,2 3,0 3,-2 1,-1 3,3-5,2-1,-2 1,-1 1,-3 2,0 1,-2 1,-1 1,0 0,-1 1,1-1,0 0,-1-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36587.83">500 2397,'0'6,"0"6,0 7,0 5,0-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36941.98">500 2397,'0'6,"0"6,0 7,0 5,0-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37264.29">468 2428,'0'21,"0"18,0 7,0 2,0-3,0-3,0-4,5-8,3-4,-2-1,0 0,-2-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37534.8">468 2522,'0'5,"0"8,0 6,0 5,0-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37821.52">437 2490,'6'0,"6"11,7 3,0 5,-3 4,-4 4,-5 2,-3 2,-2 1,-2 0,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38108.49">530 2428,'0'5,"0"8,0 6,0 5,0 5,0 2,0 1,0 0,0 1,0-1,0 0,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38383.85">437 2366,'0'5,"0"7,0 8,0 4,0 4,0 3,0 1,0-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38670.06">437 2522,'6'11,"6"8,2 7,-2 4,-3 2,3 1,-2 0,4 0,-1-1,-2 0,-4 0,-3-1,4-5,0-2,-2 1,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38943.58">593 2677,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39315.7">593 2490,'0'6,"0"11,0 10,0 4,0 3,0 0,0 1,0-2,0 0,0-1,0 5,0 2,0-1,0-2,0-1,0-18,0-16,0-14,0-10,0-7,0 2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39642.17">530 2460,'0'10,"0"15,0 8,0 3,0 2,0-1,0 4,0 0,0-1,0-3,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39873.51">468 2335,'0'5,"0"8,0 5,0 7,5 3,3 3,-2 1,0 1,-2-1,-2 0,0 0,-2 0,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40100.86">500 2490,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40339.01">500 2366,'0'10,"5"10,7 6,2 4,-2 2,3-4,-2-2,-3 0,-3 1,-2 2,2-6,1 1,-2 0,-1 1,-2-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40582.01">562 2428,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40835.73">562 2428,'0'5,"0"13,0 8,0 6,0-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41137.85">500 2180,'0'5,"0"7,0 7,0 6,0 3,0 3,0 0,0 2,0-1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41501.88">343 1993,'0'5,"6"7,1 7,5 6,0 3,-1 3,2 1,5-5,-2-2,-2 6,0 3,0 0,-4 1,-4-2,-2 1,-2-2,-1 0,-2-1,1 0,-1 0,1 0,-1 0,1-10,0-20,0-15,0-16,0-8,0-3,0 6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41819.55">500 1962,'0'10,"5"10,2 11,5 11,6-2,-1-1,-2-4,-5-1,-3-1,2-2,-1 0,4-1,0 1,-2 0,-3-1,-2 1,-3 0,-1 1,-1-1,0 0,0 0,-1 0,1 0,-1-10,1-14,0-14,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42121.67">530 2148,'0'5,"0"8,6 6,6 5,2 5,-2 2,-3 0,-2 2,1-6,1-2,-2 0,-2 2,-1 0,3 2,1 1,-2 1,0 0,-3 0,-1 1,-1-1,0 0,-1 0,-1 1,1-1,0-16,-6-16,-1-12,-6-10,-4-12,-1-5,4 0,-2 0,-3-3,2 0,3 3,5 2,-2 8,1 9</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42383.21">437 2148,'0'5,"0"8,0 6,0 5,0 5,0 2,6-5,1 5,-1 2,-1 5,-1 3,-1-1,-2-2,-1-2,0-2,0-2,0-10,0-16,-1-13,1-12,0-12,0-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42632.71">406 2055,'0'5,"0"13,5 8,2 5,0 3,-1 0,3 1,0-1,-1-2,3 1,0-2,-2 1,3-1,-1 0,-2 0,-8-6,-10-1,-2-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42930.02">343 2490,'0'-5,"0"3,0 8,0 8,0 6,0 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43315.6">343 2490,'0'6,"0"6,0 7,0 6,0 3,0 3,0 1,0 0,0 6,0 1,0 0,0-2,6-7,1-3,0-12,-2-14,-1-12,-1-9,-2-7,-1-4,0-2,0-6,0-2,0 1,-1 2,1 2,0 8</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43555.87">375 2366,'5'10,"2"10,0 6,4-2,-1 1,0 2,-4 1,4-4,-1-1,-1 1,3-4,0 1,-3 1,-1 3,-3-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43838.03">437 2117,'0'6,"0"6,0 7,0 5,6 5,1 7,-1 2,-1 2,-1-3,-1 0,-2-8</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="44195.53">437 2055,'0'-5,"0"3,0 7,6 9,1 7,-1 5,5 3,0 3,-2 0,-2 6,2 1,1 6,-3-1,-1-2,-2-3,-3-2,0-3,-1-12,0-16,0-13,-1-11,1-8,-6-5,-1-3,1 6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="44542.1">468 1868,'0'5,"0"8,0 6,0 11,0 10,5-1,3-2,-2-2,0-1,-2-2,-2-1,0 0,-2 0,-5-6,-8-11,-1-15,2-12,-3-8,1-7,-2-4,2 4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="44889.53">313 1588,'0'5,"0"7,0 13,5 6,2 4,5 1,0 0,-1-1,-3-1,2-1,0-1,-2-1,3-5,0-2,-3 0,-1 2,2 6,0 4,-2-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="46946.07">593 2709,'0'-5,"0"-13,0-8,0-11,0-4,0 0,0 1,0 3,0-4,0 0,0 3,0 1,0 2,0 2,0 1,0 1,0 0,0 0,0 0,0 0,0 1,0 15,0 15,0 14,0 9,0 6,5 4,2 1,-1 1,0-2,-2 1,-2-2,-1 0,0-1,-1 0,-1 1,1-1,0 0,0 0,-1-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="49096.08">593 2304,'0'6,"0"6,0 7,0 5,0 4,0 3,0 1,0 0,0 1,0-1,0 0,0 0,0-1,0-10,0-14,0-14,-5-11,-2-8,0-4,2-3,1-1,2 21,0 19,2 12,0 10,0 5,0 1,1 2,-1-1,0-1,0-2,0 1,0-2,0 1,0-1,0 0,0 0,0 0,0-11,0-13,-5-14,-2-11,0-8,1-4,2-3,-3-1,-2 0,2 1,2 0,1 1,-3-5,-1-1,-4 0,-1 1,3 3,3 0,2 2,2 0,-3 12,-2 24,2 17,1 11,2 5,0 1,3-1,-1 0,-4-7,-2-15,1-14,1-13,2-9,0-7,-3-4,-2-2,-4 0,0 0,2-5,2 0,3 0,3 2,0 2,2 2,1 11,-1 15,1 15,-1 10,0 7,1 6,-1 2,0 1,0 0,0-1,0 0,0-1,0 0,0-1,0 1,0-1,0 0,-6-11,-1-13,0-14,2-16,1-10,1-4,2-1,1 0,0 2,0 1,0 1,0 2,1 1,-1 0,0 0,0 0,0 0,0 0,0 1,0 9,0 15,0 13,5 10,3 9,-2 4,0 3,3 6,0 2,-1 4,-2 0,3 3,1-1,-3 2,-1-3,-2-3,-2-4,-1-3,-1-3,0-12,-1-14,1-15,0-10,-1-8,1-5,0-2,0-1,0 0,0 0,0 1,0 1,0 11,5 14,2 14,0 11,-2 8,-1 4,4 3,0 1,-1 0,-1-1,-2 0,3-6,1-13,-1-14,-2-12,-2-10,-1 5,-1 10,5 11,6 11,2 3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="50009.6">530 2770,'6'-5,"1"-7,5-2,6-8,-1-7,-3-3,-3-1,-5-1,-2 0,-2 1,-2 1,-1 0,-5 5,-7 14,-1 13,2 12,-3 5,2 4,2 4,4 3,2 2,3 1,2 1,0 0,0-11,1-8</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="50370.49">500 2397,'0'6,"0"6,0 7,0 5,0 5,0 1,0 2,0 1,0-1,0 1,0-1,0-1,0-10,0-14,-6-14,-1-11,0-13,2-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="51582.81">437 2273,'0'5,"0"7,0 7,0 6,0 3,6-3,1 0,5 6,0 4,-1 0,-3 0,-3-1,-2-1,-2 0,-1-1,0-1,-1 0,1 0,-1-10,1-15,0-13,0-11,0-8,0-4,0-3,0 0,0-1,0 0,0 2,0-1,0 2,0-1,0 1,0 0,0 0,0 0,0 11,0 13,5 9,2 9,0 7,-2 7,-1 4,-2 2,-1 2,5-5,1-3,0 1,-2 1,-1 1,-2 1,-1 1,0 0,-2 1,-4-5,-3-12,1-19,-4-15,0-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="52751.44">437 2242,'0'5,"0"8,0 6,6 5,1 4,-1 3,-1 1,-1 0,-1 1,-2-1,-1 0,0 0,0-1,0 0,0 1,-1-1,1-11,0-13,0-14,0-11,0-8,0-4,0-3,0-1,0 0,0 1,0 0,0 1,0 0,0 1,0 0,0 0,0 0,0 10,0 15,0 13,0 11,0 7,0 5,5-2,3-1,-2 0,0 1,-2 1,-2 0,0 2,-2 0,0 0,0 0,0 1,-1-1,1 0,0 0,0-10,0-15,0-12,-6-12,-1-8,0-4,2-3,1-6,1-2,2 1,1 2,0 7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53187.31">468 2428,'0'5,"0"8,0 6,0 5,0 5,5 2,3 1,-2 0,0 1,-2-1,-2 0,0-1,-2 1,0-1,0 0,0 0,-1 0,1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53409.62">406 2615,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53556.27">406 2615,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53748.15">406 2460,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="53968.89">406 2460,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56299.39">468 2553,'5'0,"3"0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56525.53">500 2553,'5'0,"2"0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56783.1">530 2553,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="56995.39">530 2553,'0'5,"0"7,0 2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57182.02">406 2740,'0'5,"0"7,0 7,0 6,0-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57333.77">406 2864,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57615.81">406 2647,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="57824.52">406 2553,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="58596.78">530 2553,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="59030.07">530 2553,'0'5,"0"7,0 8,0 4,0 5,0 1,0 2,0 1,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="59881.07">468 2397,'0'6,"0"6,0 7,0 5,0 5,0 1,0 2,0 1,0-1,0 1,0-1,0-1,0 1,0-1,0-11,0-13,0-14,0-11,0-7,0-6,0-2,0 0,0-1,0 0,0 12,0 15,0 13,0 12,0 7,0 5,0 3,0 1,0 5,0 2,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="71709.16">437 311,'0'6,"0"6,0 7,0 6,0 3,-5-2,-2-1,0 0,1 2,3 2,0 5,2 4,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="72696.81">406 591,'0'6,"0"6,0 7,0 6,0 9,0 9,0 2,0 0,0 7,0 17,0 6,0-3,0-5,0-2,0-1,0-2,0-6,0 4,0-3,0-2,0 2,0-4,0 5,0-3,0-4,0-7,0-4,0-5,-6-2,0-2,-1-1,-4 0,0 0,2 0,2 1,3-1,1 1,2 1,1-1,0 0,1 0,5-5,1-2,0 0,-1 2,-2 1,-1 2,-2 1,0 1,-1 0,4-5,3-2,-1 6,5 3,0 1,-2 0,-3 0,-1-1,-3 0,-1-1,0-12,-2-13,1-14,-1-16,1-26,0-9,0 0,-1 4,1 6,0 6,6 5,0 3,7 3,-1 0,-1 1,-3 0,2 0,0 0,-2-1,-3 0,-1 0,-2 0,-2 0,0 0,0 5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="73146.8">530 2117,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="84407.21">655 2522,'0'5,"0"8,5 6,2 5,0 4,-2 3,4-4,1-2,3-4,5-7,5-10,-1-11,-5-11,-6-6,-3-5,-5-3,-1-1,-2-1,-1 1,0 1,0 0,0 0,1 0,-1 1,1 0,0 0,0 5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="85986.07">562 2490,'0'6,"5"6,2 7,5 6,0 3,4 3,-1 1,-3-15,-4-17,-3-12,-2-10,-2-7,-1-4,0-1,-1 0,0 11,1 14,-1 15,6 5,2 7,0 6,-2-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="88608.04">530 1246,'6'-5,"6"-13,2-8,-2-5,-3-3,-2-1,-4 1,-1 0,-2 1,0 1,0 11,-1 14,1 14,-1 11,1 8,0 4,5-2,2-2,-1 2,0-11,-3-13,0-12,-2-10,0-8,-1-4,-1-3,1-1,0 1,0 0,-1 0,1 1,0 0,0 11,0 9</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="90727.68">562 468,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0 0,0-10,0-14,0-15,0-10,0-8,0-5,0-3,0 0,0-1,0 0,0 1,0 12,0 19,0 16,0 10,0 7,0 3,0 2,0-1,0-1,0-1,0 0,0-12,0-14,0-14,0-11,0-7,0-6,0-2,0 0,0-1,0 0,0 1,0 12,0 14,0 19,0 13,0 7,0-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="91174.88">530 343,'0'6,"0"6,0 7,0 5,0 5,0 1,0 2,0 1,0-1,0 1,0-2,0 1,0-1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="91668.37">530 468,'0'11,"0"8,0 7,0 4,0 2,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92104.94">406 343,'0'6,"0"6,0 7,5 0,2 2,0 3,4-3,0 1,-2 2,-3 1,4-2,0-1,-3 1,-1 3,-2 1,-2 3,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92470.19">468 654,'0'5,"0"13,0 8,0 6,0 1,0 2,0-1,0 5,0 1,0-1,0-2,0-2,0-1,0-2,0 0,0-1,0 0,0 0,0 5,0 2,0-1,0 0,0-3,0 0,0-2,0 0,0-1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92966.58">437 873,'0'5,"0"7,0 7,0 6,0 3,0 2,0 2,0 1,0-1,0 1,0-1,0-1,0 1,0-1,0 0,0 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="95623.56">406 2553,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="96899.44">623 2460,'0'5,"0"13,0 8,0 5,0 3,0 0,0 1,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="97296.62">623 2273,'0'5,"0"8,0 6,0 5,0 5,0 1,0 2,0 1,0-1,0 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="97729.07">623 2553,'0'5,"0"8,0 6,0 5,6 5,1-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="98098.4">593 2429,'0'5,"0"8,0 5,0 7,0-2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="105394.05">686 436,'0'6,"0"6,0 12,0 8,0 3,0 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="105956.56">655 499,'0'10,"0"10,0 6,0 3,0 4,0 0,0 0,0 0,0-1,0 0,0 0,0-1,0 1,0-1,0 0,0 0,0 0,0 0,0 0,0 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="106617.22">623 873,'0'5,"0"7,0 2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="107167.74">623 935,'0'5,"0"7,0 7,0 6,0 3,0 3,0 1,-5 0,-2 1,1-1,0 0,3 0,0-1,2-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="107727.99">593 1340,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="108095.9">530 1059,'0'5,"0"7,0 13,0 6,0 4,0 2,0-1,0-1,0-2,0 0,0-1,0-1,0 0,0 0,0 0,0 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="108531.29">530 1495,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="109241.78">530 1495,'0'5,"0"2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="111559.21">468 1215,'0'5,"0"8,0 6,0 5,0 4,0-2</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3418,67 +3824,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3501,14 +3907,14 @@
       <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3518,26 +3924,26 @@
       <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="68"/>
+      <c r="H13" s="76"/>
       <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="70"/>
-      <c r="K13" s="68"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="76"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="93"/>
-      <c r="H14" s="68"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="68"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="76"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="93"/>
-      <c r="H15" s="68"/>
+      <c r="H15" s="76"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="68"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="76"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3549,10 +3955,10 @@
       <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4566,19 +4972,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4590,192 +4996,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="60">
+      <c r="G2" s="89"/>
+      <c r="H2" s="92">
         <v>46176</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="64"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="91"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="71" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="72"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="71" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="72"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="71" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="72"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="92" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="72"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
     </row>
     <row r="10" spans="1:10" ht="209.25" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="67" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="92" t="s">
+      <c r="C10" s="76"/>
+      <c r="D10" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="72"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="67" t="s">
+      <c r="A11" s="79"/>
+      <c r="B11" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="92" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="72"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="71" t="s">
+      <c r="B12" s="59"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="72"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5766,6 +6172,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5774,25 +6199,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5814,16 +6220,16 @@
       <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5835,40 +6241,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8819,15 +9225,15 @@
         <v>120</v>
       </c>
       <c r="B1" s="100"/>
-      <c r="C1" s="152"/>
+      <c r="C1" s="166"/>
       <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="156"/>
+      <c r="E1" s="170"/>
       <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="156"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -8841,15 +9247,15 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="102"/>
       <c r="B2" s="103"/>
-      <c r="C2" s="143"/>
+      <c r="C2" s="146"/>
       <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="141"/>
+      <c r="E2" s="144"/>
       <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="141"/>
+      <c r="G2" s="144"/>
       <c r="H2" s="108">
         <v>46177</v>
       </c>
@@ -8861,68 +9267,68 @@
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="150"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="105"/>
       <c r="B4" s="106"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="151"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="165"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="160" t="s">
+      <c r="B5" s="168"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="171" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="162"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="173"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="158"/>
-      <c r="J6" s="163"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="134"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="164"/>
-      <c r="B7" s="165"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="165"/>
-      <c r="I7" s="165"/>
-      <c r="J7" s="166"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="102"/>
@@ -8941,10 +9347,10 @@
       <c r="B9" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="167" t="s">
+      <c r="C9" s="152" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="167"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="47" t="s">
         <v>115</v>
       </c>
@@ -8957,10 +9363,10 @@
       <c r="H9" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="167" t="s">
+      <c r="I9" s="152" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="168"/>
+      <c r="J9" s="153"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
@@ -9069,32 +9475,32 @@
       <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-      <c r="J16" s="163"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="134"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="157" t="s">
+      <c r="A17" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="158"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="169" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="170"/>
-      <c r="F17" s="170"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="171"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="138"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9103,11 +9509,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="157" t="s">
+      <c r="A18" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="158"/>
-      <c r="C18" s="159"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="135"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9120,11 +9526,11 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="172" t="s">
+      <c r="H18" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="158"/>
-      <c r="J18" s="163"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="134"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
@@ -9144,11 +9550,11 @@
       <c r="G19" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="173" t="s">
+      <c r="H19" s="143" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="133"/>
-      <c r="J19" s="134"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="142"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
@@ -9168,11 +9574,11 @@
       <c r="G20" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="132" t="s">
+      <c r="H20" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="133"/>
-      <c r="J20" s="134"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="142"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
@@ -9192,11 +9598,11 @@
       <c r="G21" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="132" t="s">
+      <c r="H21" s="140" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="133"/>
-      <c r="J21" s="134"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="142"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
@@ -9216,11 +9622,11 @@
       <c r="G22" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="132" t="s">
+      <c r="H22" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="133"/>
-      <c r="J22" s="134"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="142"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
@@ -9240,23 +9646,23 @@
       <c r="G23" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="132" t="s">
+      <c r="H23" s="140" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="142"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="136"/>
-      <c r="C24" s="137"/>
+      <c r="A24" s="154"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="156"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="140"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="158"/>
+      <c r="J24" s="159"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10237,33 +10643,6 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10280,6 +10659,33 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10299,182 +10705,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="52" t="s">
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52" t="s">
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="52" t="s">
+      <c r="P1" s="74"/>
+      <c r="Q1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="53"/>
-      <c r="S1" s="52" t="s">
+      <c r="R1" s="74"/>
+      <c r="S1" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="91"/>
+      <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="180"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="181"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="90"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="182"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="90" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="91"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="71" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="72"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="71" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="72"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10673,37 +11079,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="187" t="s">
+      <c r="B15" s="76"/>
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="174" t="s">
+      <c r="D15" s="76"/>
+      <c r="E15" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="174" t="s">
+      <c r="F15" s="76"/>
+      <c r="G15" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="70"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="174" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="68"/>
-      <c r="L15" s="174" t="s">
+      <c r="K15" s="76"/>
+      <c r="L15" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="174" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="68"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="76"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -10715,37 +11121,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="174">
         <v>1</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="186" t="s">
+      <c r="B16" s="76"/>
+      <c r="C16" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="76"/>
+      <c r="E16" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="175" t="s">
+      <c r="F16" s="76"/>
+      <c r="G16" s="182" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="175" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="177" t="s">
+      <c r="K16" s="76"/>
+      <c r="L16" s="178" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="177" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="178" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="68"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="76"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -10757,37 +11163,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="174">
         <v>2</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="186" t="s">
+      <c r="B17" s="76"/>
+      <c r="C17" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="186" t="s">
+      <c r="D17" s="76"/>
+      <c r="E17" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="175" t="s">
+      <c r="F17" s="76"/>
+      <c r="G17" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="175" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="182" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="68"/>
-      <c r="L17" s="177" t="s">
+      <c r="K17" s="76"/>
+      <c r="L17" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="177" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="178" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="68"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="76"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -10799,23 +11205,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="186"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="177"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="177"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="68"/>
+      <c r="A18" s="174"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="76"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -10827,23 +11233,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="177"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="177"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="68"/>
+      <c r="A19" s="174"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="76"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -10855,23 +11261,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="177"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="177"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="68"/>
+      <c r="A20" s="174"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="76"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -10883,23 +11289,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="177"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="68"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="76"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -10911,23 +11317,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="177"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="177"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="68"/>
+      <c r="A22" s="174"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="76"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -10939,23 +11345,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="177"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="177"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="68"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="76"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -10967,23 +11373,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="177"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="177"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="68"/>
+      <c r="A24" s="174"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="76"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -10995,23 +11401,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="177"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="68"/>
+      <c r="A25" s="174"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="76"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11023,23 +11429,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="68"/>
+      <c r="A26" s="174"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="76"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11051,23 +11457,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="177"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="68"/>
+      <c r="A27" s="174"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="76"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11079,23 +11485,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="68"/>
+      <c r="A28" s="174"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="175"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="76"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11107,23 +11513,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="177"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="68"/>
+      <c r="A29" s="174"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="76"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11135,23 +11541,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="177"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="68"/>
+      <c r="A30" s="174"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="76"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11163,23 +11569,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="188"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="75"/>
+      <c r="A31" s="176"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="63"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12177,6 +12583,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12201,118 +12719,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843C64D3-9A0C-467D-871A-733C7B2130EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC21C01-159C-4166-B097-BAB16FA75E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="1155" windowWidth="13260" windowHeight="9165" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="127">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -628,6 +628,47 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>任意項目がNULLだった場合空欄になる。メモ、期限項目は空欄可、その他は必須項目</t>
+    <rPh sb="0" eb="4">
+      <t>ニンイコウモク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>アドミン娘</t>
+    <rPh sb="4" eb="5">
+      <t>ムスメ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1582,189 +1623,330 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1795,15 +1977,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1813,140 +1989,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1954,47 +2028,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3203,8 +3244,8 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>168275</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="41" name="インク 40">
@@ -3223,7 +3264,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="41" name="インク 40">
@@ -3268,8 +3309,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>70991</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="128" name="インク 127">
@@ -3288,7 +3329,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="128" name="インク 127">
@@ -3333,8 +3374,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>268292</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="162" name="インク 161">
@@ -3353,7 +3394,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="162" name="インク 161">
@@ -3475,7 +3516,7 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7005.74">343 1276,'6'0,"6"0,2 6,-2 6,-3 12,3 3,-1 1,-3 6,-2 9,-2 7,-2 1,-1-4,4-4,1-4,0-3,-1-3,-1-2,-2 0,-1-1,-1 1,0-11,0-25,0-16,-1-16,1-7,0-6,0 0,0-2,0 2,0 0,0 2,0 5,0 4,0-2,0 0,0 3,0 2,5 7,3 14,-2 15,0 12,-2 10,-2 6,0 9,-2 4,0 0,0-2,0-2,-1-2,1 4,0 0,0-1,0-2,0-2,0-11,0-16,0-19,0-13,0-18,0-7,0-5,0 0,0 6,0-1,0-1,0-4,0 3,0 5,5-5,2 0,0 4,3 5,1 5,-2 3,-2-3,3 0,4 0,1 3,-3 1,2 1,4 6,-1 14,-3 18,-5 15,-3 9,-3 4,-2 3,-1 5,0 1,-1 4,0 0,0-3,1-4,0-2,0-3,0-2,0-1,0 5,0 1,0 6,0 0,0 4,0-2,0-2,0-3,0-4,0-2,-6-2,0-1,-6-1,-1 1,2-1,4 1,1 0,-2-5,0-18,1-16,2-16,2-10,1-5,6-5,9-7,1 1,3-3,0 4,-4-2,-4 4,-3 3,-3-5,-2-1,4 3,2 5,-1 3,4 4,0 2,-1 2,-3 0,4 1,5 5,-1 12,-1 14,-4 11,-3 16,-3 7,-2 14,-1 3,0 5,-1 7,1-1,-1-7,1 4,-1 2,1 1,0-5,0-2,0-5,0 0,0 6,0 0,0-6,0 0,0-3,0 0,0-3,0 2,0 4,0-2,0-4,0-4,0-4,0-14,0-16,0-14,0-11,0-14,0-6,0-7,0-2,0 3,0 2,0 4,0 3,0 2,0 2,0 0,0 0,0 1,0-1,0 1,0-1,0-5,0-3,0 1,0-3,0-1,0 1,0 4,0 1,0 3,0 0,0 2,0 0,0-5,0-1,0-1,0-9,0 9,0 21,0 19,0 20,0 16,0 8,0 5,0 1,0-4,0 6,0-1,0 1,0-3,0 0,0-4,0 2,-5 3,-2 2,1-1,-5-6,0-5,2-4,2-4,3-23,1-24,2-20,1-11,0-18,1-4,-1 4,0-4,1-1,-1 1,0-5,0 4,0 9,0 4,0-1,0 5,0-5,0 1,0-1,0 4,0 6,5 4,3 4,-2 4,0 1,-2 23,-2 23,0 14,-2 19,0 6,0 0,0 7,-1-2,1 5,0-3,0 0,0-7,0-5,0-1,0-4,0 3,0-3,0-2,0-3,0 2,0 0,0 4,0-1,-6-7,-1-5,0-2,2-1,1 1,-4-6,0-16,1-15,2-12,1-18,2-8,1-12,-5-1,-1 4,1 5,-5 7,1 5,1 4,3 2,2 2,1 0,-3-5,-2-2,2-6,-4-5,-1-1,-3 4,1 3,2 5,4 2,2 2,2 2,3 10,-1 16,2 34,-1 22,1 9,0 5,-1 1,0 0,0-5,0-9,0-2,0-4,0-5,0-4,0 3,0-1,0 4,0-1,-5 5,-2 3,0-1,1 2,2-2,2-5,1-4,0-4,1-13,0-16,1-14,-1-17,0-9,0-10,0-3,0-4,0-4,0-4,0 3,0 0,0 5,0-1,0 4,0 4,0 4,0 4,0 2,0 2,0 0,0 1,0-6,0-1,0-1,0 2,0 2,0 0,0-4,0 0,0-5,0-1,0 24,0 20,0 15,0 11,0 6,0 9,0 1,0 6,0-2,0 9,0-1,0 2,0-4,0 0,-5 2,-2-3,1 0,0 2,-3 3,0-3,-5 0,1 2,3-4,-3-4,1-6,-3 1,2-1,2-2,4-3,2-2,-2-7,-1-2,1-1,2 1,2-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8676.07">95 281,'5'0,"8"0,6 0,10 0,6 0,3 0,-1 0,-6-11,-3-3,-1 1,0 2,1-2,6 1,3 2,-5-1,2 0,-4-3,-2 1,-11 2,-14 4,-13 7,-9 5,-8 6,-3 7,-3 0,-1-2,0-5,6 1,3-1,-1-2,0-4,-2 9,0 2,-2-2,0-4,-1 3,-1-2,6 4,13-2,13-3,12-3,9-3,7-1,3-2,3-2,-1 1,-4-1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9347.22">126 249,'0'6,"0"6,5 2,7-2,8 2,4 0,4-4,3-2,1-4,0-2,1-1,-1-1,-5-1</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10045.05">220 374,'0'5,"0"8,5 0,7 5,7-2,0 3,2-3,3-4,8 1,4-1,-5 3,-1-2,-2-3,1-3,0-2,1-3,0-1,-5-1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10045.04">220 374,'0'5,"0"8,5 0,7 5,7-2,0 3,2-3,3-4,8 1,4-1,-5 3,-1-2,-2-3,1-3,0-2,1-3,0-1,-5-1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10697.19">343 468,'22'0,"11"0,6 0,2 0,-1 0,-2 0,-2 0,-2 0,-2 0,5 0,1 0,0 0,-2 0,-1 0,-2 0,-6 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11338.76">468 281,'5'0,"8"0,6 0,5 0,5 0,7 0,3 0,0 0,-1 0,-2 0,-7 0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="11872.58">63 249,'6'0,"6"0,7 0,6 0,3 6,3 1,1 0,0-2,1-1,4-2,2 0,-1-2,-1 0,-2 0,-1 0,-1-1,-2 1,-5 0</inkml:trace>
@@ -3506,35 +3547,35 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32041.31">500 63,'0'5,"0"8,0 5,0 12,0 5,0 3,0-1,0 0,0-3,0 0,0-1,0-2,0 1,0-2,0-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32297.02">468 1,'0'5,"0"7,0 7,0 6,0 3,0 2,0 2,0 1,0-1,0 1,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32569.68">468 281,'5'5,"3"7,4 7,0 6,4-2,-1 1,-3 1,-4 2,-3 1,-2-3</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32828.77">562 374,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32828.76">562 374,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33066.47">530 561,'0'5,"0"7,0 7,0 6,0 3,0 3,0 1,0 0,0 1,0-1,-5-5,-2-8</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33324.52">437 841,'0'5,"0"23,0 12,0 16,0 8,0-2,0 0,0-5,0-8,0-1,0-4,0-3,0-4,0-3,0-2,0-1,0 0,0-1,0 0,0-15,-5-22,-2-8</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33610.09">313 841,'0'5,"0"7,0 7,5 11,2 16,-1 6,0-1,-2-4,-2-5,-1-3,0-4,-1-3,-1-1,1 0,0-1,0 0,-1 1,1 0,0-1,0 1,0 1,0-1,0 0,0 0,0 0,0 0,0 0,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33324.51">437 841,'0'5,"0"23,0 12,0 16,0 8,0-2,0 0,0-5,0-8,0-1,0-4,0-3,0-4,0-3,0-2,0-1,0 0,0-1,0 0,0-15,-5-22,-2-8</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33610.08">313 841,'0'5,"0"7,0 7,5 11,2 16,-1 6,0-1,-2-4,-2-5,-1-3,0-4,-1-3,-1-1,1 0,0-1,0 0,-1 1,1 0,0-1,0 1,0 1,0-1,0 0,0 0,0 0,0 0,0 0,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33913.01">281 779,'0'5,"5"18,3 10,4 26,0 8,4 9,-1-3,2 1,-2-6,-3-10,-4-8,-3-4,-3 3,-1-4,-1 3,-1 3,6 4,1-3,1 1,-2-4,-1-4,-2-5,-1 1,0 0,-1-3,0-2,-1-2,1-2,0-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34200.13">343 1433,'0'10,"0"10,0 11,0 5,6 14,1 2,0-1,-2-5,4-10,1-6,-2-2,-3-1,-1 0,-2 1,5 1,0 0,0 2,-2 0,-2 0,-1 0,0 0,-2 1,0-1,0 0,-1-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34507.23">437 1743,'0'6,"0"6,0 7,0 11,0 5,0 3,0-1,6 5,1 0,-1-2,-1-2,-1-3,-1-1,3-2,2 0,-1-2,3-4,1-2,-2-1,-3 3,-2 1,-2 1,-1 2,-1 1,0-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34824.27">655 1775,'0'5,"0"8,0 5,0 7,0 9,0 3,0 7,0 1,0-2,0-3,0-3,0-2,0-2,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34200.12">343 1433,'0'10,"0"10,0 11,0 5,6 14,1 2,0-1,-2-5,4-10,1-6,-2-2,-3-1,-1 0,-2 1,5 1,0 0,0 2,-2 0,-2 0,-1 0,0 0,-2 1,0-1,0 0,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34507.22">437 1743,'0'6,"0"6,0 7,0 11,0 5,0 3,0-1,6 5,1 0,-1-2,-1-2,-1-3,-1-1,3-2,2 0,-1-2,3-4,1-2,-2-1,-3 3,-2 1,-2 1,-1 2,-1 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34824.26">655 1775,'0'5,"0"8,0 5,0 7,0 9,0 3,0 7,0 1,0-2,0-3,0-3,0-2,0-2,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35134.21">655 1962,'0'10,"0"10,0 5,0 5,0 2,0 1,0 0,0 1,0-2,0 0,0-11,0-9</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35467.2">623 1930,'0'6,"0"6,0 23,0 16,0 10,0-1,0 1,0-5,0-7,0-6,0-5,0-4,0-3,0 0,-5-7,-2-1,1 0,0-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35467.19">623 1930,'0'6,"0"6,0 23,0 16,0 10,0-1,0 1,0-5,0-7,0-6,0-5,0-4,0-3,0 0,-5-7,-2-1,1 0,0-3</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35753.54">530 1806,'0'10,"0"10,6 6,1 4,0 2,-2 1,-1 0,-1 0,-2-1,0 0,-1 0,-1-1,1 1,0-1,-1 0,1 0,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36042.39">530 2023,'0'11,"6"14,1 7,0 5,-2 1,-1-1,-1-1,3-7,2-3,-2-1,-1 1,-1 1,-2-4</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36299.26">500 2086,'0'10,"0"10,5 0,2 3,0 3,-2 1,-1 3,3-5,2-1,-2 1,-1 1,-3 2,0 1,-2 1,-1 1,0 0,-1 1,1-1,0 0,-1-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36299.25">500 2086,'0'10,"0"10,5 0,2 3,0 3,-2 1,-1 3,3-5,2-1,-2 1,-1 1,-3 2,0 1,-2 1,-1 1,0 0,-1 1,1-1,0 0,-1-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36587.83">500 2397,'0'6,"0"6,0 7,0 5,0-1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36941.98">500 2397,'0'6,"0"6,0 7,0 5,0-1</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37264.29">468 2428,'0'21,"0"18,0 7,0 2,0-3,0-3,0-4,5-8,3-4,-2-1,0 0,-2-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37264.28">468 2428,'0'21,"0"18,0 7,0 2,0-3,0-3,0-4,5-8,3-4,-2-1,0 0,-2-3</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37534.8">468 2522,'0'5,"0"8,0 6,0 5,0-1</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37821.52">437 2490,'6'0,"6"11,7 3,0 5,-3 4,-4 4,-5 2,-3 2,-2 1,-2 0,0-6</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="37821.51">437 2490,'6'0,"6"11,7 3,0 5,-3 4,-4 4,-5 2,-3 2,-2 1,-2 0,0-6</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38108.49">530 2428,'0'5,"0"8,0 6,0 5,0 5,0 2,0 1,0 0,0 1,0-1,0 0,0-6</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38383.85">437 2366,'0'5,"0"7,0 8,0 4,0 4,0 3,0 1,0-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38670.06">437 2522,'6'11,"6"8,2 7,-2 4,-3 2,3 1,-2 0,4 0,-1-1,-2 0,-4 0,-3-1,4-5,0-2,-2 1,-1-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38943.58">593 2677,'0'0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39315.7">593 2490,'0'6,"0"11,0 10,0 4,0 3,0 0,0 1,0-2,0 0,0-1,0 5,0 2,0-1,0-2,0-1,0-18,0-16,0-14,0-10,0-7,0 2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39315.69">593 2490,'0'6,"0"11,0 10,0 4,0 3,0 0,0 1,0-2,0 0,0-1,0 5,0 2,0-1,0-2,0-1,0-18,0-16,0-14,0-10,0-7,0 2</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39642.17">530 2460,'0'10,"0"15,0 8,0 3,0 2,0-1,0 4,0 0,0-1,0-3,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39873.51">468 2335,'0'5,"0"8,0 5,0 7,5 3,3 3,-2 1,0 1,-2-1,-2 0,0 0,-2 0,0-6</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40100.86">500 2490,'0'0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40339.01">500 2366,'0'10,"5"10,7 6,2 4,-2 2,3-4,-2-2,-3 0,-3 1,-2 2,2-6,1 1,-2 0,-1 1,-2-3</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40582.01">562 2428,'0'0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40835.73">562 2428,'0'5,"0"13,0 8,0 6,0-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40835.72">562 2428,'0'5,"0"13,0 8,0 6,0-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41137.85">500 2180,'0'5,"0"7,0 7,0 6,0 3,0 3,0 0,0 2,0-1,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41501.88">343 1993,'0'5,"6"7,1 7,5 6,0 3,-1 3,2 1,5-5,-2-2,-2 6,0 3,0 0,-4 1,-4-2,-2 1,-2-2,-1 0,-2-1,1 0,-1 0,1 0,-1 0,1-10,0-20,0-15,0-16,0-8,0-3,0 6</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41819.55">500 1962,'0'10,"5"10,2 11,5 11,6-2,-1-1,-2-4,-5-1,-3-1,2-2,-1 0,4-1,0 1,-2 0,-3-1,-2 1,-3 0,-1 1,-1-1,0 0,0 0,-1 0,1 0,-1-10,1-14,0-14,0-6</inkml:trace>
@@ -3579,11 +3620,11 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="90727.68">562 468,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0 0,0-10,0-14,0-15,0-10,0-8,0-5,0-3,0 0,0-1,0 0,0 1,0 12,0 19,0 16,0 10,0 7,0 3,0 2,0-1,0-1,0-1,0 0,0-12,0-14,0-14,0-11,0-7,0-6,0-2,0 0,0-1,0 0,0 1,0 12,0 14,0 19,0 13,0 7,0-2</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="91174.88">530 343,'0'6,"0"6,0 7,0 5,0 5,0 1,0 2,0 1,0-1,0 1,0-2,0 1,0-1,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="91668.37">530 468,'0'11,"0"8,0 7,0 4,0 2,0-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92104.94">406 343,'0'6,"0"6,0 7,5 0,2 2,0 3,4-3,0 1,-2 2,-3 1,4-2,0-1,-3 1,-1 3,-2 1,-2 3,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92104.93">406 343,'0'6,"0"6,0 7,5 0,2 2,0 3,4-3,0 1,-2 2,-3 1,4-2,0-1,-3 1,-1 3,-2 1,-2 3,-1-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92470.19">468 654,'0'5,"0"13,0 8,0 6,0 1,0 2,0-1,0 5,0 1,0-1,0-2,0-2,0-1,0-2,0 0,0-1,0 0,0 0,0 5,0 2,0-1,0 0,0-3,0 0,0-2,0 0,0-1,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="92966.58">437 873,'0'5,"0"7,0 7,0 6,0 3,0 2,0 2,0 1,0-1,0 1,0-1,0-1,0 1,0-1,0 0,0 0,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="95623.56">406 2553,'0'0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="96899.44">623 2460,'0'5,"0"13,0 8,0 5,0 3,0 0,0 1,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="96899.43">623 2460,'0'5,"0"13,0 8,0 5,0 3,0 0,0 1,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="97296.62">623 2273,'0'5,"0"8,0 6,0 5,0 5,0 1,0 2,0 1,0-1,0 0,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="97729.07">623 2553,'0'5,"0"8,0 6,0 5,6 5,1-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="98098.4">593 2429,'0'5,"0"8,0 5,0 7,0-2</inkml:trace>
@@ -3806,85 +3847,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="113"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3904,46 +3945,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="93" t="s">
+      <c r="G13" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="76"/>
-      <c r="I13" s="93" t="s">
+      <c r="H13" s="111"/>
+      <c r="I13" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="76"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="111"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="93"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="76"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="111"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="93"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="76"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="111"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3952,13 +3993,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="94" t="s">
+      <c r="G17" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4972,19 +5013,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="118"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="118"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4996,192 +5037,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="88" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88" t="s">
+      <c r="E2" s="120"/>
+      <c r="F2" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="92">
+      <c r="G2" s="120"/>
+      <c r="H2" s="125">
         <v>46176</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="130"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="86"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="55" t="s">
+      <c r="B5" s="146"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="153"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="134" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="135"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="134" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="133" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="58" t="s">
+      <c r="B8" s="110"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="134" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="60"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="135"/>
     </row>
     <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="147" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="61" t="s">
+      <c r="C9" s="111"/>
+      <c r="D9" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="135"/>
     </row>
     <row r="10" spans="1:10" ht="209.25" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="80" t="s">
+      <c r="A10" s="148"/>
+      <c r="B10" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="61" t="s">
+      <c r="C10" s="111"/>
+      <c r="D10" s="154" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="60"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="135"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="80" t="s">
+      <c r="A11" s="149"/>
+      <c r="B11" s="132" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="61" t="s">
+      <c r="C11" s="111"/>
+      <c r="D11" s="154" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="135"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="58" t="s">
+      <c r="B12" s="110"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="135"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="150" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="151"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6172,17 +6215,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -6191,14 +6231,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6217,19 +6260,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="87" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="87" t="s">
+      <c r="E1" s="118"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="118"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6241,40 +6284,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="142"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="130"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="86"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7631,19 +7674,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="123" t="s">
+      <c r="B1" s="162"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="124"/>
-      <c r="F1" s="123" t="s">
+      <c r="E1" s="170"/>
+      <c r="F1" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="124"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -7655,564 +7698,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="117"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="125" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="126"/>
-      <c r="F2" s="125" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="126"/>
-      <c r="H2" s="108">
+      <c r="G2" s="171"/>
+      <c r="H2" s="70">
         <v>46177</v>
       </c>
-      <c r="I2" s="111" t="s">
+      <c r="I2" s="73" t="s">
         <v>119</v>
       </c>
-      <c r="J2" s="112"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="113"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="160"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="120"/>
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="161"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="99"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="101"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="156"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="104"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="98"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="98"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="102"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="104"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="102"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="102"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="104"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="102"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="102"/>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="104"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="98"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="102"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="104"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="102"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="104"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="98"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="104"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="98"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="104"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="98"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="104"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="98"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="104"/>
+      <c r="A20" s="82"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="98"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="104"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="98"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="104"/>
+      <c r="A22" s="82"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="104"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="98"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="104"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="98"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="98"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="104"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="98"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="104"/>
+      <c r="A27" s="82"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="98"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="103"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="104"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="98"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="103"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="104"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="98"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="103"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="103"/>
-      <c r="J30" s="104"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="98"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="103"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="104"/>
+      <c r="A31" s="82"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="98"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="102"/>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="104"/>
+      <c r="A32" s="82"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="98"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="102"/>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="104"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="98"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="102"/>
-      <c r="B34" s="103"/>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="104"/>
+      <c r="A34" s="82"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="98"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="102"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="104"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="98"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="102"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="103"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="104"/>
+      <c r="A36" s="82"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="98"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="102"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="104"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="98"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="102"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="104"/>
+      <c r="A38" s="82"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="98"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="102"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="103"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="103"/>
-      <c r="J39" s="104"/>
+      <c r="A39" s="82"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="98"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="102"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
-      <c r="I40" s="103"/>
-      <c r="J40" s="104"/>
+      <c r="A40" s="82"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="98"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="102"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="103"/>
-      <c r="D41" s="103"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="103"/>
-      <c r="I41" s="103"/>
-      <c r="J41" s="104"/>
+      <c r="A41" s="82"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="98"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="102"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="103"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="103"/>
-      <c r="J42" s="104"/>
+      <c r="A42" s="82"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="98"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="102"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="103"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="103"/>
-      <c r="H43" s="103"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="104"/>
+      <c r="A43" s="82"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="98"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="102"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="103"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="103"/>
-      <c r="J44" s="104"/>
+      <c r="A44" s="82"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="98"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="102"/>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="104"/>
+      <c r="A45" s="82"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="98"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="102"/>
-      <c r="B46" s="103"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="103"/>
-      <c r="J46" s="104"/>
+      <c r="A46" s="82"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="98"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="105"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="106"/>
-      <c r="D47" s="106"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="106"/>
-      <c r="G47" s="106"/>
-      <c r="H47" s="106"/>
-      <c r="I47" s="106"/>
-      <c r="J47" s="107"/>
+      <c r="A47" s="84"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
+      <c r="I47" s="85"/>
+      <c r="J47" s="157"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
@@ -9221,19 +9264,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="123" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="123" t="s">
+      <c r="E1" s="90"/>
+      <c r="F1" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="90"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -9245,112 +9288,112 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="125" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="144"/>
-      <c r="F2" s="125" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="108">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>46177</v>
       </c>
-      <c r="I2" s="111" t="s">
+      <c r="I2" s="73" t="s">
         <v>119</v>
       </c>
-      <c r="J2" s="112"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="164"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="105"/>
-      <c r="B4" s="106"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="165"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="171" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="94" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="173"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="97"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="98"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="152" t="s">
+      <c r="C9" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="152"/>
+      <c r="D9" s="102"/>
       <c r="E9" s="47" t="s">
         <v>115</v>
       </c>
@@ -9363,20 +9406,20 @@
       <c r="H9" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="152" t="s">
+      <c r="I9" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="153"/>
+      <c r="J9" s="103"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="83" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="103"/>
+      <c r="D10" s="83"/>
       <c r="E10" s="42" t="s">
         <v>108</v>
       </c>
@@ -9389,20 +9432,20 @@
       <c r="H10" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="103" t="s">
+      <c r="I10" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="J10" s="104"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="103"/>
+      <c r="D11" s="83"/>
       <c r="E11" s="42" t="s">
         <v>104</v>
       </c>
@@ -9410,97 +9453,97 @@
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="H11" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="I11" s="103" t="s">
+      <c r="I11" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="104"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="104"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="104"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="98"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="44"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="43"/>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="104"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="132" t="s">
+      <c r="A16" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="97"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="136" t="s">
+      <c r="B17" s="92"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="138"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="106"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9509,11 +9552,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="132" t="s">
+      <c r="A18" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="133"/>
-      <c r="C18" s="135"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9526,18 +9569,18 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="139" t="s">
+      <c r="H18" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="134"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A19" s="129" t="s">
+      <c r="A19" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="130"/>
-      <c r="C19" s="131"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="36" t="s">
         <v>96</v>
       </c>
@@ -9550,18 +9593,18 @@
       <c r="G19" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="143" t="s">
+      <c r="H19" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="141"/>
-      <c r="J19" s="142"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="57"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="129" t="s">
+      <c r="A20" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="130"/>
-      <c r="C20" s="131"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="36" t="s">
         <v>91</v>
       </c>
@@ -9574,18 +9617,18 @@
       <c r="G20" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="140" t="s">
+      <c r="H20" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="141"/>
-      <c r="J20" s="142"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="129" t="s">
+      <c r="A21" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="130"/>
-      <c r="C21" s="131"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="36" t="s">
         <v>85</v>
       </c>
@@ -9598,18 +9641,18 @@
       <c r="G21" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="140" t="s">
+      <c r="H21" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="57"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="130"/>
-      <c r="C22" s="131"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="36" t="s">
         <v>81</v>
       </c>
@@ -9622,18 +9665,18 @@
       <c r="G22" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="140" t="s">
+      <c r="H22" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="141"/>
-      <c r="J22" s="142"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="129" t="s">
+      <c r="A23" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="130"/>
-      <c r="C23" s="131"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="37" t="s">
         <v>77</v>
       </c>
@@ -9646,23 +9689,23 @@
       <c r="G23" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="140" t="s">
+      <c r="H23" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="141"/>
-      <c r="J23" s="142"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="154"/>
-      <c r="B24" s="155"/>
-      <c r="C24" s="156"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="60"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="159"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="63"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10643,6 +10686,33 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10659,33 +10729,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10705,182 +10748,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="87" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="87" t="s">
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="87" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="87" t="s">
+      <c r="P1" s="118"/>
+      <c r="Q1" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="74"/>
-      <c r="S1" s="87" t="s">
+      <c r="R1" s="118"/>
+      <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="57"/>
+      <c r="T1" s="153"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="186"/>
+      <c r="A2" s="142"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="180"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="187"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="181"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="188"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="182"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="55" t="s">
+      <c r="B5" s="146"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="57"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
+      <c r="R5" s="146"/>
+      <c r="S5" s="146"/>
+      <c r="T5" s="153"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="58" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="60"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="110"/>
+      <c r="T6" s="135"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="58" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="60"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="135"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11079,37 +11122,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="76"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="183" t="s">
+      <c r="D15" s="111"/>
+      <c r="E15" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="76"/>
-      <c r="G15" s="183" t="s">
+      <c r="F15" s="111"/>
+      <c r="G15" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="183" t="s">
+      <c r="H15" s="110"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="76"/>
-      <c r="L15" s="183" t="s">
+      <c r="K15" s="111"/>
+      <c r="L15" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="183" t="s">
+      <c r="M15" s="110"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="76"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="111"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -11121,37 +11164,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="174">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="175" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="175" t="s">
+      <c r="D16" s="111"/>
+      <c r="E16" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="76"/>
-      <c r="G16" s="182" t="s">
+      <c r="F16" s="111"/>
+      <c r="G16" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="182" t="s">
+      <c r="H16" s="110"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="76"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="111"/>
+      <c r="L16" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="110"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="76"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="111"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -11163,37 +11206,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="174">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="175" t="s">
+      <c r="B17" s="111"/>
+      <c r="C17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="175" t="s">
+      <c r="D17" s="111"/>
+      <c r="E17" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="76"/>
-      <c r="G17" s="182" t="s">
+      <c r="F17" s="111"/>
+      <c r="G17" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="182" t="s">
+      <c r="H17" s="110"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="76"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="111"/>
+      <c r="L17" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="110"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="76"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="111"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -11205,23 +11248,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="174"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="76"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="111"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -11233,23 +11276,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="174"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="76"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="111"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -11261,23 +11304,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="174"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="182"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="76"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="111"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -11289,23 +11332,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="76"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="110"/>
+      <c r="Q21" s="111"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -11317,23 +11360,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="174"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="76"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="186"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="111"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -11345,23 +11388,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="174"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="76"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="110"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="110"/>
+      <c r="Q23" s="111"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -11373,23 +11416,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="174"/>
-      <c r="B24" s="76"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="76"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="111"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11401,23 +11444,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="76"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="110"/>
+      <c r="Q25" s="111"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11429,23 +11472,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="174"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="76"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="76"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="111"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11457,23 +11500,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="174"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="76"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="111"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="110"/>
+      <c r="Q27" s="111"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11485,23 +11528,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="76"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="76"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="110"/>
+      <c r="Q28" s="111"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11513,23 +11556,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="76"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="76"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="110"/>
+      <c r="Q29" s="111"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11541,23 +11584,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="174"/>
-      <c r="B30" s="76"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="76"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="111"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11569,23 +11612,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="63"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="137"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="137"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="137"/>
+      <c r="Q31" s="138"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12583,62 +12626,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12663,62 +12706,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC21C01-159C-4166-B097-BAB16FA75E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5CBCB7-A46D-4343-A1E0-AA1FAFED2ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="1155" windowWidth="13260" windowHeight="9165" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -249,19 +249,6 @@
       <t>イチラン</t>
     </rPh>
     <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>登録されているタスク一覧を表示する</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -580,10 +567,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>登録済みタスクの一覧、または「登録されているタスクはありません。」というメッセージが表示される</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>E1:データベース接続に失敗した場合。
 E1-1.基本フロー2でシステムはデータベース接続に失敗する。
 E1-2.システムはエラーメッセージを表示する。
@@ -595,35 +578,6 @@
       <t>ガメン</t>
     </rPh>
     <rPh sb="94" eb="96">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">A1:タスク情報が存在しない場合
-A1-1:基本フロー2でシステムはタスク情報が0件であることを確認する。
-A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
-A2:メモ、期限の任意項目が未入力の場合
-A2-1:基本フロー5でシステムが任意項目の値を確認する。
-A2-2:システムが任意項目がNULLであることを確認する。
-A2-3:システムが空文字を設定する。
-A2-4:システムが一覧表示画面の任意項目で空文字を表示する。
-</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
-2.システムがデータベースからタスク情報を取得する。
-3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
-4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
-5:システムがログイン中のユーザIDとタスクの担当者IDを比較する
-6:担当者IDがログイン中のユーザIDと一致したら該当タスクにラジオボタンを表示する。
-7. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
-</t>
-    <rPh sb="180" eb="182">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="193" eb="195">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -666,6 +620,124 @@
     <t>アドミン娘</t>
     <rPh sb="4" eb="5">
       <t>ムスメ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
+2.システムがデータベースからタスク情報を取得する。
+3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
+4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
+5:システムがログイン中のユーザIDとタスクの担当者IDを比較する
+6:担当者IDがログイン中のユーザIDと一致したら該当タスクにラジオボタンを表示する。
+7. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+8.従業員はタスクを選択し削除ボタンか編集ボタンを押下する
+9.削除画面か編集画面へ遷移する
+</t>
+    <rPh sb="180" eb="182">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="193" eb="195">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="255" eb="258">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="263" eb="265">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="266" eb="268">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="272" eb="274">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="278" eb="280">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="285" eb="289">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="290" eb="294">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="295" eb="297">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>登録されているタスク一覧を表示、自身のタスクを選択し編集画面か削除画面へ遷移</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A1:タスク情報が存在しない場合
+A1-1:基本フロー2でシステムはタスク情報が0件であることを確認する。
+A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
+A2:メモ、期限の任意項目が未入力の場合
+A2-1:基本フロー5でシステムが任意項目の値を確認する。
+A2-2:システムが任意項目がNULLであることを確認する。
+A2-3:システムが空文字を設定する。
+A2-4:システムが一覧表示画面の任意項目で空文字を表示する。
+A1:タスク未選択で削除ボタン押下した場合
+A1-1:基本フロー8でシステムはタスク未選択を検出する
+A1-2:システムは一覧画面を再表示する
+A1-3:システムは「削除するタスクを選択してください。」と表示する
+A1:タスク未選択で編集ボタン押下した場合
+A1-1:基本フロー8でシステムはタスク未選択を検出する
+A1-2:システムは一覧画面を再表示する
+A1-3:システムは「編集するタスクを選択してください。」と表示する
+</t>
+    <rPh sb="354" eb="356">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="427" eb="429">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">登録済みタスクの一覧の表示、または「登録されているタスクはありません。」というメッセージが表示される
+削除、編集画面への遷移
+</t>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="54" eb="58">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1632,6 +1704,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1641,6 +1740,48 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1659,24 +1800,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1713,12 +1836,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1740,15 +1857,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1758,42 +1866,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1818,12 +1890,105 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1833,105 +1998,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1989,53 +2061,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2057,20 +2129,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9134758" cy="6144490"/>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>858280</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>147638</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98F04DD4-F1C8-4514-9156-A6E561798A8D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6260464A-8B5C-4062-084B-260BFFC6F2E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2092,8 +2169,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="895351"/>
-          <a:ext cx="9134758" cy="6144490"/>
+          <a:off x="0" y="1190625"/>
+          <a:ext cx="8573530" cy="5910263"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2101,7 +2178,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3547,16 +3624,16 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32041.31">500 63,'0'5,"0"8,0 5,0 12,0 5,0 3,0-1,0 0,0-3,0 0,0-1,0-2,0 1,0-2,0-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32297.02">468 1,'0'5,"0"7,0 7,0 6,0 3,0 2,0 2,0 1,0-1,0 1,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32569.68">468 281,'5'5,"3"7,4 7,0 6,4-2,-1 1,-3 1,-4 2,-3 1,-2-3</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32828.76">562 374,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="32828.75">562 374,'0'5,"0"8,0 6,0 5,0 4,0 3,0 1,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33066.47">530 561,'0'5,"0"7,0 7,0 6,0 3,0 3,0 1,0 0,0 1,0-1,-5-5,-2-8</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33324.51">437 841,'0'5,"0"23,0 12,0 16,0 8,0-2,0 0,0-5,0-8,0-1,0-4,0-3,0-4,0-3,0-2,0-1,0 0,0-1,0 0,0-15,-5-22,-2-8</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33610.08">313 841,'0'5,"0"7,0 7,5 11,2 16,-1 6,0-1,-2-4,-2-5,-1-3,0-4,-1-3,-1-1,1 0,0-1,0 0,-1 1,1 0,0-1,0 1,0 1,0-1,0 0,0 0,0 0,0 0,0 0,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="33913.01">281 779,'0'5,"5"18,3 10,4 26,0 8,4 9,-1-3,2 1,-2-6,-3-10,-4-8,-3-4,-3 3,-1-4,-1 3,-1 3,6 4,1-3,1 1,-2-4,-1-4,-2-5,-1 1,0 0,-1-3,0-2,-1-2,1-2,0-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34200.12">343 1433,'0'10,"0"10,0 11,0 5,6 14,1 2,0-1,-2-5,4-10,1-6,-2-2,-3-1,-1 0,-2 1,5 1,0 0,0 2,-2 0,-2 0,-1 0,0 0,-2 1,0-1,0 0,-1-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34507.22">437 1743,'0'6,"0"6,0 7,0 11,0 5,0 3,0-1,6 5,1 0,-1-2,-1-2,-1-3,-1-1,3-2,2 0,-1-2,3-4,1-2,-2-1,-3 3,-2 1,-2 1,-1 2,-1 1,0-5</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34824.26">655 1775,'0'5,"0"8,0 5,0 7,0 9,0 3,0 7,0 1,0-2,0-3,0-3,0-2,0-2,0-7</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34200.11">343 1433,'0'10,"0"10,0 11,0 5,6 14,1 2,0-1,-2-5,4-10,1-6,-2-2,-3-1,-1 0,-2 1,5 1,0 0,0 2,-2 0,-2 0,-1 0,0 0,-2 1,0-1,0 0,-1-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34507.21">437 1743,'0'6,"0"6,0 7,0 11,0 5,0 3,0-1,6 5,1 0,-1-2,-1-2,-1-3,-1-1,3-2,2 0,-1-2,3-4,1-2,-2-1,-3 3,-2 1,-2 1,-1 2,-1 1,0-5</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="34824.25">655 1775,'0'5,"0"8,0 5,0 7,0 9,0 3,0 7,0 1,0-2,0-3,0-3,0-2,0-2,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35134.21">655 1962,'0'10,"0"10,0 5,0 5,0 2,0 1,0 0,0 1,0-2,0 0,0-11,0-9</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35467.19">623 1930,'0'6,"0"6,0 23,0 16,0 10,0-1,0 1,0-5,0-7,0-6,0-5,0-4,0-3,0 0,-5-7,-2-1,1 0,0-3</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35467.18">623 1930,'0'6,"0"6,0 23,0 16,0 10,0-1,0 1,0-5,0-7,0-6,0-5,0-4,0-3,0 0,-5-7,-2-1,1 0,0-3</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="35753.54">530 1806,'0'10,"0"10,6 6,1 4,0 2,-2 1,-1 0,-1 0,-2-1,0 0,-1 0,-1-1,1 1,0-1,-1 0,1 0,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36042.39">530 2023,'0'11,"6"14,1 7,0 5,-2 1,-1-1,-1-1,3-7,2-3,-2-1,-1 1,-1 1,-2-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="36299.25">500 2086,'0'10,"0"10,5 0,2 3,0 3,-2 1,-1 3,3-5,2-1,-2 1,-1 1,-3 2,0 1,-2 1,-1 1,0 0,-1 1,1-1,0 0,-1-4</inkml:trace>
@@ -3569,13 +3646,13 @@
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38383.85">437 2366,'0'5,"0"7,0 8,0 4,0 4,0 3,0 1,0-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38670.06">437 2522,'6'11,"6"8,2 7,-2 4,-3 2,3 1,-2 0,4 0,-1-1,-2 0,-4 0,-3-1,4-5,0-2,-2 1,-1-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="38943.58">593 2677,'0'0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39315.69">593 2490,'0'6,"0"11,0 10,0 4,0 3,0 0,0 1,0-2,0 0,0-1,0 5,0 2,0-1,0-2,0-1,0-18,0-16,0-14,0-10,0-7,0 2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39315.68">593 2490,'0'6,"0"11,0 10,0 4,0 3,0 0,0 1,0-2,0 0,0-1,0 5,0 2,0-1,0-2,0-1,0-18,0-16,0-14,0-10,0-7,0 2</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39642.17">530 2460,'0'10,"0"15,0 8,0 3,0 2,0-1,0 4,0 0,0-1,0-3,0-7</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39873.51">468 2335,'0'5,"0"8,0 5,0 7,5 3,3 3,-2 1,0 1,-2-1,-2 0,0 0,-2 0,0-6</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40100.86">500 2490,'0'0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40339.01">500 2366,'0'10,"5"10,7 6,2 4,-2 2,3-4,-2-2,-3 0,-3 1,-2 2,2-6,1 1,-2 0,-1 1,-2-3</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40582.01">562 2428,'0'0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40835.72">562 2428,'0'5,"0"13,0 8,0 6,0-4</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40835.71">562 2428,'0'5,"0"13,0 8,0 6,0-4</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41137.85">500 2180,'0'5,"0"7,0 7,0 6,0 3,0 3,0 0,0 2,0-1,0-5</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41501.88">343 1993,'0'5,"6"7,1 7,5 6,0 3,-1 3,2 1,5-5,-2-2,-2 6,0 3,0 0,-4 1,-4-2,-2 1,-2-2,-1 0,-2-1,1 0,-1 0,1 0,-1 0,1-10,0-20,0-15,0-16,0-8,0-3,0 6</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41819.55">500 1962,'0'10,"5"10,2 11,5 11,6-2,-1-1,-2-4,-5-1,-3-1,2-2,-1 0,4-1,0 1,-2 0,-3-1,-2 1,-3 0,-1 1,-1-1,0 0,0 0,-1 0,1 0,-1-10,1-14,0-14,0-6</inkml:trace>
@@ -5013,19 +5090,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="137"/>
+      <c r="F1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="118"/>
+      <c r="G1" s="137"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -5037,194 +5114,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
+      <c r="A2" s="131"/>
       <c r="B2" s="113"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="119" t="s">
+      <c r="C2" s="132"/>
+      <c r="D2" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="120"/>
-      <c r="F2" s="119" t="s">
+      <c r="E2" s="151"/>
+      <c r="F2" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="120"/>
-      <c r="H2" s="125">
+      <c r="G2" s="151"/>
+      <c r="H2" s="154">
         <v>46176</v>
       </c>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="129"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
+      <c r="A3" s="131"/>
       <c r="B3" s="113"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="130"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="147"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="148"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="146"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="152" t="s">
+      <c r="B5" s="121"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="146"/>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="153"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="122"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="138" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="110"/>
       <c r="C6" s="111"/>
-      <c r="D6" s="134" t="s">
-        <v>70</v>
+      <c r="D6" s="123" t="s">
+        <v>124</v>
       </c>
       <c r="E6" s="110"/>
       <c r="F6" s="110"/>
       <c r="G6" s="110"/>
       <c r="H6" s="110"/>
       <c r="I6" s="110"/>
-      <c r="J6" s="135"/>
+      <c r="J6" s="124"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="138" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="110"/>
       <c r="C7" s="111"/>
-      <c r="D7" s="134" t="s">
-        <v>71</v>
+      <c r="D7" s="123" t="s">
+        <v>70</v>
       </c>
       <c r="E7" s="110"/>
       <c r="F7" s="110"/>
       <c r="G7" s="110"/>
       <c r="H7" s="110"/>
       <c r="I7" s="110"/>
-      <c r="J7" s="135"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="138" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="110"/>
       <c r="C8" s="111"/>
-      <c r="D8" s="134" t="s">
-        <v>72</v>
+      <c r="D8" s="123" t="s">
+        <v>71</v>
       </c>
       <c r="E8" s="110"/>
       <c r="F8" s="110"/>
       <c r="G8" s="110"/>
       <c r="H8" s="110"/>
       <c r="I8" s="110"/>
-      <c r="J8" s="135"/>
+      <c r="J8" s="124"/>
     </row>
     <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="147" t="s">
+      <c r="A9" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="142" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="111"/>
-      <c r="D9" s="154" t="s">
-        <v>124</v>
+      <c r="D9" s="125" t="s">
+        <v>123</v>
       </c>
       <c r="E9" s="110"/>
       <c r="F9" s="110"/>
       <c r="G9" s="110"/>
       <c r="H9" s="110"/>
       <c r="I9" s="110"/>
-      <c r="J9" s="135"/>
-    </row>
-    <row r="10" spans="1:10" ht="209.25" customHeight="1">
-      <c r="A10" s="148"/>
-      <c r="B10" s="132" t="s">
+      <c r="J9" s="124"/>
+    </row>
+    <row r="10" spans="1:10" ht="309" customHeight="1">
+      <c r="A10" s="140"/>
+      <c r="B10" s="142" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="111"/>
-      <c r="D10" s="154" t="s">
-        <v>123</v>
+      <c r="D10" s="125" t="s">
+        <v>125</v>
       </c>
       <c r="E10" s="110"/>
       <c r="F10" s="110"/>
       <c r="G10" s="110"/>
       <c r="H10" s="110"/>
       <c r="I10" s="110"/>
-      <c r="J10" s="135"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="149"/>
-      <c r="B11" s="132" t="s">
+      <c r="A11" s="141"/>
+      <c r="B11" s="142" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="111"/>
-      <c r="D11" s="154" t="s">
-        <v>122</v>
+      <c r="D11" s="125" t="s">
+        <v>120</v>
       </c>
       <c r="E11" s="110"/>
       <c r="F11" s="110"/>
       <c r="G11" s="110"/>
       <c r="H11" s="110"/>
       <c r="I11" s="110"/>
-      <c r="J11" s="135"/>
+      <c r="J11" s="124"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="133" t="s">
+      <c r="A12" s="138" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="110"/>
       <c r="C12" s="111"/>
-      <c r="D12" s="134" t="s">
-        <v>121</v>
+      <c r="D12" s="125" t="s">
+        <v>126</v>
       </c>
       <c r="E12" s="110"/>
       <c r="F12" s="110"/>
       <c r="G12" s="110"/>
       <c r="H12" s="110"/>
       <c r="I12" s="110"/>
-      <c r="J12" s="135"/>
+      <c r="J12" s="124"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="136" t="s">
+      <c r="A13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="150" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="151"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="117" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="119"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6215,6 +6292,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -6223,25 +6319,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6263,16 +6340,16 @@
       <c r="A1" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="137"/>
+      <c r="F1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="118"/>
+      <c r="G1" s="137"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6284,40 +6361,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
+      <c r="A2" s="131"/>
       <c r="B2" s="113"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="129"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
+      <c r="A3" s="131"/>
       <c r="B3" s="113"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="130"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="147"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="148"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7674,16 +7751,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="96" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="163"/>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="104" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="170"/>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="104" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="170"/>
@@ -7701,21 +7778,21 @@
       <c r="A2" s="164"/>
       <c r="B2" s="165"/>
       <c r="C2" s="166"/>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="69" t="s">
         <v>68</v>
       </c>
       <c r="E2" s="171"/>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="69" t="s">
         <v>66</v>
       </c>
       <c r="G2" s="171"/>
-      <c r="H2" s="70">
+      <c r="H2" s="87">
         <v>46177</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="J2" s="76"/>
+      <c r="I2" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="J2" s="93"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="164"/>
@@ -7742,519 +7819,519 @@
       <c r="J4" s="161"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="79"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
+      <c r="A5" s="96"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
       <c r="J5" s="156"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="82"/>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="98"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="98"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="82"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="98"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="82"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="98"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="67"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="82"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="98"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="98"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="98"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="98"/>
+      <c r="A13" s="78"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="67"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="82"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="98"/>
+      <c r="A14" s="78"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="82"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="98"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="67"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="98"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="82"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="98"/>
+      <c r="A17" s="78"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="98"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="82"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="98"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="82"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="98"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="98"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="82"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="98"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="82"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="98"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="67"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="82"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="98"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="67"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="82"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="98"/>
+      <c r="A25" s="78"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="67"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="82"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="98"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="67"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="82"/>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="98"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="67"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="82"/>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="98"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="67"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="82"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="98"/>
+      <c r="A29" s="78"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="67"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="82"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="98"/>
+      <c r="A30" s="78"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="67"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="82"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="98"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="67"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="82"/>
-      <c r="B32" s="83"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="98"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="67"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="82"/>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="98"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="67"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="82"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="98"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="67"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="82"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="98"/>
+      <c r="A35" s="78"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="67"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="82"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="98"/>
+      <c r="A36" s="78"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="67"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="82"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="98"/>
+      <c r="A37" s="78"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="67"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="82"/>
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="98"/>
+      <c r="A38" s="78"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="67"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="82"/>
-      <c r="B39" s="83"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="98"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="67"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="82"/>
-      <c r="B40" s="83"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="98"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="67"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="82"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="98"/>
+      <c r="A41" s="78"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="67"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="82"/>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="98"/>
+      <c r="A42" s="78"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="67"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="82"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="98"/>
+      <c r="A43" s="78"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="67"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="82"/>
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="98"/>
+      <c r="A44" s="78"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="67"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="82"/>
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="98"/>
+      <c r="A45" s="78"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="67"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="82"/>
-      <c r="B46" s="83"/>
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="98"/>
+      <c r="A46" s="78"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="67"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="84"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
+      <c r="A47" s="99"/>
+      <c r="B47" s="100"/>
+      <c r="C47" s="100"/>
+      <c r="D47" s="100"/>
+      <c r="E47" s="100"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="100"/>
+      <c r="H47" s="100"/>
+      <c r="I47" s="100"/>
       <c r="J47" s="157"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9264,19 +9341,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="89" t="s">
+      <c r="A1" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="89" t="s">
+      <c r="E1" s="105"/>
+      <c r="F1" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="90"/>
+      <c r="G1" s="105"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -9288,275 +9365,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="70"/>
+      <c r="F2" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="70">
+      <c r="G2" s="70"/>
+      <c r="H2" s="87">
         <v>46177</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="J2" s="76"/>
+      <c r="I2" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="J2" s="93"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="82"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="84"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="95"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="96"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="106" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="108"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="97"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="101"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="77"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="82"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="98"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="102"/>
+      <c r="C9" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="79"/>
       <c r="E9" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="I9" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="J9" s="103"/>
+      <c r="I9" s="79" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" s="80"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="83" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="83"/>
+      <c r="C10" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="55"/>
       <c r="E10" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F10" s="46">
         <v>46203</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="I10" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="J10" s="98"/>
+      <c r="I10" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="83"/>
+        <v>99</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="55"/>
       <c r="E11" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F11" s="46">
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="98"/>
+      <c r="I11" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
+        <v>99</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="98"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
+        <v>99</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="98"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="67"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
+        <v>99</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="98"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="44"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="43"/>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="98"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="67"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="92"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="92"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="97"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="104" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="106"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="62"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9569,143 +9646,143 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="107" t="s">
+      <c r="H18" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="92"/>
-      <c r="J18" s="97"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="53"/>
       <c r="C19" s="54"/>
       <c r="D19" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
+      <c r="H19" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="I19" s="65"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="53"/>
       <c r="C20" s="54"/>
       <c r="D20" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
+      <c r="H20" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="65"/>
+      <c r="J20" s="66"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="53"/>
       <c r="C21" s="54"/>
       <c r="D21" s="36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="56"/>
-      <c r="J21" s="57"/>
+      <c r="H21" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="65"/>
+      <c r="J21" s="66"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="53"/>
       <c r="C22" s="54"/>
       <c r="D22" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
+      <c r="H22" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" s="65"/>
+      <c r="J22" s="66"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="53"/>
       <c r="C23" s="54"/>
       <c r="D23" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
+      <c r="H23" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="58"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="60"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="63"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="86"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10686,33 +10763,6 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10729,6 +10779,33 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10748,133 +10825,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="128" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="117" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="117" t="s">
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="117" t="s">
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="117" t="s">
+      <c r="P1" s="137"/>
+      <c r="Q1" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="118"/>
-      <c r="S1" s="117" t="s">
+      <c r="R1" s="137"/>
+      <c r="S1" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="153"/>
+      <c r="T1" s="122"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
+      <c r="A2" s="131"/>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
       <c r="D2" s="113"/>
       <c r="E2" s="113"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="180"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="150"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="150"/>
+      <c r="R2" s="151"/>
+      <c r="S2" s="150"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
+      <c r="A3" s="131"/>
       <c r="B3" s="113"/>
       <c r="C3" s="113"/>
       <c r="D3" s="113"/>
       <c r="E3" s="113"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="121"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="152"/>
       <c r="H3" s="113"/>
       <c r="I3" s="113"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="121"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="152"/>
       <c r="L3" s="113"/>
       <c r="M3" s="113"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="121"/>
-      <c r="T3" s="181"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="152"/>
+      <c r="P3" s="132"/>
+      <c r="Q3" s="152"/>
+      <c r="R3" s="132"/>
+      <c r="S3" s="152"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="144"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="144"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="144"/>
-      <c r="M4" s="144"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="123"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="123"/>
-      <c r="T4" s="182"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="153"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="153"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="153"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="153"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="146"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="146"/>
-      <c r="E5" s="146"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="152" t="s">
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="146"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
-      <c r="R5" s="146"/>
-      <c r="S5" s="146"/>
-      <c r="T5" s="153"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="121"/>
+      <c r="S5" s="121"/>
+      <c r="T5" s="122"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="181" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="110"/>
@@ -10882,7 +10959,7 @@
       <c r="D6" s="110"/>
       <c r="E6" s="110"/>
       <c r="F6" s="111"/>
-      <c r="G6" s="134" t="s">
+      <c r="G6" s="123" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="110"/>
@@ -10897,10 +10974,10 @@
       <c r="Q6" s="110"/>
       <c r="R6" s="110"/>
       <c r="S6" s="110"/>
-      <c r="T6" s="135"/>
+      <c r="T6" s="124"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="181" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="110"/>
@@ -10908,7 +10985,7 @@
       <c r="D7" s="110"/>
       <c r="E7" s="110"/>
       <c r="F7" s="111"/>
-      <c r="G7" s="134" t="s">
+      <c r="G7" s="123" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="110"/>
@@ -10923,7 +11000,7 @@
       <c r="Q7" s="110"/>
       <c r="R7" s="110"/>
       <c r="S7" s="110"/>
-      <c r="T7" s="135"/>
+      <c r="T7" s="124"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11122,33 +11199,33 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="181" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="111"/>
-      <c r="C15" s="187" t="s">
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="111"/>
-      <c r="E15" s="174" t="s">
+      <c r="E15" s="183" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="111"/>
-      <c r="G15" s="174" t="s">
+      <c r="G15" s="183" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="110"/>
       <c r="I15" s="111"/>
-      <c r="J15" s="174" t="s">
+      <c r="J15" s="183" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="111"/>
-      <c r="L15" s="174" t="s">
+      <c r="L15" s="183" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="110"/>
       <c r="N15" s="111"/>
-      <c r="O15" s="174" t="s">
+      <c r="O15" s="183" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="110"/>
@@ -11164,33 +11241,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="174">
         <v>1</v>
       </c>
       <c r="B16" s="111"/>
-      <c r="C16" s="186" t="s">
+      <c r="C16" s="175" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="111"/>
-      <c r="E16" s="186" t="s">
+      <c r="E16" s="175" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="111"/>
-      <c r="G16" s="175" t="s">
+      <c r="G16" s="182" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="110"/>
       <c r="I16" s="111"/>
-      <c r="J16" s="175" t="s">
+      <c r="J16" s="182" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="111"/>
-      <c r="L16" s="177" t="s">
+      <c r="L16" s="178" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="110"/>
       <c r="N16" s="111"/>
-      <c r="O16" s="177" t="s">
+      <c r="O16" s="178" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="110"/>
@@ -11206,33 +11283,33 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="174">
         <v>2</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="175" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="111"/>
-      <c r="E17" s="186" t="s">
+      <c r="E17" s="175" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="111"/>
-      <c r="G17" s="175" t="s">
+      <c r="G17" s="182" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="110"/>
       <c r="I17" s="111"/>
-      <c r="J17" s="175" t="s">
+      <c r="J17" s="182" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="111"/>
-      <c r="L17" s="177" t="s">
+      <c r="L17" s="178" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="110"/>
       <c r="N17" s="111"/>
-      <c r="O17" s="177" t="s">
+      <c r="O17" s="178" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="110"/>
@@ -11248,21 +11325,21 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
+      <c r="A18" s="174"/>
       <c r="B18" s="111"/>
-      <c r="C18" s="186"/>
+      <c r="C18" s="175"/>
       <c r="D18" s="111"/>
-      <c r="E18" s="186"/>
+      <c r="E18" s="175"/>
       <c r="F18" s="111"/>
-      <c r="G18" s="175"/>
+      <c r="G18" s="182"/>
       <c r="H18" s="110"/>
       <c r="I18" s="111"/>
-      <c r="J18" s="175"/>
+      <c r="J18" s="182"/>
       <c r="K18" s="111"/>
-      <c r="L18" s="177"/>
+      <c r="L18" s="178"/>
       <c r="M18" s="110"/>
       <c r="N18" s="111"/>
-      <c r="O18" s="177"/>
+      <c r="O18" s="178"/>
       <c r="P18" s="110"/>
       <c r="Q18" s="111"/>
       <c r="R18" s="27"/>
@@ -11276,21 +11353,21 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
+      <c r="A19" s="174"/>
       <c r="B19" s="111"/>
-      <c r="C19" s="186"/>
+      <c r="C19" s="175"/>
       <c r="D19" s="111"/>
-      <c r="E19" s="186"/>
+      <c r="E19" s="175"/>
       <c r="F19" s="111"/>
-      <c r="G19" s="175"/>
+      <c r="G19" s="182"/>
       <c r="H19" s="110"/>
       <c r="I19" s="111"/>
-      <c r="J19" s="175"/>
+      <c r="J19" s="182"/>
       <c r="K19" s="111"/>
-      <c r="L19" s="177"/>
+      <c r="L19" s="178"/>
       <c r="M19" s="110"/>
       <c r="N19" s="111"/>
-      <c r="O19" s="177"/>
+      <c r="O19" s="178"/>
       <c r="P19" s="110"/>
       <c r="Q19" s="111"/>
       <c r="R19" s="27"/>
@@ -11304,21 +11381,21 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
+      <c r="A20" s="174"/>
       <c r="B20" s="111"/>
-      <c r="C20" s="186"/>
+      <c r="C20" s="175"/>
       <c r="D20" s="111"/>
-      <c r="E20" s="186"/>
+      <c r="E20" s="175"/>
       <c r="F20" s="111"/>
-      <c r="G20" s="175"/>
+      <c r="G20" s="182"/>
       <c r="H20" s="110"/>
       <c r="I20" s="111"/>
-      <c r="J20" s="175"/>
+      <c r="J20" s="182"/>
       <c r="K20" s="111"/>
-      <c r="L20" s="177"/>
+      <c r="L20" s="178"/>
       <c r="M20" s="110"/>
       <c r="N20" s="111"/>
-      <c r="O20" s="177"/>
+      <c r="O20" s="178"/>
       <c r="P20" s="110"/>
       <c r="Q20" s="111"/>
       <c r="R20" s="27"/>
@@ -11332,21 +11409,21 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
+      <c r="A21" s="174"/>
       <c r="B21" s="111"/>
-      <c r="C21" s="186"/>
+      <c r="C21" s="175"/>
       <c r="D21" s="111"/>
-      <c r="E21" s="186"/>
+      <c r="E21" s="175"/>
       <c r="F21" s="111"/>
-      <c r="G21" s="175"/>
+      <c r="G21" s="182"/>
       <c r="H21" s="110"/>
       <c r="I21" s="111"/>
-      <c r="J21" s="175"/>
+      <c r="J21" s="182"/>
       <c r="K21" s="111"/>
-      <c r="L21" s="177"/>
+      <c r="L21" s="178"/>
       <c r="M21" s="110"/>
       <c r="N21" s="111"/>
-      <c r="O21" s="177"/>
+      <c r="O21" s="178"/>
       <c r="P21" s="110"/>
       <c r="Q21" s="111"/>
       <c r="R21" s="27"/>
@@ -11360,21 +11437,21 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
+      <c r="A22" s="174"/>
       <c r="B22" s="111"/>
-      <c r="C22" s="186"/>
+      <c r="C22" s="175"/>
       <c r="D22" s="111"/>
-      <c r="E22" s="186"/>
+      <c r="E22" s="175"/>
       <c r="F22" s="111"/>
-      <c r="G22" s="175"/>
+      <c r="G22" s="182"/>
       <c r="H22" s="110"/>
       <c r="I22" s="111"/>
-      <c r="J22" s="175"/>
+      <c r="J22" s="182"/>
       <c r="K22" s="111"/>
-      <c r="L22" s="177"/>
+      <c r="L22" s="178"/>
       <c r="M22" s="110"/>
       <c r="N22" s="111"/>
-      <c r="O22" s="177"/>
+      <c r="O22" s="178"/>
       <c r="P22" s="110"/>
       <c r="Q22" s="111"/>
       <c r="R22" s="27"/>
@@ -11388,21 +11465,21 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
+      <c r="A23" s="174"/>
       <c r="B23" s="111"/>
-      <c r="C23" s="186"/>
+      <c r="C23" s="175"/>
       <c r="D23" s="111"/>
-      <c r="E23" s="186"/>
+      <c r="E23" s="175"/>
       <c r="F23" s="111"/>
-      <c r="G23" s="175"/>
+      <c r="G23" s="182"/>
       <c r="H23" s="110"/>
       <c r="I23" s="111"/>
-      <c r="J23" s="175"/>
+      <c r="J23" s="182"/>
       <c r="K23" s="111"/>
-      <c r="L23" s="177"/>
+      <c r="L23" s="178"/>
       <c r="M23" s="110"/>
       <c r="N23" s="111"/>
-      <c r="O23" s="177"/>
+      <c r="O23" s="178"/>
       <c r="P23" s="110"/>
       <c r="Q23" s="111"/>
       <c r="R23" s="27"/>
@@ -11416,21 +11493,21 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
+      <c r="A24" s="174"/>
       <c r="B24" s="111"/>
-      <c r="C24" s="186"/>
+      <c r="C24" s="175"/>
       <c r="D24" s="111"/>
-      <c r="E24" s="186"/>
+      <c r="E24" s="175"/>
       <c r="F24" s="111"/>
-      <c r="G24" s="175"/>
+      <c r="G24" s="182"/>
       <c r="H24" s="110"/>
       <c r="I24" s="111"/>
-      <c r="J24" s="175"/>
+      <c r="J24" s="182"/>
       <c r="K24" s="111"/>
-      <c r="L24" s="177"/>
+      <c r="L24" s="178"/>
       <c r="M24" s="110"/>
       <c r="N24" s="111"/>
-      <c r="O24" s="177"/>
+      <c r="O24" s="178"/>
       <c r="P24" s="110"/>
       <c r="Q24" s="111"/>
       <c r="R24" s="27"/>
@@ -11444,21 +11521,21 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
+      <c r="A25" s="174"/>
       <c r="B25" s="111"/>
-      <c r="C25" s="186"/>
+      <c r="C25" s="175"/>
       <c r="D25" s="111"/>
-      <c r="E25" s="186"/>
+      <c r="E25" s="175"/>
       <c r="F25" s="111"/>
-      <c r="G25" s="175"/>
+      <c r="G25" s="182"/>
       <c r="H25" s="110"/>
       <c r="I25" s="111"/>
-      <c r="J25" s="175"/>
+      <c r="J25" s="182"/>
       <c r="K25" s="111"/>
-      <c r="L25" s="177"/>
+      <c r="L25" s="178"/>
       <c r="M25" s="110"/>
       <c r="N25" s="111"/>
-      <c r="O25" s="177"/>
+      <c r="O25" s="178"/>
       <c r="P25" s="110"/>
       <c r="Q25" s="111"/>
       <c r="R25" s="27"/>
@@ -11472,21 +11549,21 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
+      <c r="A26" s="174"/>
       <c r="B26" s="111"/>
-      <c r="C26" s="186"/>
+      <c r="C26" s="175"/>
       <c r="D26" s="111"/>
-      <c r="E26" s="186"/>
+      <c r="E26" s="175"/>
       <c r="F26" s="111"/>
-      <c r="G26" s="175"/>
+      <c r="G26" s="182"/>
       <c r="H26" s="110"/>
       <c r="I26" s="111"/>
-      <c r="J26" s="175"/>
+      <c r="J26" s="182"/>
       <c r="K26" s="111"/>
-      <c r="L26" s="177"/>
+      <c r="L26" s="178"/>
       <c r="M26" s="110"/>
       <c r="N26" s="111"/>
-      <c r="O26" s="177"/>
+      <c r="O26" s="178"/>
       <c r="P26" s="110"/>
       <c r="Q26" s="111"/>
       <c r="R26" s="27"/>
@@ -11500,21 +11577,21 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
+      <c r="A27" s="174"/>
       <c r="B27" s="111"/>
-      <c r="C27" s="186"/>
+      <c r="C27" s="175"/>
       <c r="D27" s="111"/>
-      <c r="E27" s="186"/>
+      <c r="E27" s="175"/>
       <c r="F27" s="111"/>
-      <c r="G27" s="175"/>
+      <c r="G27" s="182"/>
       <c r="H27" s="110"/>
       <c r="I27" s="111"/>
-      <c r="J27" s="175"/>
+      <c r="J27" s="182"/>
       <c r="K27" s="111"/>
-      <c r="L27" s="177"/>
+      <c r="L27" s="178"/>
       <c r="M27" s="110"/>
       <c r="N27" s="111"/>
-      <c r="O27" s="177"/>
+      <c r="O27" s="178"/>
       <c r="P27" s="110"/>
       <c r="Q27" s="111"/>
       <c r="R27" s="27"/>
@@ -11528,21 +11605,21 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
+      <c r="A28" s="174"/>
       <c r="B28" s="111"/>
-      <c r="C28" s="186"/>
+      <c r="C28" s="175"/>
       <c r="D28" s="111"/>
-      <c r="E28" s="186"/>
+      <c r="E28" s="175"/>
       <c r="F28" s="111"/>
-      <c r="G28" s="175"/>
+      <c r="G28" s="182"/>
       <c r="H28" s="110"/>
       <c r="I28" s="111"/>
-      <c r="J28" s="175"/>
+      <c r="J28" s="182"/>
       <c r="K28" s="111"/>
-      <c r="L28" s="177"/>
+      <c r="L28" s="178"/>
       <c r="M28" s="110"/>
       <c r="N28" s="111"/>
-      <c r="O28" s="177"/>
+      <c r="O28" s="178"/>
       <c r="P28" s="110"/>
       <c r="Q28" s="111"/>
       <c r="R28" s="27"/>
@@ -11556,21 +11633,21 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
+      <c r="A29" s="174"/>
       <c r="B29" s="111"/>
-      <c r="C29" s="186"/>
+      <c r="C29" s="175"/>
       <c r="D29" s="111"/>
-      <c r="E29" s="186"/>
+      <c r="E29" s="175"/>
       <c r="F29" s="111"/>
-      <c r="G29" s="175"/>
+      <c r="G29" s="182"/>
       <c r="H29" s="110"/>
       <c r="I29" s="111"/>
-      <c r="J29" s="175"/>
+      <c r="J29" s="182"/>
       <c r="K29" s="111"/>
-      <c r="L29" s="177"/>
+      <c r="L29" s="178"/>
       <c r="M29" s="110"/>
       <c r="N29" s="111"/>
-      <c r="O29" s="177"/>
+      <c r="O29" s="178"/>
       <c r="P29" s="110"/>
       <c r="Q29" s="111"/>
       <c r="R29" s="27"/>
@@ -11584,21 +11661,21 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
+      <c r="A30" s="174"/>
       <c r="B30" s="111"/>
-      <c r="C30" s="186"/>
+      <c r="C30" s="175"/>
       <c r="D30" s="111"/>
-      <c r="E30" s="186"/>
+      <c r="E30" s="175"/>
       <c r="F30" s="111"/>
-      <c r="G30" s="175"/>
+      <c r="G30" s="182"/>
       <c r="H30" s="110"/>
       <c r="I30" s="111"/>
-      <c r="J30" s="175"/>
+      <c r="J30" s="182"/>
       <c r="K30" s="111"/>
-      <c r="L30" s="177"/>
+      <c r="L30" s="178"/>
       <c r="M30" s="110"/>
       <c r="N30" s="111"/>
-      <c r="O30" s="177"/>
+      <c r="O30" s="178"/>
       <c r="P30" s="110"/>
       <c r="Q30" s="111"/>
       <c r="R30" s="27"/>
@@ -11612,23 +11689,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="188"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="137"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="137"/>
-      <c r="Q31" s="138"/>
+      <c r="A31" s="176"/>
+      <c r="B31" s="127"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="127"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="127"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="127"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="118"/>
+      <c r="Q31" s="127"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12626,6 +12703,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12650,118 +12839,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5CBCB7-A46D-4343-A1E0-AA1FAFED2ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5F031A-7E07-4362-900B-A8C425623207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -307,13 +307,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>選択したテーブルの削除画面に遷移する</t>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>削除</t>
     <rPh sb="0" eb="2">
       <t>サクジョ</t>
@@ -332,19 +325,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>選択したテーブルの編集画面に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>ヘンシュウガメン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>編集</t>
     <rPh sb="0" eb="2">
       <t>ヘンシュウ</t>
@@ -360,22 +340,6 @@
   </si>
   <si>
     <t>③</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>選択したレコードに登録、削除機能を使用する</t>
-    <rPh sb="0" eb="2">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>サクジョキノウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シヨウ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -624,49 +588,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
-2.システムがデータベースからタスク情報を取得する。
-3. システムがカテゴリ情報・担当者情報・ステータス情報を取得する。
-4. システムがカテゴリ名・担当者名・ステータス名へ変換する。
-5:システムがログイン中のユーザIDとタスクの担当者IDを比較する
-6:担当者IDがログイン中のユーザIDと一致したら該当タスクにラジオボタンを表示する。
-7. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
-8.従業員はタスクを選択し削除ボタンか編集ボタンを押下する
-9.削除画面か編集画面へ遷移する
-</t>
-    <rPh sb="180" eb="182">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="193" eb="195">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="255" eb="258">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="263" eb="265">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="266" eb="268">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="272" eb="274">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="278" eb="280">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="285" eb="289">
-      <t>サクジョガメン</t>
-    </rPh>
-    <rPh sb="290" eb="294">
-      <t>ヘンシュウガメン</t>
-    </rPh>
-    <rPh sb="295" eb="297">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>登録されているタスク一覧を表示、自身のタスクを選択し編集画面か削除画面へ遷移</t>
     <rPh sb="0" eb="2">
       <t>トウロク</t>
@@ -738,6 +659,81 @@
     </rPh>
     <rPh sb="60" eb="62">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
+2.システムがデータベースからタスク情報を取得する。
+3:システムがログイン中のユーザIDとタスクの担当者IDを比較する。
+6:担当者IDがログイン中のユーザIDと一致したら該当タスクにラジオボタンを表示する。
+7. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+8.従業員はラジオボタンを選択する。
+8.従業員は削除ボタンか編集ボタンを押下する。
+9.削除画面か編集画面へ遷移する。
+</t>
+    <rPh sb="114" eb="116">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="189" eb="192">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="208" eb="211">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="217" eb="219">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="224" eb="228">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="230" eb="234">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクに登録、削除機能を使用する</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>サクジョキノウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクの編集画面に遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>選択したタスクの削除画面に遷移する</t>
+    <rPh sb="8" eb="10">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1695,6 +1691,237 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1704,7 +1931,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1713,10 +2012,34 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1732,334 +2055,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2067,47 +2096,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3924,85 +3920,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="113"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4022,46 +4018,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="116" t="s">
+      <c r="E8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="113"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="109" t="s">
+      <c r="G13" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="111"/>
-      <c r="I13" s="109" t="s">
+      <c r="H13" s="68"/>
+      <c r="I13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="110"/>
-      <c r="K13" s="111"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="109"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="111"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="109"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="111"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4070,13 +4066,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="112" t="s">
+      <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="80"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5090,19 +5086,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="149" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="149" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -5114,194 +5110,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="150" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="154">
+      <c r="G2" s="55"/>
+      <c r="H2" s="60">
         <v>46176</v>
       </c>
-      <c r="I2" s="143" t="s">
+      <c r="I2" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="146"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="147"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="120" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="122"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="91"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="138" t="s">
+      <c r="A6" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="123" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="124"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="138" t="s">
+      <c r="A7" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="123" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="124"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="110"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="123" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="124"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="125" t="s">
+      <c r="C9" s="68"/>
+      <c r="D9" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="124"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="309" customHeight="1">
-      <c r="A10" s="140"/>
-      <c r="B10" s="142" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="125" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="124"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="141"/>
-      <c r="B11" s="142" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="125" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="124"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="125" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="124"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="118"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="117" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="119"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6292,17 +6288,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -6311,14 +6304,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6337,19 +6333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="149" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="149" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="137"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6361,40 +6357,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="146"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="147"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7751,19 +7747,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="104" t="s">
+      <c r="B1" s="115"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="124"/>
+      <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="124"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -7775,564 +7771,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="117"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="171"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="126"/>
+      <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="87">
+      <c r="G2" s="126"/>
+      <c r="H2" s="108">
         <v>46177</v>
       </c>
-      <c r="I2" s="90" t="s">
-        <v>118</v>
-      </c>
-      <c r="J2" s="93"/>
+      <c r="I2" s="111" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="160"/>
+      <c r="A3" s="117"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="167"/>
-      <c r="B4" s="168"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="161"/>
+      <c r="A4" s="120"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="96"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="156"/>
+      <c r="A5" s="99"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="78"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="67"/>
+      <c r="A6" s="102"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="78"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="67"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="67"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="67"/>
+      <c r="A9" s="102"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="104"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="67"/>
+      <c r="A10" s="102"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="67"/>
+      <c r="A11" s="102"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="78"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="67"/>
+      <c r="A12" s="102"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="78"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="67"/>
+      <c r="A13" s="102"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="78"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="67"/>
+      <c r="A14" s="102"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="78"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="67"/>
+      <c r="A15" s="102"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="78"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="67"/>
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="104"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="78"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="67"/>
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="104"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="67"/>
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="104"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="78"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="67"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="104"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="78"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="67"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="104"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="78"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="67"/>
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="104"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="78"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="67"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="104"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="78"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="67"/>
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="104"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="78"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="67"/>
+      <c r="A24" s="102"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="104"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="78"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="67"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="104"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="78"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="67"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="104"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="78"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="67"/>
+      <c r="A27" s="102"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="104"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="78"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="67"/>
+      <c r="A28" s="102"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="103"/>
+      <c r="J28" s="104"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="78"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="67"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="104"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="78"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="67"/>
+      <c r="A30" s="102"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="103"/>
+      <c r="J30" s="104"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="78"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="67"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="104"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="78"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="67"/>
+      <c r="A32" s="102"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="104"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="78"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="67"/>
+      <c r="A33" s="102"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="104"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="78"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="67"/>
+      <c r="A34" s="102"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="104"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="78"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="67"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="104"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="78"/>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="67"/>
+      <c r="A36" s="102"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="104"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="78"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="67"/>
+      <c r="A37" s="102"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="104"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="78"/>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="67"/>
+      <c r="A38" s="102"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="104"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="78"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="67"/>
+      <c r="A39" s="102"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="104"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="78"/>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="67"/>
+      <c r="A40" s="102"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="104"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="78"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="67"/>
+      <c r="A41" s="102"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="103"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="103"/>
+      <c r="J41" s="104"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="78"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="67"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="104"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="78"/>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="67"/>
+      <c r="A43" s="102"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="104"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="78"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="67"/>
+      <c r="A44" s="102"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="103"/>
+      <c r="J44" s="104"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="78"/>
-      <c r="B45" s="55"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="67"/>
+      <c r="A45" s="102"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="103"/>
+      <c r="J45" s="104"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="78"/>
-      <c r="B46" s="55"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="67"/>
+      <c r="A46" s="102"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="103"/>
+      <c r="J46" s="104"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="99"/>
-      <c r="B47" s="100"/>
-      <c r="C47" s="100"/>
-      <c r="D47" s="100"/>
-      <c r="E47" s="100"/>
-      <c r="F47" s="100"/>
-      <c r="G47" s="100"/>
-      <c r="H47" s="100"/>
-      <c r="I47" s="100"/>
-      <c r="J47" s="157"/>
+      <c r="A47" s="105"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="106"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="106"/>
+      <c r="I47" s="106"/>
+      <c r="J47" s="107"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
@@ -9341,19 +9337,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="104" t="s">
+      <c r="A1" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="100"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="105"/>
-      <c r="F1" s="104" t="s">
+      <c r="E1" s="156"/>
+      <c r="F1" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="105"/>
+      <c r="G1" s="156"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -9365,275 +9361,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="141"/>
+      <c r="F2" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="87">
+      <c r="G2" s="141"/>
+      <c r="H2" s="108">
         <v>46177</v>
       </c>
-      <c r="I2" s="90" t="s">
-        <v>118</v>
-      </c>
-      <c r="J2" s="93"/>
+      <c r="I2" s="111" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="99"/>
-      <c r="B4" s="100"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="95"/>
+      <c r="A4" s="105"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="151"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="106" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="108"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="160" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="162"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="58"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="163"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="75"/>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="77"/>
+      <c r="A7" s="164"/>
+      <c r="B7" s="165"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="166"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="67"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="79"/>
+        <v>113</v>
+      </c>
+      <c r="C9" s="167" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="167"/>
       <c r="E9" s="47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="79" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="80"/>
+        <v>108</v>
+      </c>
+      <c r="I9" s="167" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="168"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="55"/>
+        <v>106</v>
+      </c>
+      <c r="C10" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="103"/>
       <c r="E10" s="42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F10" s="46">
         <v>46203</v>
       </c>
       <c r="G10" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="H10" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I10" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="J10" s="67"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="55"/>
+        <v>96</v>
+      </c>
+      <c r="C11" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="103"/>
       <c r="E11" s="42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F11" s="46">
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="J11" s="67"/>
+        <v>98</v>
+      </c>
+      <c r="I11" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
+        <v>96</v>
+      </c>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
+        <v>96</v>
+      </c>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="67"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
+        <v>96</v>
+      </c>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="44"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
       <c r="E15" s="43"/>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="67"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="58"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="163"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="62"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="169" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="170"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="59"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9646,68 +9642,68 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="63" t="s">
+      <c r="H18" s="172" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="57"/>
-      <c r="J18" s="58"/>
+      <c r="I18" s="158"/>
+      <c r="J18" s="163"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A19" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
+      <c r="A19" s="129" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="130"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F19" s="36" t="s">
         <v>74</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="65"/>
-      <c r="J19" s="66"/>
+        <v>90</v>
+      </c>
+      <c r="H19" s="173" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="133"/>
+      <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
+      <c r="A20" s="129" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="130"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" s="65"/>
-      <c r="J20" s="66"/>
+        <v>84</v>
+      </c>
+      <c r="H20" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="133"/>
+      <c r="J20" s="134"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="54"/>
+      <c r="A21" s="129" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="130"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E21" s="36" t="s">
         <v>75</v>
@@ -9716,22 +9712,22 @@
         <v>74</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="65"/>
-      <c r="J21" s="66"/>
+        <v>81</v>
+      </c>
+      <c r="H21" s="132" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="133"/>
+      <c r="J21" s="134"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
+      <c r="A22" s="129" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="130"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="36" t="s">
         <v>75</v>
@@ -9740,20 +9736,20 @@
         <v>74</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="66"/>
+      <c r="H22" s="132" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="133"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="54"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="37" t="s">
         <v>76</v>
       </c>
@@ -9766,23 +9762,23 @@
       <c r="G23" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="64" t="s">
+      <c r="H23" s="132" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="134"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="81"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="83"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="137"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="86"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="140"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10763,6 +10759,33 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10779,33 +10802,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10825,182 +10821,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="149" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="149" t="s">
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="149" t="s">
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="149" t="s">
+      <c r="P1" s="53"/>
+      <c r="Q1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="137"/>
-      <c r="S1" s="149" t="s">
+      <c r="R1" s="53"/>
+      <c r="S1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="122"/>
+      <c r="T1" s="91"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="131"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="150"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="150"/>
-      <c r="R2" s="151"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="186"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="180"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="152"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="152"/>
-      <c r="R3" s="132"/>
-      <c r="S3" s="152"/>
-      <c r="T3" s="187"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="181"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="133"/>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="153"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="153"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="153"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="153"/>
-      <c r="T4" s="188"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="182"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="120" t="s">
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="121"/>
-      <c r="T5" s="122"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="91"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="123" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="110"/>
-      <c r="S6" s="110"/>
-      <c r="T6" s="124"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="123" t="s">
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="110"/>
-      <c r="T7" s="124"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="72"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11199,37 +11195,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="68"/>
+      <c r="C15" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="111"/>
-      <c r="E15" s="183" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="111"/>
-      <c r="G15" s="183" t="s">
+      <c r="F15" s="68"/>
+      <c r="G15" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="110"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="183" t="s">
+      <c r="H15" s="70"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="111"/>
-      <c r="L15" s="183" t="s">
+      <c r="K15" s="68"/>
+      <c r="L15" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="110"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="183" t="s">
+      <c r="M15" s="70"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="111"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="68"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -11241,37 +11237,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="174">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="175" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="111"/>
-      <c r="E16" s="175" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="111"/>
-      <c r="G16" s="182" t="s">
+      <c r="F16" s="68"/>
+      <c r="G16" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="110"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="182" t="s">
+      <c r="H16" s="70"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="111"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="68"/>
+      <c r="L16" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="110"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="70"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="111"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="68"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -11283,37 +11279,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="174">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="175" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="111"/>
-      <c r="E17" s="175" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="111"/>
-      <c r="G17" s="182" t="s">
+      <c r="F17" s="68"/>
+      <c r="G17" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="110"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="182" t="s">
+      <c r="H17" s="70"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="111"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="68"/>
+      <c r="L17" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="110"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="70"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="111"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="68"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -11325,23 +11321,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="174"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="111"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="111"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="68"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -11353,23 +11349,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="174"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="111"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="68"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -11381,23 +11377,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="174"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="182"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="111"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="68"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -11409,23 +11405,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="111"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="68"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -11437,23 +11433,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="174"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="111"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="186"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -11465,23 +11461,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="174"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="110"/>
-      <c r="Q23" s="111"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="68"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -11493,23 +11489,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="174"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="110"/>
-      <c r="Q24" s="111"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="68"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11521,23 +11517,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="111"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="68"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11549,23 +11545,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="174"/>
-      <c r="B26" s="111"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="111"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="68"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11577,23 +11573,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="174"/>
-      <c r="B27" s="111"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="111"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="68"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11605,23 +11601,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="111"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="110"/>
-      <c r="Q28" s="111"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="68"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11633,23 +11629,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="111"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="110"/>
-      <c r="Q29" s="111"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="68"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11661,23 +11657,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="174"/>
-      <c r="B30" s="111"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="110"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="110"/>
-      <c r="Q30" s="111"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="68"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11689,23 +11685,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="127"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="118"/>
-      <c r="N31" s="127"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="118"/>
-      <c r="Q31" s="127"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="75"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12703,62 +12699,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12783,62 +12779,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5F031A-7E07-4362-900B-A8C425623207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70527D20-C9A6-483F-B8F6-85AE08FF8A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -343,13 +343,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>t_taskテーブルのtask_idの値</t>
-    <rPh sb="19" eb="20">
-      <t>アタイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>taskId</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -382,28 +375,6 @@
     </rPh>
     <rPh sb="23" eb="24">
       <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>t_taskテーブルの値(タスク名、カテゴリ情報、期限、担当者情報、ステータス情報、メモ)</t>
-    <rPh sb="11" eb="12">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="28" eb="33">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -737,6 +708,35 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>タスクテーブルの値(タスク名、カテゴリ情報、期限、担当者情報、ステータス情報、メモ)</t>
+    <rPh sb="8" eb="9">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="25" eb="30">
+      <t>タントウシャジョウホウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクテーブルのtask_idの値</t>
+    <rPh sb="16" eb="17">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1691,12 +1691,219 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1706,222 +1913,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1931,6 +1931,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1940,6 +1964,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1958,21 +2015,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2006,15 +2048,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2024,86 +2057,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3920,85 +3920,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4018,46 +4018,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="93" t="s">
+      <c r="G13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="68"/>
-      <c r="I13" s="93" t="s">
+      <c r="H13" s="84"/>
+      <c r="I13" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="70"/>
-      <c r="K13" s="68"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="84"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="93"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="68"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="93"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="68"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="84"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4066,13 +4066,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="94" t="s">
+      <c r="G17" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5086,19 +5086,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="110"/>
+      <c r="F1" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="110"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -5110,194 +5110,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54" t="s">
+      <c r="E2" s="124"/>
+      <c r="F2" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="60">
+      <c r="G2" s="124"/>
+      <c r="H2" s="127">
         <v>46176</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="64"/>
+      <c r="J2" s="119"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="120"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="91"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="95"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="92" t="s">
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="96" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="97"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="111" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="96" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="97"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="111" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="97"/>
+    </row>
+    <row r="9" spans="1:10" ht="180.75" customHeight="1">
+      <c r="A9" s="112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="84"/>
+      <c r="D9" s="98" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="97"/>
+    </row>
+    <row r="10" spans="1:10" ht="309" customHeight="1">
+      <c r="A10" s="113"/>
+      <c r="B10" s="115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="84"/>
+      <c r="D10" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="97"/>
+    </row>
+    <row r="11" spans="1:10" ht="108" customHeight="1">
+      <c r="A11" s="114"/>
+      <c r="B11" s="115" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="84"/>
+      <c r="D11" s="98" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="97"/>
+    </row>
+    <row r="12" spans="1:10" ht="99.75" customHeight="1">
+      <c r="A12" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="72"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="92" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="72"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="92" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="72"/>
-    </row>
-    <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="71" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="72"/>
-    </row>
-    <row r="10" spans="1:10" ht="309" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="71" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="72"/>
-    </row>
-    <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="72"/>
-    </row>
-    <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="71" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="72"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="89"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6288,6 +6288,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -6296,25 +6315,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6333,19 +6333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="110"/>
+      <c r="F1" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="110"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6357,40 +6357,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="119"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="65"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="120"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7747,19 +7747,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="123" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="124"/>
-      <c r="F1" s="123" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="124"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -7771,564 +7771,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="117"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="125" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="126"/>
-      <c r="F2" s="125" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="126"/>
-      <c r="H2" s="108">
+      <c r="G2" s="79"/>
+      <c r="H2" s="61">
         <v>46177</v>
       </c>
-      <c r="I2" s="111" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="112"/>
+      <c r="I2" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="113"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="120"/>
-      <c r="B4" s="121"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="99"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="101"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="104"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="102"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="104"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="102"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="102"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="104"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="102"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="57"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="102"/>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="104"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="102"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="104"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="102"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="104"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="57"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="104"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="57"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="104"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="57"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="104"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="57"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="104"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="104"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="57"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="104"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="104"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="104"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="57"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="57"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="104"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="57"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="104"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="57"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="103"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="104"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="103"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="104"/>
+      <c r="A29" s="55"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="57"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="103"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="103"/>
-      <c r="J30" s="104"/>
+      <c r="A30" s="55"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="57"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="103"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="104"/>
+      <c r="A31" s="55"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="57"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="102"/>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="104"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="57"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="102"/>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="104"/>
+      <c r="A33" s="55"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="57"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="102"/>
-      <c r="B34" s="103"/>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="104"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="57"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="102"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="104"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="57"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="102"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="103"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="104"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="57"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="102"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="104"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="57"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="102"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="104"/>
+      <c r="A38" s="55"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="57"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="102"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="103"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="103"/>
-      <c r="J39" s="104"/>
+      <c r="A39" s="55"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="57"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="102"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
-      <c r="I40" s="103"/>
-      <c r="J40" s="104"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="57"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="102"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="103"/>
-      <c r="D41" s="103"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="103"/>
-      <c r="I41" s="103"/>
-      <c r="J41" s="104"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="57"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="102"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="103"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="103"/>
-      <c r="J42" s="104"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="57"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="102"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="103"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="103"/>
-      <c r="H43" s="103"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="104"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="57"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="102"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="103"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="103"/>
-      <c r="J44" s="104"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="57"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="102"/>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="104"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="57"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="102"/>
-      <c r="B46" s="103"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="103"/>
-      <c r="J46" s="104"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="57"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="105"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="106"/>
-      <c r="D47" s="106"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="106"/>
-      <c r="G47" s="106"/>
-      <c r="H47" s="106"/>
-      <c r="I47" s="106"/>
-      <c r="J47" s="107"/>
+      <c r="A47" s="58"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="60"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
@@ -9337,19 +9337,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="99" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="123" t="s">
+      <c r="A1" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="156"/>
-      <c r="F1" s="123" t="s">
+      <c r="E1" s="170"/>
+      <c r="F1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="156"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -9361,275 +9361,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="125" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="141"/>
-      <c r="F2" s="125" t="s">
+      <c r="E2" s="144"/>
+      <c r="F2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="141"/>
-      <c r="H2" s="108">
+      <c r="G2" s="144"/>
+      <c r="H2" s="61">
         <v>46177</v>
       </c>
-      <c r="I2" s="111" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="112"/>
+      <c r="I2" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="150"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="164"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="105"/>
-      <c r="B4" s="106"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="151"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="165"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="160" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="162"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="171" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="173"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="158"/>
-      <c r="J6" s="163"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="134"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="164"/>
-      <c r="B7" s="165"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="165"/>
-      <c r="I7" s="165"/>
-      <c r="J7" s="166"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="167" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="167"/>
+        <v>111</v>
+      </c>
+      <c r="C9" s="152" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="152"/>
       <c r="E9" s="47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="167" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="168"/>
+        <v>106</v>
+      </c>
+      <c r="I9" s="152" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="153"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="103" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="103"/>
+        <v>104</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="56"/>
       <c r="E10" s="42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F10" s="46">
         <v>46203</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="103" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="104"/>
+        <v>101</v>
+      </c>
+      <c r="I10" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="103" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="103"/>
+        <v>94</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="56"/>
       <c r="E11" s="42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F11" s="46">
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="103" t="s">
-        <v>97</v>
-      </c>
-      <c r="J11" s="104"/>
+        <v>96</v>
+      </c>
+      <c r="I11" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
+        <v>94</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="104"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
+        <v>94</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="57"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
+        <v>94</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="104"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="44"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="43"/>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="104"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-      <c r="J16" s="163"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="134"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="157" t="s">
+      <c r="A17" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="158"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="169" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="170"/>
-      <c r="F17" s="170"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="171"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="138"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="157" t="s">
+      <c r="A18" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="158"/>
-      <c r="C18" s="159"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="135"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9642,59 +9642,59 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="172" t="s">
+      <c r="H18" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="158"/>
-      <c r="J18" s="163"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="134"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="129" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B19" s="130"/>
       <c r="C19" s="131"/>
       <c r="D19" s="36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F19" s="36" t="s">
         <v>74</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="173" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="133"/>
-      <c r="J19" s="134"/>
+        <v>125</v>
+      </c>
+      <c r="H19" s="143" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="141"/>
+      <c r="J19" s="142"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="129" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="130"/>
       <c r="C20" s="131"/>
       <c r="D20" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="H20" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="I20" s="133"/>
-      <c r="J20" s="134"/>
+        <v>126</v>
+      </c>
+      <c r="H20" s="140" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" s="141"/>
+      <c r="J20" s="142"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="129" t="s">
@@ -9714,11 +9714,11 @@
       <c r="G21" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="132" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" s="133"/>
-      <c r="J21" s="134"/>
+      <c r="H21" s="140" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" s="141"/>
+      <c r="J21" s="142"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="129" t="s">
@@ -9738,11 +9738,11 @@
       <c r="G22" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="132" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="133"/>
-      <c r="J22" s="134"/>
+      <c r="H22" s="140" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="141"/>
+      <c r="J22" s="142"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="129" t="s">
@@ -9762,23 +9762,23 @@
       <c r="G23" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="132" t="s">
+      <c r="H23" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="I23" s="141"/>
+      <c r="J23" s="142"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="136"/>
-      <c r="C24" s="137"/>
+      <c r="A24" s="154"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="156"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="140"/>
+      <c r="H24" s="157"/>
+      <c r="I24" s="158"/>
+      <c r="J24" s="159"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10759,33 +10759,6 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10802,6 +10775,33 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10821,182 +10821,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="52" t="s">
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52" t="s">
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="52" t="s">
+      <c r="P1" s="110"/>
+      <c r="Q1" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="53"/>
-      <c r="S1" s="52" t="s">
+      <c r="R1" s="110"/>
+      <c r="S1" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="91"/>
+      <c r="T1" s="95"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="180"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="181"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="182"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="126"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="90" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="91"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
+      <c r="T5" s="95"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="92" t="s">
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="72"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="97"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="92" t="s">
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="72"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="97"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11195,37 +11195,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="187" t="s">
+      <c r="B15" s="84"/>
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="174" t="s">
+      <c r="D15" s="84"/>
+      <c r="E15" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="174" t="s">
+      <c r="F15" s="84"/>
+      <c r="G15" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="70"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="174" t="s">
+      <c r="H15" s="83"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="68"/>
-      <c r="L15" s="174" t="s">
+      <c r="K15" s="84"/>
+      <c r="L15" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="174" t="s">
+      <c r="M15" s="83"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="68"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="84"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -11237,37 +11237,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="174">
         <v>1</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="186" t="s">
+      <c r="B16" s="84"/>
+      <c r="C16" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="84"/>
+      <c r="E16" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="175" t="s">
+      <c r="F16" s="84"/>
+      <c r="G16" s="182" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="175" t="s">
+      <c r="H16" s="83"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="177" t="s">
+      <c r="K16" s="84"/>
+      <c r="L16" s="178" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="177" t="s">
+      <c r="M16" s="83"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="178" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="68"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="84"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -11279,37 +11279,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="174">
         <v>2</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="186" t="s">
+      <c r="B17" s="84"/>
+      <c r="C17" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="186" t="s">
+      <c r="D17" s="84"/>
+      <c r="E17" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="175" t="s">
+      <c r="F17" s="84"/>
+      <c r="G17" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="175" t="s">
+      <c r="H17" s="83"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="182" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="68"/>
-      <c r="L17" s="177" t="s">
+      <c r="K17" s="84"/>
+      <c r="L17" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="177" t="s">
+      <c r="M17" s="83"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="178" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="68"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="84"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -11321,23 +11321,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="186"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="177"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="177"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="68"/>
+      <c r="A18" s="174"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="83"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="84"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -11349,23 +11349,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="177"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="177"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="68"/>
+      <c r="A19" s="174"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="84"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -11377,23 +11377,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="177"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="177"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="68"/>
+      <c r="A20" s="174"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="83"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="84"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -11405,23 +11405,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="177"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="68"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="84"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -11433,23 +11433,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="177"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="177"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="68"/>
+      <c r="A22" s="174"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="84"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -11461,23 +11461,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="177"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="177"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="68"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="84"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -11489,23 +11489,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="177"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="177"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="68"/>
+      <c r="A24" s="174"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="84"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11517,23 +11517,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="177"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="68"/>
+      <c r="A25" s="174"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="175"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="84"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11545,23 +11545,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="68"/>
+      <c r="A26" s="174"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="175"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="84"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11573,23 +11573,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="177"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="68"/>
+      <c r="A27" s="174"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="84"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11601,23 +11601,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="68"/>
+      <c r="A28" s="174"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="175"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="84"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11629,23 +11629,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="177"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="68"/>
+      <c r="A29" s="174"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="175"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="83"/>
+      <c r="Q29" s="84"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11657,23 +11657,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="177"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="68"/>
+      <c r="A30" s="174"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="84"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11685,23 +11685,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="188"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="75"/>
+      <c r="A31" s="176"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="100"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12699,6 +12699,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12723,118 +12835,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70527D20-C9A6-483F-B8F6-85AE08FF8A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8486831D-762A-4C40-B6EF-CD86556A4F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -404,10 +404,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-edit-form.jsp, task-delete-form.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>〇</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -590,32 +586,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">A1:タスク情報が存在しない場合
-A1-1:基本フロー2でシステムはタスク情報が0件であることを確認する。
-A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
-A2:メモ、期限の任意項目が未入力の場合
-A2-1:基本フロー5でシステムが任意項目の値を確認する。
-A2-2:システムが任意項目がNULLであることを確認する。
-A2-3:システムが空文字を設定する。
-A2-4:システムが一覧表示画面の任意項目で空文字を表示する。
-A1:タスク未選択で削除ボタン押下した場合
-A1-1:基本フロー8でシステムはタスク未選択を検出する
-A1-2:システムは一覧画面を再表示する
-A1-3:システムは「削除するタスクを選択してください。」と表示する
-A1:タスク未選択で編集ボタン押下した場合
-A1-1:基本フロー8でシステムはタスク未選択を検出する
-A1-2:システムは一覧画面を再表示する
-A1-3:システムは「編集するタスクを選択してください。」と表示する
-</t>
-    <rPh sb="354" eb="356">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="427" eb="429">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t xml:space="preserve">登録済みタスクの一覧の表示、または「登録されているタスクはありません。」というメッセージが表示される
 削除、編集画面への遷移
 </t>
@@ -629,45 +599,6 @@
       <t>ヘンシュウガメン</t>
     </rPh>
     <rPh sb="60" eb="62">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
-2.システムがデータベースからタスク情報を取得する。
-3:システムがログイン中のユーザIDとタスクの担当者IDを比較する。
-6:担当者IDがログイン中のユーザIDと一致したら該当タスクにラジオボタンを表示する。
-7. システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
-8.従業員はラジオボタンを選択する。
-8.従業員は削除ボタンか編集ボタンを押下する。
-9.削除画面か編集画面へ遷移する。
-</t>
-    <rPh sb="114" eb="116">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="127" eb="129">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="189" eb="192">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="200" eb="202">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="208" eb="211">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="217" eb="219">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="224" eb="228">
-      <t>サクジョガメン</t>
-    </rPh>
-    <rPh sb="230" eb="234">
-      <t>ヘンシュウガメン</t>
-    </rPh>
-    <rPh sb="235" eb="237">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -735,6 +666,33 @@
     <rPh sb="16" eb="17">
       <t>アタイ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskEditServlet, task-delete-form.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
+2.システムがログイン中のユーザIDを取得する。
+3.システムがデータベースからタスク情報を取得する。
+4.システムがログイン中のユーザIDとタスクの担当者IDを比較する。
+5.システムが担当者IDとログイン中のユーザIDが一致するタスクにラジオボタンを表示する。
+6.システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+7.ステムがタスク一覧画面を表示する。
+</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A1:タスク情報が存在しない場合
+A1-1:基本フロー2でシステムはタスク情報が0件であることを確認する。
+A1-2:システムが一覧表示画面に「登録されているタスクはありません。」を表示する。
+A2:メモ、期限の任意項目が未入力の場合
+A2-1:基本フロー6でシステムが任意項目がNULLであることを確認する
+A2-2:システムが空文字を設定する。
+A2-3:システムが一覧表示画面の任意項目で空文字を表示する。
+</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1691,48 +1649,330 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1763,15 +2003,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1781,281 +2015,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2063,47 +2054,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3920,85 +3878,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="113"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4018,46 +3976,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="89" t="s">
+      <c r="E8" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="84"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="111"/>
+      <c r="I13" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="83"/>
-      <c r="K13" s="84"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="111"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="82"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="84"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="111"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="82"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="84"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="111"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4066,13 +4024,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="85" t="s">
+      <c r="G17" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5086,19 +5044,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="118"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="110"/>
+      <c r="G1" s="118"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -5110,194 +5068,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="123" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="124"/>
-      <c r="F2" s="123" t="s">
+      <c r="E2" s="120"/>
+      <c r="F2" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="124"/>
-      <c r="H2" s="127">
+      <c r="G2" s="120"/>
+      <c r="H2" s="125">
         <v>46176</v>
       </c>
-      <c r="I2" s="116" t="s">
+      <c r="I2" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="119"/>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="120"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="130"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="121"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="93" t="s">
+      <c r="B5" s="146"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="95"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="153"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="96" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="135"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="110"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="154" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="135"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="133" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="110"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="154" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="135"/>
+    </row>
+    <row r="9" spans="1:10" ht="137.25" customHeight="1">
+      <c r="A9" s="147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="111"/>
+      <c r="D9" s="134" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="135"/>
+    </row>
+    <row r="10" spans="1:10" ht="177.75" customHeight="1">
+      <c r="A10" s="148"/>
+      <c r="B10" s="132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="111"/>
+      <c r="D10" s="134" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="135"/>
+    </row>
+    <row r="11" spans="1:10" ht="108" customHeight="1">
+      <c r="A11" s="149"/>
+      <c r="B11" s="132" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="111"/>
+      <c r="D11" s="134" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="135"/>
+    </row>
+    <row r="12" spans="1:10" ht="99.75" customHeight="1">
+      <c r="A12" s="133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="110"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="134" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="97"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="111" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="96" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="97"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="111" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="97"/>
-    </row>
-    <row r="9" spans="1:10" ht="180.75" customHeight="1">
-      <c r="A9" s="112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="98" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="97"/>
-    </row>
-    <row r="10" spans="1:10" ht="309" customHeight="1">
-      <c r="A10" s="113"/>
-      <c r="B10" s="115" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="84"/>
-      <c r="D10" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="97"/>
-    </row>
-    <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="114"/>
-      <c r="B11" s="115" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="98" t="s">
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="135"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="137"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="97"/>
-    </row>
-    <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="111" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="98" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="97"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="90" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="92"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="151"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6288,17 +6246,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -6307,14 +6262,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6333,19 +6291,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="118"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="110"/>
+      <c r="G1" s="118"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6357,40 +6315,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="119"/>
+      <c r="A2" s="142"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="129"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="120"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="130"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="121"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="131"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7747,19 +7705,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="162"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="170"/>
+      <c r="F1" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="170"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -7771,564 +7729,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="171"/>
+      <c r="F2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="61">
+      <c r="G2" s="171"/>
+      <c r="H2" s="70">
         <v>46177</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="66"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="160"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="73"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="161"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="156"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="55"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="55"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="98"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="55"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="57"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="98"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="55"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="57"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="55"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="57"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="55"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="57"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="55"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="57"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="55"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="57"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="55"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="57"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="98"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="55"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="55"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="98"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="55"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="98"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="55"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="57"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="98"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="55"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="57"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="98"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="55"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="57"/>
+      <c r="A20" s="82"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="98"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="55"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="57"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="98"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="55"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
+      <c r="A22" s="82"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="55"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="98"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="57"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="98"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="57"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="98"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="55"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="57"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="98"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="57"/>
+      <c r="A27" s="82"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="98"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="55"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="57"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="98"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="55"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="57"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="98"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="55"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="57"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="98"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="55"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="57"/>
+      <c r="A31" s="82"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="98"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="55"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="57"/>
+      <c r="A32" s="82"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="98"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="55"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="57"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="98"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="55"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="57"/>
+      <c r="A34" s="82"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="98"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="55"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="57"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="98"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="55"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="57"/>
+      <c r="A36" s="82"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="98"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="55"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="57"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="98"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="55"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="57"/>
+      <c r="A38" s="82"/>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="98"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="55"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="57"/>
+      <c r="A39" s="82"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="98"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="55"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="57"/>
+      <c r="A40" s="82"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="98"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="55"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="57"/>
+      <c r="A41" s="82"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="98"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="55"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="57"/>
+      <c r="A42" s="82"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="98"/>
     </row>
     <row r="43" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A43" s="55"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="57"/>
+      <c r="A43" s="82"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="98"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="55"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="57"/>
+      <c r="A44" s="82"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="98"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="55"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="57"/>
+      <c r="A45" s="82"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="98"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="55"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="57"/>
+      <c r="A46" s="82"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="83"/>
+      <c r="I46" s="83"/>
+      <c r="J46" s="98"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A47" s="58"/>
-      <c r="B47" s="59"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="60"/>
+      <c r="A47" s="84"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
+      <c r="I47" s="85"/>
+      <c r="J47" s="157"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="49" spans="10:10" ht="12.75" customHeight="1"/>
@@ -9337,19 +9295,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="76" t="s">
+      <c r="A1" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="90"/>
+      <c r="F1" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="90"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -9361,262 +9319,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="55"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="144"/>
-      <c r="F2" s="78" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="61">
+      <c r="G2" s="65"/>
+      <c r="H2" s="70">
         <v>46177</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="55"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="164"/>
+      <c r="A3" s="82"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="58"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="148"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="165"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="171" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="173"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="132" t="s">
+      <c r="A6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="97"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="55"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="57"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="98"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="45"/>
       <c r="B9" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="152"/>
+      <c r="C9" s="102" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="102"/>
       <c r="E9" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H9" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="152" t="s">
         <v>105</v>
       </c>
-      <c r="J9" s="153"/>
+      <c r="I9" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="103"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="45"/>
       <c r="B10" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="56"/>
+      <c r="C10" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="83"/>
       <c r="E10" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="46">
         <v>46203</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="57"/>
+      <c r="I10" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="45"/>
       <c r="B11" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="56"/>
+        <v>93</v>
+      </c>
+      <c r="C11" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="83"/>
       <c r="E11" s="42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F11" s="46">
         <v>46295</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="J11" s="57"/>
+      <c r="I11" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="45"/>
       <c r="B12" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
+        <v>93</v>
+      </c>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="57"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="45"/>
       <c r="B13" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
+        <v>93</v>
+      </c>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="57"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="45"/>
       <c r="B14" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
+        <v>93</v>
+      </c>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="42"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="57"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="98"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="44"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="43"/>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="132" t="s">
+      <c r="A16" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="97"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="136" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="138"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="104" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="106"/>
       <c r="I17" s="40" t="s">
         <v>27</v>
       </c>
@@ -9625,11 +9583,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="132" t="s">
+      <c r="A18" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="133"/>
-      <c r="C18" s="135"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="40" t="s">
         <v>29</v>
       </c>
@@ -9642,18 +9600,18 @@
       <c r="G18" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="139" t="s">
+      <c r="H18" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="134"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A19" s="129" t="s">
+      <c r="A19" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="130"/>
-      <c r="C19" s="131"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="36" t="s">
         <v>90</v>
       </c>
@@ -9664,20 +9622,20 @@
         <v>74</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="H19" s="143" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="I19" s="141"/>
-      <c r="J19" s="142"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="57"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="129" t="s">
+      <c r="A20" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="130"/>
-      <c r="C20" s="131"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="36" t="s">
         <v>86</v>
       </c>
@@ -9688,20 +9646,20 @@
         <v>84</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="140" t="s">
-        <v>122</v>
-      </c>
-      <c r="I20" s="141"/>
-      <c r="J20" s="142"/>
+        <v>123</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="56"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="129" t="s">
+      <c r="A21" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="130"/>
-      <c r="C21" s="131"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="36" t="s">
         <v>82</v>
       </c>
@@ -9714,18 +9672,18 @@
       <c r="G21" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="140" t="s">
-        <v>123</v>
-      </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="H21" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="56"/>
+      <c r="J21" s="57"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="130"/>
-      <c r="C22" s="131"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="36" t="s">
         <v>79</v>
       </c>
@@ -9738,18 +9696,18 @@
       <c r="G22" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="140" t="s">
-        <v>124</v>
-      </c>
-      <c r="I22" s="141"/>
-      <c r="J22" s="142"/>
+      <c r="H22" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" s="56"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="129" t="s">
+      <c r="A23" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="130"/>
-      <c r="C23" s="131"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="37" t="s">
         <v>76</v>
       </c>
@@ -9762,23 +9720,23 @@
       <c r="G23" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="140" t="s">
+      <c r="H23" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="141"/>
-      <c r="J23" s="142"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" spans="1:10" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A24" s="154"/>
-      <c r="B24" s="155"/>
-      <c r="C24" s="156"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="60"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="159"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="63"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10759,6 +10717,33 @@
     <row r="1001" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A24:C24"/>
@@ -10775,33 +10760,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10821,182 +10779,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="122" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="122" t="s">
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="122" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="122" t="s">
+      <c r="P1" s="118"/>
+      <c r="Q1" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="110"/>
-      <c r="S1" s="122" t="s">
+      <c r="R1" s="118"/>
+      <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="95"/>
+      <c r="T1" s="153"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="123"/>
-      <c r="T2" s="186"/>
+      <c r="A2" s="142"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="179"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="179"/>
+      <c r="M2" s="179"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="180"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="125"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="125"/>
-      <c r="T3" s="187"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="181"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="126"/>
-      <c r="T4" s="188"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="182"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="93" t="s">
+      <c r="B5" s="146"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
-      <c r="S5" s="94"/>
-      <c r="T5" s="95"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
+      <c r="R5" s="146"/>
+      <c r="S5" s="146"/>
+      <c r="T5" s="153"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="181" t="s">
+      <c r="A6" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="96" t="s">
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="154" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="97"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="110"/>
+      <c r="T6" s="135"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="96" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="97"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="135"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11195,37 +11153,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="183" t="s">
+      <c r="D15" s="111"/>
+      <c r="E15" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="84"/>
-      <c r="G15" s="183" t="s">
+      <c r="F15" s="111"/>
+      <c r="G15" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="83"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="183" t="s">
+      <c r="H15" s="110"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="84"/>
-      <c r="L15" s="183" t="s">
+      <c r="K15" s="111"/>
+      <c r="L15" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="83"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="183" t="s">
+      <c r="M15" s="110"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="84"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="111"/>
       <c r="R15" s="14" t="s">
         <v>51</v>
       </c>
@@ -11237,37 +11195,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="174">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
-      <c r="B16" s="84"/>
-      <c r="C16" s="175" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="84"/>
-      <c r="E16" s="175" t="s">
+      <c r="D16" s="111"/>
+      <c r="E16" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="84"/>
-      <c r="G16" s="182" t="s">
+      <c r="F16" s="111"/>
+      <c r="G16" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="83"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="182" t="s">
+      <c r="H16" s="110"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="175" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="84"/>
-      <c r="L16" s="178" t="s">
+      <c r="K16" s="111"/>
+      <c r="L16" s="177" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="83"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="178" t="s">
+      <c r="M16" s="110"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="177" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="83"/>
-      <c r="Q16" s="84"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="111"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -11279,37 +11237,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="174">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="175" t="s">
+      <c r="B17" s="111"/>
+      <c r="C17" s="186" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="84"/>
-      <c r="E17" s="175" t="s">
+      <c r="D17" s="111"/>
+      <c r="E17" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="84"/>
-      <c r="G17" s="182" t="s">
+      <c r="F17" s="111"/>
+      <c r="G17" s="175" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="83"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="182" t="s">
+      <c r="H17" s="110"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="84"/>
-      <c r="L17" s="178" t="s">
+      <c r="K17" s="111"/>
+      <c r="L17" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="83"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="178" t="s">
+      <c r="M17" s="110"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="83"/>
-      <c r="Q17" s="84"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="111"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -11321,23 +11279,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="174"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="175"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="84"/>
-      <c r="L18" s="178"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="84"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="83"/>
-      <c r="Q18" s="84"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="177"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="111"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -11349,23 +11307,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="174"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="178"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="84"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="84"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="177"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="111"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -11377,23 +11335,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="174"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="182"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="178"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="84"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="177"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="177"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="111"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -11405,23 +11363,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="84"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="84"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="177"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="177"/>
+      <c r="P21" s="110"/>
+      <c r="Q21" s="111"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -11433,23 +11391,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="174"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="175"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="178"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="83"/>
-      <c r="Q22" s="84"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="186"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="177"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="111"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -11461,23 +11419,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="174"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="84"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="177"/>
+      <c r="M23" s="110"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="177"/>
+      <c r="P23" s="110"/>
+      <c r="Q23" s="111"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -11489,23 +11447,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="174"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="178"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="84"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="84"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="186"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="177"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="111"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -11517,23 +11475,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="84"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="182"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="84"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="186"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="177"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="177"/>
+      <c r="P25" s="110"/>
+      <c r="Q25" s="111"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -11545,23 +11503,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="174"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="178"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="84"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="186"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="111"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -11573,23 +11531,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="174"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="84"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="186"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="111"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="110"/>
+      <c r="Q27" s="111"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -11601,23 +11559,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="84"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="110"/>
+      <c r="Q28" s="111"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -11629,23 +11587,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="84"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="84"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="186"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="111"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="177"/>
+      <c r="P29" s="110"/>
+      <c r="Q29" s="111"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -11657,23 +11615,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="174"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="182"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="178"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="84"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="84"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="177"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="111"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -11685,23 +11643,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="100"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="100"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="91"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="91"/>
-      <c r="Q31" s="100"/>
+      <c r="A31" s="188"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="189"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="189"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="176"/>
+      <c r="H31" s="137"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="176"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="178"/>
+      <c r="M31" s="137"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="137"/>
+      <c r="Q31" s="138"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -12699,62 +12657,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12779,62 +12737,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク一覧表示機能_詳細設計書.xlsx
+++ b/document/タスク一覧表示機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8486831D-762A-4C40-B6EF-CD86556A4F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18607066-DF87-431D-BCBA-C111E738B12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,74 +514,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>任意項目がNULLだった場合空欄になる。メモ、期限項目は空欄可、その他は必須項目</t>
-    <rPh sb="0" eb="4">
-      <t>ニンイコウモク</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>クウラン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>クウラン</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>アドミン娘</t>
     <rPh sb="4" eb="5">
       <t>ムスメ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>登録されているタスク一覧を表示、自身のタスクを選択し編集画面か削除画面へ遷移</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>サクジョガメン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -673,17 +608,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
-2.システムがログイン中のユーザIDを取得する。
-3.システムがデータベースからタスク情報を取得する。
-4.システムがログイン中のユーザIDとタスクの担当者IDを比較する。
-5.システムが担当者IDとログイン中のユーザIDが一致するタスクにラジオボタンを表示する。
-6.システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
-7.ステムがタスク一覧画面を表示する。
-</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t xml:space="preserve">
 A1:タスク情報が存在しない場合
 A1-1:基本フロー2でシステムはタスク情報が0件であることを確認する。
@@ -693,6 +617,73 @@
 A2-2:システムが空文字を設定する。
 A2-3:システムが一覧表示画面の任意項目で空文字を表示する。
 </t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>登録されているタスク一覧を表示</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員がメニュー画面で「タスク一覧」を選択する。
+2.システムがデータベースからタスク情報を取得する。
+3.システムがログイン中のユーザIDとタスクの担当者IDを比較する。
+4.システムがタスク一覧画面にタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを表示する。
+5.システムが担当者IDとログイン中のユーザIDが一致するタスクにラジオボタンを表示する。
+6.システムがタスク一覧画面を表示する。
+</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>任意項目がNULLだった場合空欄になる。メモ、期限項目は空欄可、その他は必須項目。
+ラジオボタンはログイン済みの従業員が担当しているタスク1つだけ選択できる部品</t>
+    <rPh sb="0" eb="4">
+      <t>ニンイコウモク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="56" eb="59">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>タントウ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1649,6 +1640,234 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1658,6 +1877,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1667,6 +1910,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1685,72 +1961,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1760,21 +1991,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1784,284 +2003,56 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3878,85 +3869,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="113"/>
-      <c r="M6" s="113"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="113"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3976,46 +3967,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="116" t="s">
+      <c r="E8" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="113"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="109" t="s">
+      <c r="G13" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="111"/>
-      <c r="I13" s="109" t="s">
+      <c r="H13" s="75"/>
+      <c r="I13" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="110"/>
-      <c r="K13" s="111"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="75"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="109"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="111"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="75"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="109"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="111"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="75"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4024,13 +4015,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="112" t="s">
+      <c r="G17" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5044,19 +5035,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="118"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -5068,194 +5059,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="119" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="120"/>
-      <c r="F2" s="119" t="s">
+      <c r="E2" s="88"/>
+      <c r="F2" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="120"/>
-      <c r="H2" s="125">
+      <c r="G2" s="88"/>
+      <c r="H2" s="91">
         <v>46176</v>
       </c>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="129"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="130"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="146"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="152" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="146"/>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="153"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="56"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="154" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="135"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="154" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="135"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="59"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="110"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="154" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="135"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="59"/>
     </row>
     <row r="9" spans="1:10" ht="137.25" customHeight="1">
-      <c r="A9" s="147" t="s">
+      <c r="A9" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="134" t="s">
+      <c r="C9" s="75"/>
+      <c r="D9" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="135"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="1:10" ht="177.75" customHeight="1">
-      <c r="A10" s="148"/>
-      <c r="B10" s="132" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="134" t="s">
+      <c r="C10" s="75"/>
+      <c r="D10" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="59"/>
+    </row>
+    <row r="11" spans="1:10" ht="108" customHeight="1">
+      <c r="A11" s="78"/>
+      <c r="B11" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="75"/>
+      <c r="D11" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="59"/>
+    </row>
+    <row r="12" spans="1:10" ht="99.75" customHeight="1">
+      <c r="A12" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="59"/>
+    </row>
+    <row r="13" spans="1:10" ht="48" customHeight="1">
+      <c r="A13" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="52"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="135"/>
-    </row>
-    <row r="11" spans="1:10" ht="108" customHeight="1">
-      <c r="A11" s="149"/>
-      <c r="B11" s="132" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="134" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="135"/>
-    </row>
-    <row r="12" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A12" s="133" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="110"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="134" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="135"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="136" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="150" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="151"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6246,6 +6237,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -6254,25 +6264,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6291,19 +6282,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="117" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="118"/>
-      <c r="F1" s="117" t="s">
+      <c r="E1" s="73"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="118"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6315,40 +6306,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="129"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="130"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="143"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="131"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7705,19 +7696,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="89" t="s">
+      <c r="B1" s="114"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="89" t="s">
+      <c r="E1" s="123"/>
+      <c r="F1" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="123"/>
       <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
@@ -7729,564 +7720,564 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="64" t="s">
+      <c r="A2" s="116"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="171"/>
-      <c r="F2" s="64" t="s">
+      <c r="E2" s="125"/>
+      <c r="F2" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="171"/>
-      <c r="H2" s="70">
+      <c r="G2" s="125"/>
+      <c r="H2" s="107">
         <v>46177</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="110" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="160"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="167"/>
-      <c r="B4" s="168"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="161"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="113"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="79"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="156"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="100"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="82"/>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="98"/>
+      <c r="A6" s="101"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="103"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="98"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="103"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="82"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="98"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="103"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="82"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="98"/>
+      <c r="A9" s="101"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="103"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="82"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="98"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="103"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="98"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="103"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="98"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="103"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="98"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="82"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="98"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="103"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="82"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="98"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="103"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="98"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="103"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="82"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="98"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="103"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="98"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="103"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="82"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="98"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="103"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="82"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="98"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="98"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="103"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="82"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="98"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="103"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="82"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="98"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="102"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="103"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="82"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="98"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="103"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="82"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="98"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="103"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="82"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="98"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="103"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="82"/>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="98"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="103"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="82"/>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="98"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="103"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="82"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="98"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="103"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="82"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="98"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="102"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="103"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="82"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="98"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="103"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="82"/>
-      <c r="B32" s="83"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="98"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="103"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="82"/>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="98"/>
+      <c r="A33" s="101"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="103"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="82"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="98"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="102"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="103"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="82"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="98"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="102"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="102"/>
+      <c r="E35" s="102"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="103"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="82"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="98"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="102"/>
+      <c r="C36" s="102"/>
+      <c r="D36" s="102"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="103"/>
     </row>
     <row r="37" spans="1:10" ht=